--- a/data/livestreams.xlsx
+++ b/data/livestreams.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J77"/>
+  <dimension ref="A1:J106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2342,11 +2342,763 @@
           <t>https://youtube.com/watch?v=02V_bAxmxfc</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Global dialogue on artificial intelligence governance - Opening session</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Watch the plenary presentation of the annual report of the multidisciplinary Independent International Scientific Panel on Artificial ...</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-07-06T07:10:36Z</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=s_q3TU6ZKUk</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>No Holds Barred Radio Automation</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-06-29T04:02:01Z</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=EzhSAzTqKtM</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>【FGU 4KLiveCam｜GenAI LiveChat】佛光大學＠蘭陽平原 即時影像 Lanyang Plain Live View</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>即時鳥瞰  美景共享× GenAI即時景色聊聊  ｜ 佛光大學正式啟用「即時影像網路直播」！  ✨ 坐落於礁溪林美山上的佛大，透過網 ...</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-07-06T07:30:31Z</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=GS0p1OoeoDM</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>XonoBots — Professional Tools for YouTube &amp;amp; Twitch Creators | Grow Faster with Automation</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>XonoBots — Professional Tools for YouTube and Twitch Creators Take your content to the next level with XonoBots, a powerful ...</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-02-12T07:00:00Z</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=5N22-QgCFqY</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Live Stream Bot Automation Tool | 유튜브 채널 자동 성장 봇</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>This video introduces a powerful Live Stream Automation Bot designed to help creators manage chat activity, comments, likes, ...</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-02-14T07:30:00Z</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=xk8efUPDXXU</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>What Is AI ? | Learning Videos For Kids | Artificial Intelligence Explained | EMoMee</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Hello Curious Kids! In today's fun cartoon, we dive into one of those big “WHY?” questions curious kids like you love to ask!</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-06-02T09:57:27Z</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=hs67716TQ3U</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>LIVE: Opening Session of Global Dialogue on Artificial Intelligence Governance | Day 1</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>The Global Dialogue on Artificial Intelligence Governance begins with its Day 1 Opening Session, bringing together government ...</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-07-06T09:15:24Z</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=l-N7mbtTtaw</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Automate With Python| Live Code |  AI Engineer | Back to Basics After AI Layoff 2026 |</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Learn Data Engineering from scratch with practical examples, real-world projects, and industry best practices. In this video, you'll ...</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-07-06T07:30:20Z</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=dpwt9QmVYLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>How To Get Watching &amp;amp; Likes, Chats in Live Streams &amp;amp; Grow With Pbh STORE Softwares With Mobile Or PC</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>How To Get Watching &amp; Likes, Chats in Live Streams &amp; Grow With Pbh STORE Softwares With Mobile Or PC #Bot #StreamBot ...</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-02-12T05:40:00Z</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=9-mmDf7FBX4</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Inside Modern Factory: How Plantain Chips Are Processed | Full Production Line (24/7 LIVE)</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Welcome to AGRO FACTORY SECRETS — your ultimate destination for discovering how everyday foods are processed inside ...</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-04-17T16:10:00Z</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=A6ifA-SUfm8</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>YouTube Live View Bot ❤️‍🔥YOUTUBE VIEW BOT | LIVE Growth Tool Demo — Increase Likes, Subs &amp;amp; Comments</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Welcome to the LIVE demo of XONO Bots — Live Stream Automation Software This stream shows how you can manage ...</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-04-20T09:15:00Z</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=JMd-1ikizdA</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Turn $100 into $1,000,000 Challenge with Trading Bot 🔥 MT4 Real Account ( FREE EA )</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Trading Bot Challenge (LIVE) What if you could turn a small account into something massive… using pure automation? In this live ...</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-06-29T04:42:59Z</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=VhAL5PoisiE</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>YBE AI – Your All-in-One Free AI Platform 🇮🇳</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Link ai.ybeapp.com **Welcome to YBE AI – Your All-in-One Free AI Platform!** Experience the power of artificial intelligence ...</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-07-02T18:43:33Z</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=vAxlkLjP-Xs</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Welcome to SmartAISchool! 🚀</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Dive into the world of Artificial Intelligence, tech trends, and digital skills with us! From AI tutorials, tool reviews, and industry ...</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-07-06T04:50:00Z</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=GRPzhZPzV0g</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>My firmware for livestream projects with AI features.</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Hello everyone! This test-mode livestream is launched to verify stable workflow of my own software for live streaming in a high ...</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-04-20T21:23:11Z</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=_dyOinvkmIc</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>XAUUSD LIVE AI FOREX TRADING 06-07-2026 -- FRANK H1 BOT #forex #frankbot #xauusd #bot</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Frank Bot – Live Automated Forex Trading Frank Bot is a fully automated Forex trading system built to execute a proven ...</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-07-06T10:16:46Z</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=VB6VTeI3Hek</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>🔴LIVE: Fable 5 vs Gemini 3.1 AI Trading EA on XAUUSD (MT5/MT4) — DoIt Alpha Pulse AI</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>LIVE forward test of my AI Trading EA for MetaTrader 5 / MetaTrader 4: DoIt Alpha Pulse AI. Today we're also testing Gemini 3.1 ...</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-06-26T08:13:18Z</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=DFnrNNTJ4Vk</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Make Money With Claude AI — The Complete FREE Course (24/7 Live)</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>The complete FREE course on making money with Claude AI — now running 24/7. 16 modules, 90 minutes, on loop. ▷ Watch the ...</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026-07-04T10:16:43Z</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=tkMFq7Jrr2Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Live News &amp;amp; World Events — 24/7 | Defaxon Live (English)</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Defaxon Live — 24/7 AI World-Event Intelligence A live, AI-curated map of what's happening on Earth — every domain, every ...</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026-06-27T09:16:18Z</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=E20okCc9MOQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>🔴 LIVE: 100+ AI Agents Trading ETH Futures | Real PNL 24/7</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Trading Wars — Clash of Agents 100+ autonomous AI agents battle every 5 minutes to win the next trade. Watch AI agents ...</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2026-06-16T18:07:58Z</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=PcWuca4Q6Dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>AI Automation Masterclass - Demo for Small Businesses &amp; ...</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>AI Automation Masterclass - Demo for Small Businesses &amp; ...
+Eventbrite
+https://www.eventbrite.com › ai-auto...</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Webinar: AI Automation Processes – How to Boost Efficiency ...</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Webinar: AI Automation Processes – How to Boost Efficiency ...
+YouTube · HYVE
+&gt;60 lượt xem: · 8 tháng trước</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>AI Automation Fundamentals: An Introduction to Zapier &amp; ...</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>AI Automation Fundamentals: An Introduction to Zapier &amp; ...
+Eventbrite
+https://www.eventbrite.com › ai-auto...</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>FHMoms Free Webinar AI Automation Webinar with live demo ...</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>FHMoms Free Webinar AI Automation Webinar with live demo ...
+YouTube · Filipina Homebased Moms
+&gt;530 lượt xem: · 4 tháng trước</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>AI Automation Masterclass Replay, n8n Training &amp; AI ...</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>AI Automation Masterclass Replay, n8n Training &amp; AI ...
+YouTube · Solomon Christ AI + Automation Mastery
+&gt;740 lượt xem: · 1 tháng trước</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>AI Automation Full Course 2026 [FREE] | AI Automation ...</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>AI Automation Full Course 2026 [FREE] | AI Automation ...
+YouTube · Simplilearn
+&gt;31,8 N lượt xem: · 1 tháng trước</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Be WOWED by Live AI &amp; Automation — Watch It Build and ...</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Be WOWED by Live AI &amp; Automation — Watch It Build and ...
+Eventbrite
+https://www.eventbrite.com › be-wow...</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>AI + Automation Study Hall Live, n8n Workflows &amp; Business AI</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>AI + Automation Study Hall Live, n8n Workflows &amp; Business AI
+YouTube · Solomon Christ AI + Automation Mastery
+&gt;120 lượt xem: · 2 ngày trước</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>AI Systems with Crew AI: Build Powerful Automation | Live ...</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>AI Systems with Crew AI: Build Powerful Automation | Live ...
+YouTube · Interview Kickstart India
+&gt;100 lượt xem: · 3 tuần trước</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/livestreams.xlsx
+++ b/data/livestreams.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J106"/>
+  <dimension ref="A1:J123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3093,12 +3093,420 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>[Tutorial] Create a Charity Livestream Event Using Twitch and ...</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>[Tutorial] Create a Charity Livestream Event Using Twitch and ...
+YouTube · Point of Pride
+&gt;240 lượt xem: · 4 năm trước</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>{LIVESTREAM} Charity Livestream! #ColouringForCancer ...</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>{LIVESTREAM} Charity Livestream! #ColouringForCancer ...
+YouTube · Axik Fumbles
+&gt;1,1 N lượt xem: · 5 tháng trước</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Charity Livestream 2023</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Charity Livestream 2023
+YouTube
+https://m.youtube.com › playlist</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Charity Livestream TerraFirmaCraft Part 1 of 2</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Charity Livestream TerraFirmaCraft Part 1 of 2
+Twitch · kijkers
+&gt;1,6 N lượt xem: · 13 năm trước</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>OpenFront Charity Livestream!</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>OpenFront Charity Livestream!
+YouTube · Ultimus_Rex
+&gt;7,4 N lượt xem: · 6 tháng trước</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Charity livestream(noch zu sortieren)</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Charity livestream(noch zu sortieren)
+YouTube Music
+https://music.youtube.com › playlist</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>E Sports Charity Livestream</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>E Sports Charity Livestream
+YouTube · Suffolk New College
+&gt;10 lượt xem: · 2 tháng trước</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>How To Run A Successful Charity Livestream - 7 Tips</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>How To Run A Successful Charity Livestream - 7 Tips
+YouTube · Gaming Careers
+&gt;28,4 N lượt xem: · 7 năm trước</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Fallout 4 Hope | Charity LIVE Stream</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Fallout 4 Hope | Charity LIVE Stream
+YouTube · Gopher
+&gt;3,2 N lượt xem: · 1 tuần trước</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Extra Life Charity Live Stream 2024</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Extra Life Charity Live Stream 2024
+YouTube · Aaron Longstaff
+&gt;3,2 N lượt xem: · 1 năm trước</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Finding Pride! A Charity Live Stream Event June 14th! Time TBA!</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Finding Pride! A Charity Live Stream Event June 14th! Time TBA!
+YouTube · BogWitchSophie
+3 lượt xem · 1 năm trước</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Fallout 4 Hope | Charity LIVE Stream !donate</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Fallout 4 Hope | Charity LIVE Stream !donate
+YouTube · Gopher
+&gt;4,3 N lượt xem: · 5 ngày trước</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>First Charity Live Stream Event - Hilarious Highlights</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>First Charity Live Stream Event - Hilarious Highlights
+YouTube · LPX Tech
+&gt;140 lượt xem: · 11 năm trước</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>charitylivestream</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>charitylivestream
+YouTube
+https://www.youtube.com › hashtag › c...</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Alex Hirsch &amp; Pals BIG CHARITY DRAW-A-THON for the LA ...</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Alex Hirsch &amp; Pals BIG CHARITY DRAW-A-THON for the LA ...
+YouTube · TheMysteryofGF
+&gt;188,4 N lượt xem: · 1 năm trước</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Whitney Teaches Sam Burlesque | Sam's 24-Hour Charity ...</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Whitney Teaches Sam Burlesque | Sam's 24-Hour Charity ...
+YouTube · Critical Role
+&gt;45,4 N lượt xem: · 2 tháng trước</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Sharing is Caring | Charity #live #livestream #philippines ...</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Sharing is Caring | Charity #live #livestream #philippines ...
+YouTube · FARMGIRL NG ISABELA
+&gt;1,5 N lượt xem: · 2 tuần trước</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/livestreams.xlsx
+++ b/data/livestreams.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J123"/>
+  <dimension ref="A1:J129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3501,12 +3501,156 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Charity Network Webinar: Building Your Voice &amp; Visibility</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Charity Network Webinar: Building Your Voice &amp; Visibility
+eventbrite.com
+https://www.eventbrite.com › charity-...</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Webinar: Is your charity AI ready? [Hear from a real range ...</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Webinar: Is your charity AI ready? [Hear from a real range ...
+Eventbrite
+https://www.eventbrite.com › webinar...</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Best Charity &amp; Causes Seminar Online - Events &amp; Activities</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Best Charity &amp; Causes Seminar Online - Events &amp; Activities
+Eventbrite
+https://www.eventbrite.com › online › charity-and-caus...</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Charity &amp; Causes events Online</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Charity &amp; Causes events Online
+Eventbrite
+https://www.eventbrite.com › Online › Online Events</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>YPI Charity Webinar September 2024</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>YPI Charity Webinar September 2024
+Vimeo
+https://vimeo.com › ... › Videos</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Charity Webinar - Fundraising Events 2025</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Charity Webinar - Fundraising Events 2025
+YouTube · Eventmaster
+&gt;50 lượt xem: · 1 năm trước</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/livestreams.xlsx
+++ b/data/livestreams.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J129"/>
+  <dimension ref="A1:J147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3645,12 +3645,444 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Small Charity Week 2026: Fundamentals of Fundraising webinar</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Small Charity Week 2026: Fundamentals of Fundraising webinar
+YouTube · Big Give
+&gt;70 lượt xem: · 1 tháng trước</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Plan a Perfect Charity Event in 14 Steps</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Plan a Perfect Charity Event in 14 Steps
+Eventbrite
+https://www.eventbrite.com › blog › h...</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Small Charity Week 2025: Application Webinar</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Small Charity Week 2025: Application Webinar
+YouTube · Big Give
+&gt;920 lượt xem: · 1 năm trước</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Twitch's Charity Tool for Creators</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Twitch's Charity Tool for Creators
+Twitch
+https://help.twitch.tv › twitch-charity</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>How to Organise a Charity Fundraising Event (UK Fundraising ...</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>How to Organise a Charity Fundraising Event (UK Fundraising ...
+YouTube · Evolve Catalyst | Charity Management Consultancy
+&gt;200 lượt xem: · 4 tháng trước</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>OVER 2,000 PEOPLE PARTICIPATE IN CHARITY WALK AND ...</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>OVER 2,000 PEOPLE PARTICIPATE IN CHARITY WALK AND ...
+YouTube · HTV Tin Tức
+&gt;280 lượt xem: · 1 tuần trước</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>How to Run a Successful Charity Livestream</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>How to Run a Successful Charity Livestream
+YouTube · Funds2Orgs
+&gt;370 lượt xem: · 6 năm trước</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Mastering Charity Events: Your Ultimate Guide to Making a ...</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Mastering Charity Events: Your Ultimate Guide to Making a ...
+YouTube · Event Crowd
+&gt;120 lượt xem: · 2 năm trước</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>How to Set Clear Goals for a Successful Charity Event</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>How to Set Clear Goals for a Successful Charity Event
+YouTube
+https://m.youtube.com › shorts</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Panel Discussion - The evolution of event fundraising</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Panel Discussion - The evolution of event fundraising
+YouTube · Charity Digital
+&gt;20 lượt xem: · 1 năm trước</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>What is Livestream Fundraising? | Funraise Nonprofit ...</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>What is Livestream Fundraising? | Funraise Nonprofit ...
+YouTube · Funraise
+&gt;240 lượt xem: · 6 năm trước</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Fundraising Ideas for Live Streaming Online</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Fundraising Ideas for Live Streaming Online
+YouTube · PTZOptics
+&gt;350 lượt xem: · 1 năm trước</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>How To Use Facebook Live For Fundraising Events</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>How To Use Facebook Live For Fundraising Events
+YouTube · Aplos
+&gt;1,5 N lượt xem: · 5 năm trước</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>How to do a virtual livestream fundraiser with Eventgroove ...</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>How to do a virtual livestream fundraiser with Eventgroove ...
+YouTube · Eventgroove
+&gt;160 lượt xem: · 4 năm trước</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>The New Telethon How Live Streaming Has Changed ...</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>The New Telethon How Live Streaming Has Changed ...
+YouTube · Neon One
+&gt;360 lượt xem: · 5 năm trước</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Livestream Fundraising — With Max (CEO) &amp; Tori (Customer ...</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Livestream Fundraising — With Max (CEO) &amp; Tori (Customer ...
+YouTube · Givebutter
+&gt;1,8 N lượt xem: · 6 năm trước</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Facebook Live Fundraising Best Practices for Nonprofits ...</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Facebook Live Fundraising Best Practices for Nonprofits ...
+YouTube · MobileCause now GiveSmart
+&gt;2 N lượt xem: · 9 năm trước</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>How to Increase Attendance at Your Next Fundraising Event ...</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>How to Increase Attendance at Your Next Fundraising Event ...
+YouTube · MobileCause now GiveSmart
+&gt;9,6 N lượt xem: · 6 năm trước</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/livestreams.xlsx
+++ b/data/livestreams.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J147"/>
+  <dimension ref="A1:J165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4077,12 +4077,444 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
-      <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>[webinar] Online Event Fundraiser: Lessons to Share</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>[webinar] Online Event Fundraiser: Lessons to Share
+Vimeo
+https://vimeo.com › ... › Videos</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>[Webinar] Hit your fundraising goals without hosting another ...</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>[Webinar] Hit your fundraising goals without hosting another ...
+YouTube · Givebutter
+&gt;330 lượt xem: · 3 tháng trước</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Monthly trending searches in 67199, Australia Newport</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Monthly trending searches in 67199, Australia Newport
+Eventbrite
+https://www.eventbrite.com › trending › australia--new...</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Charity Fundraiser LIVESTREAM for Mental Health w ...</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Charity Fundraiser LIVESTREAM for Mental Health w ...
+YouTube · Stuff &amp; Whiskey
+&gt;3,1 N lượt xem: · 3 năm trước</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>EPIC Fundraiser Stream for Children's Healthcare</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>EPIC Fundraiser Stream for Children's Healthcare
+YouTube · Jorge Rivera-Herrans
+&gt;167,3 N lượt xem: · 4 tháng trước</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Pledge.to Guide: How to Create a Live Event Display</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Pledge.to Guide: How to Create a Live Event Display
+YouTube · Pledge
+&gt;190 lượt xem: · 1 năm trước</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Stream #WithMe Live Event | Creator Fundraiser</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Stream #WithMe Live Event | Creator Fundraiser
+YouTube · YouTube Originals
+6 năm trước</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>(PAST LIVESTREAM) #TeamSeas Live Count ($30 Million ...</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>(PAST LIVESTREAM) #TeamSeas Live Count ($30 Million ...
+YouTube · YT Battles
+4 năm trước</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>How to Start a Charity Live Stream | Streamlabs</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>How to Start a Charity Live Stream | Streamlabs
+YouTube · Streamlabs
+&gt;17,6 N lượt xem: · 5 năm trước</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Lands Between Fundraiser Stream Benefiting KOI</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Lands Between Fundraiser Stream Benefiting KOI
+YouTube · Noah Caldwell-Gervais
+&gt;10 N lượt xem: · 3 tuần trước</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Massive Holiday Livestream 2025!</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Massive Holiday Livestream 2025!
+YouTube · 3D Printing Nerd
+&gt;26,9 N lượt xem: · 6 tháng trước</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>EPIC Fundraiser Stream for Children's Healthcare Pt. 2</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>EPIC Fundraiser Stream for Children's Healthcare Pt. 2
+YouTube · Jorge Rivera-Herrans
+&gt;93,1 N lượt xem: · 4 tháng trước</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>*• TRUTH or DARE – PRIDE LIVESTREAM FUNDRAISER ...</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>*• TRUTH or DARE – PRIDE LIVESTREAM FUNDRAISER ...
+YouTube · Not-So-Average-Fangirl
+&gt;21,8 N lượt xem: · 1 tuần trước</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>One song, millions raised: The phenomenon of the Polish ...</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>One song, millions raised: The phenomenon of the Polish ...
+YouTube · TVP WORLD
+&gt;10,3 N lượt xem: · 2 tháng trước</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>24 Hour Livestream Fundraiser Event Announcement for CMN ...</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>24 Hour Livestream Fundraiser Event Announcement for CMN ...
+YouTube · DarkTaker1990
+&gt;20 lượt xem: · 4 tuần trước</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>T-Ball Under the Lights Livestream Fundraiser</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>T-Ball Under the Lights Livestream Fundraiser
+YouTube · HPS Stream Team
+4 ngày trước</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>PET NEEDS Van Fundraiser Livestream</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>PET NEEDS Van Fundraiser Livestream
+YouTube · PET NEEDS
+&gt;560 lượt xem: · 10 tháng trước</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>One Beating Heart: A Livestream Fundraiser for Covid-19 ...</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>One Beating Heart: A Livestream Fundraiser for Covid-19 ...
+YouTube · The Midnight
+&gt;70,5 N lượt xem: · 6 năm trước</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/livestreams.xlsx
+++ b/data/livestreams.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J165"/>
+  <dimension ref="A1:J235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4509,12 +4509,1451 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr"/>
-      <c r="F165" t="inlineStr"/>
-      <c r="G165" t="inlineStr"/>
-      <c r="H165" t="inlineStr"/>
-      <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Tokenization Webinar with Apex Capital</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Tokenization Webinar with Apex Capital
+Eventbrite
+https://www.eventbrite.com › tokeniza...</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Webinar: Tokenization in the UAE</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Webinar: Tokenization in the UAE
+YouTube · DigiShares
+&gt;480 lượt xem: · 1 năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Real-World Asset Tokenization | 2-Hour Online Workshop</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Real-World Asset Tokenization | 2-Hour Online Workshop
+Eventbrite
+https://www.eventbrite.com › real-wor...</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Unlocking the Future: Tokenization Webinar with Innowise's ...</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Unlocking the Future: Tokenization Webinar with Innowise's ...
+YouTube · Innowise Global
+&gt;380 lượt xem: · 2 năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Real Estate Tokenization Webinar with Aurora Cloud</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Real Estate Tokenization Webinar with Aurora Cloud
+YouTube · Aurora
+&gt;440 lượt xem: · 2 năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Tokenization Webinar with Alex Chan</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Tokenization Webinar with Alex Chan
+YouTube
+https://www.youtube.com › watch</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Learning with LEVERAGE: Tokenization Webinar, January 10 ...</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Learning with LEVERAGE: Tokenization Webinar, January 10 ...
+YouTube · LeagueofSECUs
+&gt;80 lượt xem: · 3 năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>EMV Tokenization Webinar</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>EMV Tokenization Webinar
+YouTube · Secure Technology Alliance
+&gt;17,2 N lượt xem: · 6 năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Financial security tokenization, Fri, Jul 3, 2026, 12:00 AM</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Financial security tokenization, Fri, Jul 3, 2026, 12:00 AM
+Meetup
+https://www.meetup.com › events</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>EN | Real World Asset Tokenization Live Use Cases Across ...</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>EN | Real World Asset Tokenization Live Use Cases Across ...
+YouTube · MERGE
+&gt;20 lượt xem: · 2 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>XRP CRYPTO TOKENIZATION LIVE NOW!!!!!</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>XRP CRYPTO TOKENIZATION LIVE NOW!!!!!
+YouTube · Oscar Ramos
+&gt;15,2 N lượt xem: · 3 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Explore Tokenization with the DigiShares Webinar Series</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Explore Tokenization with the DigiShares Webinar Series
+YouTube · DigiShares
+&gt;60 lượt xem: · 2 năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>How to Tell If Your Asset Is Ready for Tokenization — Live ...</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>How to Tell If Your Asset Is Ready for Tokenization — Live ...
+YouTube · Stobox
+&gt;130 lượt xem: · 1 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Adversarial Tokenization</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Adversarial Tokenization
+YouTube
+&gt;40 lượt xem: · 11 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>GeneticBPE: Motif-Preserving Tokenization for Robust miRNA ...</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>GeneticBPE: Motif-Preserving Tokenization for Robust miRNA ...
+YouTube
+&gt;20 lượt xem: · 11 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Webinars</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Webinars
+YouTube · DigiShares
+&gt;2,1 N người theo dõi</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Beyond the Hype:Top 3 Risk-First Applications of ...</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Beyond the Hype:Top 3 Risk-First Applications of ...
+Eventbrite
+https://www.eventbrite.com › beyond-...</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Token Cost Management: Bringing Spend Under Control</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Meetup</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Organizer: Kong/HO-CHI-MINH-CITY
+Attendees: </t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Tue, Jul 21 · 10:00 PM ICT</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/kong-ho-chi-minh-city/events/315576574/</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>&lt;Free Online Event&gt;International exchange (Only Japanese language)✨日本語だけで国際交流</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Meetup</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Organizer: Enjoy Japanese!  Vietnam　～日本語だけの国際交流会～
+Attendees: </t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Every Wed · Jul 8 · 7:00 PM ICT</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/online-enjoy-nihongo-vietnam-other-14-countries/events/315312113/</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Global - Dev Automation and Harness Engineering I</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Meetup</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Organizer: Advanced AI Concepts-Ho Chi Minh City
+Attendees: </t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Sun, Jul 12 · 9:00 PM ICT</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/advanced-ai-concepts-ho-chi-minh-city/events/315556791/</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Global - Anthropic Certified Architect Prep</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Meetup</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Organizer: Advanced AI Concepts-Ho Chi Minh City
+Attendees: </t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Sun, Jul 19 · 9:00 PM ICT</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/advanced-ai-concepts-ho-chi-minh-city/events/315538127/</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Anthropic Certified Architect Prep</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Meetup</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Organizer: Advanced AI Concepts-Ho Chi Minh City
+Attendees: </t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Sat, Jul 18 · 7:00 AM ICT</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/advanced-ai-concepts-ho-chi-minh-city/events/315536180/</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Get Leads Online with AI (Live Workshop Preview)</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Meetup</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Organizer: Internet Entrepreneurs Network (Vietnam)
+Attendees: </t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Thu, Jul 9 · 10:00 AM ICT</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/internet-entrepreneurs-network-vietnam/events/315497013/</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Saigon Sunday Free Online Guided Meditation- Beginners and Intermediate</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Meetup</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Organizer: Saigon Sahaja Yoga Meditation
+Attendees: 4 attendees</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Every Sun · Jul 12 · 8:45 AM ICT</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/saigon-meditation/events/315566317/</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Khoá Học Professional Scrum Master (PSM) - Lớp Online</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Meetup</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Organizer: Scrum Day Vietnam
+Attendees: </t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Sat, Jul 25 · 9:00 AM ICT</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/scrum-day-vietnam/events/315264764/</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Beginners Free Online Guided Meditation and Follow-Up</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Meetup</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Organizer: Saigon Sahaja Yoga Meditation
+Attendees: 5 attendees</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Every Sun · Jul 12 · 8:45 PM ICT</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/saigon-meditation/events/315368406/</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>AI Governance for AI Developers</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Meetup</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Organizer: Advanced AI Concepts-Ho Chi Minh City
+Attendees: </t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Sat, Jul 25 · 7:00 AM ICT</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/advanced-ai-concepts-ho-chi-minh-city/events/315538437/</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Global - AI Governance for AI Developers</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Meetup</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Organizer: Advanced AI Concepts-Ho Chi Minh City
+Attendees: </t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Sun, Jul 26 · 9:00 PM ICT</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/advanced-ai-concepts-ho-chi-minh-city/events/315538596/</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>African Roof Top Solar Makes Families Money #EDMA #bitcoin ...</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>African Roof Top Solar Makes Families Money #EDMA #bitcoin ...
+YouTube
+https://www.youtube.com › shorts</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>LIVE from Dubai: Why RWAs Are Dominating Token2049 + ...</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>LIVE from Dubai: Why RWAs Are Dominating Token2049 + ...
+YouTube · Action Crypto
+&gt;1,2 N lượt xem: · 1 năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Webinar with CEO of DigiU: RWA-Marketplace</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Webinar with CEO of DigiU: RWA-Marketplace
+YouTube · DIGIU
+&gt;16 N người theo dõi</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>RWA Day NYC</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>RWA Day NYC
+lu.ma
+https://lu.ma › rwa</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Tokenized RWA Bootcamp</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Tokenized RWA Bootcamp
+lu.ma
+https://lu.ma › Tokenized-RWA-bootc...</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Bridging the Trillion: Institutional RWA Tokenization Meets ...</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Bridging the Trillion: Institutional RWA Tokenization Meets ...
+Eventbrite
+https://www.eventbrite.com › bridgin...</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>RWA</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>RWA
+Vimeo
+https://vimeo.com › user212606547</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>RWA Live @ Korea Buidl Week</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>RWA Live @ Korea Buidl Week
+lu.ma
+https://lu.ma › ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>20/20 in Maths| RWA Live Mock 28 June 26 Complete ...</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>20/20 in Maths| RWA Live Mock 28 June 26 Complete ...
+YouTube · Learn with HiM
+&gt;1,2 N lượt xem: · 1 tuần trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>RWA Live Mock 05 July 2026 Maths Solution | Score 20/20 ...</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>RWA Live Mock 05 July 2026 Maths Solution | Score 20/20 ...
+YouTube · Learn with HiM
+&gt;250 lượt xem: · 1 ngày trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>RWA Live 5 Main Event The Agency vs The Abruzzis pt 1</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>RWA Live 5 Main Event The Agency vs The Abruzzis pt 1
+YouTube
+https://m.youtube.com › watch</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>RWA Live 5 Main Event The Agency vs The Abruzzis pt 3</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>RWA Live 5 Main Event The Agency vs The Abruzzis pt 3
+YouTube
+https://m.youtube.com › watch</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>SSC GD 2026 | RWA Live Mock 25 January 2026 maths ...</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>SSC GD 2026 | RWA Live Mock 25 January 2026 maths ...
+YouTube · math with praveen bajpai
+&gt;900 lượt xem: · 5 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>RWA Live 4 Main Event Cipriano Abruzzi vs T Phoenix pt 1</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>RWA Live 4 Main Event Cipriano Abruzzi vs T Phoenix pt 1
+YouTube · Renegade Wrestling Alliance
+&gt;140 lượt xem: · 15 năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>RWA Live ´03 Video VEGAS 4 FREE</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>RWA Live ´03 Video VEGAS 4 FREE
+YouTube · Rings of Europe - PRO Wrestling
+&gt;710 lượt xem: · 6 năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>RWA Livestream with Townsquare &amp; Monad</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>RWA Livestream with Townsquare &amp; Monad
+YouTube
+https://www.youtube.com › watch</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>$TX Talk 🎙️ Late Night tx Market and RWA Livestream</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>$TX Talk 🎙️ Late Night tx Market and RWA Livestream
+YouTube
+https://www.youtube.com › watch</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>AURUM NEO BANK and GOLD RWA (Webinar 16 April 2026)</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>AURUM NEO BANK and GOLD RWA (Webinar 16 April 2026)
+YouTube
+https://www.youtube.com › watch</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Biology Vs Chemistry ⚗️ | Life Vs Lab Showdown | RWA ...</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Biology Vs Chemistry ⚗️ | Life Vs Lab Showdown | RWA ...
+YouTube · UP Board English Medium RWA
+&gt;3,4 N lượt xem: · 11 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>naveen sir fan #naveen #rwa #livestream #rwaclasses #aakitsir ...</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>naveen sir fan #naveen #rwa #livestream #rwaclasses #aakitsir ...
+YouTube
+https://www.youtube.com › shorts</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Renegade Wrestling Alliance</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Renegade Wrestling Alliance
+YouTube · Renegade Wrestling Alliance
+&gt;2,8 N người theo dõi</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Free Career Empowerment &amp; Meditation Class</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Meetup</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Organizer: Free Career Empowerment &amp; Meditation Series
+Attendees: 2 attendees</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Every Wed · Jul 8 · 7:30 AM ICT</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/hanoi-career-empowerment-meditation-series/events/315509530/</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Bridging the Trillion: Institutional RWA Tokenization Meets ...</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Bridging the Trillion: Institutional RWA Tokenization Meets ...
+Eventbrite
+https://www.eventbrite.com › bridgin...</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>[Webinar] Growing Tezos Ecosystem with RWA Tokenization &amp; ...</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>[Webinar] Growing Tezos Ecosystem with RWA Tokenization &amp; ...
+YouTube
+https://m.youtube.com › watch</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Webinar: RWA Tokenization on Provenance, Polygon, Liquid ...</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Webinar: RWA Tokenization on Provenance, Polygon, Liquid ...
+YouTube · DigiShares
+&gt;380 lượt xem: · 1 năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>RWA Tokenization: Why 2026 Matters</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>RWA Tokenization: Why 2026 Matters
+YouTube · Brickken
+&gt;70 lượt xem: · 4 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>RWA Live @ Korea Buidl Week</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>RWA Live @ Korea Buidl Week
+lu.ma
+https://lu.ma › ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>20/20 in Maths| RWA Live Mock 28 June 26 Complete ...</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>20/20 in Maths| RWA Live Mock 28 June 26 Complete ...
+YouTube · Learn with HiM
+&gt;1,2 N lượt xem: · 1 tuần trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>RWA Live Mock 05 July 2026 Maths Solution | Score 20/20 ...</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>RWA Live Mock 05 July 2026 Maths Solution | Score 20/20 ...
+YouTube · Learn with HiM
+&gt;250 lượt xem: · 1 ngày trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>RWA Live 5 Main Event The Agency vs The Abruzzis pt 1</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>RWA Live 5 Main Event The Agency vs The Abruzzis pt 1
+YouTube
+https://m.youtube.com › watch</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>RWA Live 5 Main Event The Agency vs The Abruzzis pt 3</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>RWA Live 5 Main Event The Agency vs The Abruzzis pt 3
+YouTube
+https://m.youtube.com › watch</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>SSC GD 2026 | RWA Live Mock 25 January 2026 maths ...</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>SSC GD 2026 | RWA Live Mock 25 January 2026 maths ...
+YouTube · math with praveen bajpai
+&gt;900 lượt xem: · 5 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>RWA Live 4 Main Event Cipriano Abruzzi vs T Phoenix pt 1</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>RWA Live 4 Main Event Cipriano Abruzzi vs T Phoenix pt 1
+YouTube · Renegade Wrestling Alliance
+&gt;140 lượt xem: · 15 năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>RWA Live ´03 Video VEGAS 4 FREE</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>RWA Live ´03 Video VEGAS 4 FREE
+YouTube · Rings of Europe - PRO Wrestling
+&gt;710 lượt xem: · 6 năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>RWA Livestream with Townsquare &amp; Monad</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>RWA Livestream with Townsquare &amp; Monad
+YouTube
+https://www.youtube.com › watch</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>$TX Talk 🎙️ Late Night tx Market and RWA Livestream</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>$TX Talk 🎙️ Late Night tx Market and RWA Livestream
+YouTube
+https://www.youtube.com › watch</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Tokenization in the U.S. Webinar | Expert Panel Discussion</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Tokenization in the U.S. Webinar | Expert Panel Discussion
+YouTube · DigiShares
+&gt;510 lượt xem: · 6 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Tokenizing commodities &amp; RWAs presented by zenGate Global</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Tokenizing commodities &amp; RWAs presented by zenGate Global
+YouTube · Cardano Foundation
+&gt;960 lượt xem: · 2 năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Biology Vs Chemistry ⚗️ | Life Vs Lab Showdown | RWA ...</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Biology Vs Chemistry ⚗️ | Life Vs Lab Showdown | RWA ...
+YouTube · UP Board English Medium RWA
+&gt;3,4 N lượt xem: · 11 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>naveen sir fan #naveen #rwa #livestream #rwaclasses #aakitsir ...</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>naveen sir fan #naveen #rwa #livestream #rwaclasses #aakitsir ...
+YouTube
+https://www.youtube.com › shorts</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Webinars</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Webinars
+YouTube · DigiShares
+&gt;2,1 N người theo dõi</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Renegade Wrestling Alliance</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Renegade Wrestling Alliance
+YouTube · Renegade Wrestling Alliance
+&gt;2,8 N người theo dõi</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" t="inlineStr"/>
+      <c r="F235" t="inlineStr"/>
+      <c r="G235" t="inlineStr"/>
+      <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr"/>
+      <c r="J235" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/livestreams.xlsx
+++ b/data/livestreams.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Livestreams" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Livestreams" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J235"/>
+  <dimension ref="A1:J236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5947,13 +5947,30 @@
 &gt;2,8 N người theo dõi</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
-      <c r="E235" t="inlineStr"/>
-      <c r="F235" t="inlineStr"/>
-      <c r="G235" t="inlineStr"/>
-      <c r="H235" t="inlineStr"/>
-      <c r="I235" t="inlineStr"/>
-      <c r="J235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Test Event</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr"/>
+      <c r="D236" t="inlineStr"/>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=unique123</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr"/>
+      <c r="G236" t="inlineStr"/>
+      <c r="H236" t="inlineStr"/>
+      <c r="I236" t="inlineStr"/>
+      <c r="J236" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/livestreams.xlsx
+++ b/data/livestreams.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O29"/>
+  <dimension ref="A1:O57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1788,12 +1788,1387 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>[webinar] Online Event Fundraiser: Lessons to Share</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>48</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Fundarise Livestream</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>For organizations with limited online presence, what strategies have you found most effective in leveraging social media to promote online events and drive ticket sales?</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>[webinar] Online Event Fundraiser: Lessons to Share
+Vimeo
+https://vimeo.com › ... › Videos</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Best 1 RWA tokenization platforms - S-PRO</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>55</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Tokenization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người?</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Best 1 RWA tokenization platforms - S-PROS-PROhttps://s-pro.io › rwa-tokenization-platforms</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Tokenization Protocols - Meegle</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>55</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Tokenization</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Have you considered the implications of tokenization on data governance, particularly in regulated industries like finance where data residency and sovereignty are major concerns?</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Tokenization Protocols - MeegleMeeglehttps://www.meegle.com › en_us › topics › tokenization-...</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>[Webinar] Hit your fundraising goals without hosting another ...</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>71</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Organization Manager</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Charity</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người?</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>[Webinar] Hit your fundraising goals without hosting another ...
+YouTube · Givebutter
+&gt;330 lượt xem: · 3 tháng trước</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Fund Tokenization: Building Bridges in Global Fund Distribution</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>55</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Tokenization</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>How do you see tokenization addressing the issue of fragmented fund ownership structures, which can lead to inefficient distribution and high costs for investors?</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Fund Tokenization: Building Bridges in Global Fund Distribution
+Nicsa
+https://nicsa.org › product › fund-tok...</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>🔴 LIVE | Fundraiser for Jantar Mantar Students | Every Donation Makes a Difference ❤️</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>165</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Gamers and philanthropists</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>How will the funds raised from this BGMI charity stream be allocated to support the students at Jantar Mantar, are there any specific programs or initiatives that will be prioritized? | I'd love to know more about the current challenges faced by the students at Jantar Mantar and how this charity stream aims to address them, are there any specific stories or examples you can share? | Will there be any opportunities for donors to get involved beyond just contributing financially, such as volunteering or mentoring the students at Jantar Mantar?</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>LIVE BGMI Charity Stream | Supporting Students at Jantar Mantar ❤️     Welcome to today's **BGMI LIVE Charity Stream!</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2026-07-21T15:33:34Z</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=djx068LuF4Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>LIVE Fundraiser Minecraft and Heal behind the scenes in real life of a nonprofit</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>145</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Philanthropist/Gamer</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Nonprofit</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>I'm curious to know how the Eudaimonia Project Film Festival plans to allocate the donated funds, will they be used for specific programs or general operational costs? | How does the nonprofit plan to measure the impact of the fundraiser, are there any specific metrics or outcomes they're hoping to achieve with the donations? | Are there any plans to collaborate with other nonprofits or organizations in the charity sector to amplify the effects of the fundraiser and the film festival?</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Please Donte https://live.givebutter.com/c/the-eudaimonia-project-film-festival-b2vu4h.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2026-07-21T13:33:44Z</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=OTqbl8UnInE</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>🔴 LIVE CHARITY STREAM | Save Little Krishna ❤️ Every Donation Can Save a Life 🙏</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>145</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Empathetic Donor</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Non-Profit/Healthcare</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>What's the current status of Little Krishna's treatment and how will the donations from this stream be allocated to support his medical expenses? | Are there any plans for long-term support or follow-up care for Little Krishna after the initial treatment, and how can we as a community continue to help? | Can you share more about the specific medical condition Little Krishna is facing and what the prognosis is with timely and proper treatment, so we can better understand the urgency of the situation?</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Please Help Save Little Krishna Little Krishna is fighting a serious medical condition and urgently needs support for treatment.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2026-07-21T15:35:00Z</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=I0yjeB8Tqf4</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>the andrew nocturnna and wEndy charity stream</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>110</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>supporter/donor</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>gaming/charity</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Just donated to the GoFundMe campaign, hoping Andrew gets the support he needs - what's the current status on his housing situation? | How will the funds raised from this stream be allocated to support Andrew's rehabilitation and education? | Are there any plans for long-term support or mentorship programs for Andrew and others who've experienced similar situations, perhaps through partnerships with local charities?</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>the gofundme fundraiser: https://www.gofundme.com/f/andrew-hospitalized-by-abusive-parents-now-homeless.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2026-01-13T05:40:03Z</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=tETQ11QlHGo</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>pls donate</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>83</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Charity</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>What's the primary cause that this charity is supporting, and how will the donated funds be allocated? | Are there any specific donation milestones or targets that we can help reach during this livestream? | Will there be any matching donations or sponsorships to amplify the impact of our contributions?</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2026-07-21T13:00:19Z</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=P3-fKqN2b8A</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Wolf&amp;#39;s Den Takeover Tuesday of the AGB Charity channel on kick!! !AGB !face !AGB !face</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>80</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Gamers, particularly those interested in charity events and community engagement</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Love the gaming for a cause concept, how does the AGB Charity channel plan to allocate donations from tonight's stream? | MnK, what's your strategy for tackling tough levels in the games you're playing, and will you be taking donations for specific charity milestones? | Will the stream be featuring any charity-specific games or challenges, like a 'donate to skip' level or a 'charity boss fight'?</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>MnK old Fart playing some Games.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2026-07-21T13:52:24Z</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=uMuJEqYyFr0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>deep focus lofi radio 🎯 24/7 charity beats for deep work (live now)</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>80</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Students, programmers, and individuals seeking focus or relaxation</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Music/Entertainment</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>I've noticed the lofi beats have a calming effect, do you think the same tracks could be used in therapy sessions for anxiety relief in homeless shelters? | How does the donation process work - is it a fixed amount per listener or based on the total hours streamed? | Are there any plans to collaborate with mental health professionals to create customized lofi playlists for specific conditions, like PTSD, which is common among the homeless population?</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>24/7 Lofi beats for deep focus, sleep, and anxiety relief. Every minute you listen helps provide real support for the homeless.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2026-07-21T10:00:07Z</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=5vgTpAWTqy4</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>🔴CHARITY🔴DONATE = CHANGE THE GAME🔴GEOMETRY DASH TRIATHLON</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>80</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Gamers, charity supporters</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>How does the donation tier system work in terms of unlocking exclusive rewards in the Geometry Dash triathlon? | I'm curious to know if there are any specific charity initiatives or causes that the Globed Room 360648 is supporting through this event? | Are there any plans to offer additional challenges or bonus levels for donors who contribute above a certain amount, similar to the ones mentioned in the Challenge Info section?</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Donate here: https://charity.gd/gdce/ Globed Room: 360648 Challenge Info   Depending on the amount donated, you can buy ...</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2026-07-21T13:00:00Z</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=woFm1lBy8cE</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>God says&amp;quot; Today Marks the End of That Affliction | Evang Charity Odochi is live!</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>80</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Individuals seeking spiritual guidance or solace</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Religion/Spirituality</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Evang Charity, what role do you believe faith-based organizations can play in addressing systemic afflictions, such as poverty and inequality, in our communities? | Can you share an example of a successful charity initiative that you've been involved with, and how it's helped alleviate affliction for a specific group of people? | How do you think we can balance spiritual guidance with tangible support in charity work, to ensure we're making a lasting impact on those we're trying to help?</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>God says" Today Marks the End of That Affliction | Evang Charity Odochi is live!</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2026-07-21T13:35:36Z</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=wVHnJwaSpWI</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Ready For Battle⚔️🛡️ || Kidz Family Camp 2026 || Pastor Charity Kalstrup</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>80</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Christian families with children</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Religion</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Pastor Charity, how do you think the Kidz Family Camp 2026 can be used as a platform to raise awareness and funds for local charities, particularly those supporting underprivileged kids? | I'm curious to know more about the chooselife Kidz Ministry's outreach programs - are there any plans to collaborate with other organizations to amplify the impact of the Kidz Family Camp? | What role do you envision the church community playing in supporting the Kidz Family Camp, and are there opportunities for volunteers to get involved in the planning and execution process?</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>This message was recorded live at chooselife CHURCH in Hobbs, NM. For more information about Chooselife Kidz Ministry visit ...</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2026-07-21T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=pQS1z_hYIco</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Charity Cup Mini S-10</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>80</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Gamers, Esports enthusiasts</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>How does the Charity Cup Mini S-10 format impact donor engagement, particularly in terms of repeat participation? | What's the strategy behind using #PRISMLiveStudio for this event, and how does it enhance the overall charity experience? | Are there any plans to offer virtual participation options for the Charity Cup Mini S-10, to expand the reach and inclusivity of the event?</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>This stream is created with #PRISMLiveStudio.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2026-07-21T16:18:41Z</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=Mod7A6OTwZw</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Breaking News LIVE | Current Affairs News | CJP Protest | Headlines | Ram Mandir Donation</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>75</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Individuals interested in current events and news, particularly those from India or with an interest in Indian affairs</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>News/Media</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Curious to know how the Ram Mandir donation drive is impacting local communities, are there any plans to allocate funds to support social causes? | Can you provide an update on the CJP protest and its potential implications on the current political landscape, particularly in regards to charitable organizations? | How do you think the recent developments in the Ram Mandir donation campaign will influence philanthropic efforts in India, especially for charities focused on education and healthcare?</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Aaj Tak Breaking News LIVE | Current Affairs News | CJP Protest | Headlines | Ram Mandir Donation Aaj Tak LIVE – International ...</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2026-07-21T12:30:00Z</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=7rhl6BGcLUA</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>WE HAVE YOUR 6 JULY FUNDRAISING FOR REGIMENT is in full swing!!</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>65</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>gamers</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>gaming</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>How does the Spearhead update impact the gameplay experience for Regiment players, and will the fundraising campaign offer exclusive in-game content? | What's the current progress on the WE HAVE YOUR 6 JULY FUNDRAISING campaign, and are there any specific charity initiatives that RegimentGG is supporting this month? | Will the Gray Zone Warfare 0.4 update include any new features that allow players to create custom charity events or tournaments within the game, similar to what we've seen in other gaming communities?</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>LIVE NOW – Gray Zone Warfare 0.4 “SPEARHEAD” UPDATE!! ​ ⁨@madfingergames⁩ ⁨@RegimentGG⁩ The battlefield just ...</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2026-07-21T00:06:27Z</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=d1TEM_LuSbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Skyview - West of Frontier Ag Inc - Goodland, KS</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>30</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Farmers, Agricultural Professionals, or Local Community Members</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>I'm curious to know if Frontier Ag Inc has considered partnering with local charities to use this skyview service for environmental monitoring or disaster response efforts? | How does the community service aspect of this skyview project align with Frontier Ag Inc's overall corporate social responsibility goals, particularly in terms of supporting local Kansas initiatives? | Are there any plans to use the footage from this skyview service to support educational programs or workshops, potentially in partnership with local non-profits or charities focused on agriculture or conservation?</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>View of the skies west of Frontier Ag Inc in Goodland Kansas. A community service from Frontier Ag Inc. https://frontieraginc.com/</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2025-12-17T05:45:00Z</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=XjuKPeQx2V0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Skyview - East of Frontier Ag Inc - Goodland, KS</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>30</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Farmers, Agricultural Professionals, or Local Community Members</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>I'm curious to know if Frontier Ag Inc has considered partnering with local charities to utilize this skyview for environmental monitoring or conservation efforts? | How does the community service aspect of this skyview project align with Frontier Ag Inc's overall corporate social responsibility initiatives? | Are there any plans to use this skyview to support disaster relief or emergency response efforts in the Goodland, KS area, potentially in collaboration with local non-profits?</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>View of the skies east of Frontier Ag Inc in Goodland Kansas. A community service from Frontier Ag Inc. https://frontieraginc.com/</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2025-12-17T05:50:00Z</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=PrqfpZq4ERI</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Skyview - South of Frontier Ag Inc - Goodland, KS</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>30</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Farmers, Agricultural professionals, or individuals interested in weather conditions</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>I'm curious to know if the community service initiative by Frontier Ag Inc has led to any notable improvements in local air quality monitoring, given the proximity to agricultural areas? | Has Frontier Ag Inc considered partnering with local charities or environmental groups to further amplify the impact of their community service efforts in Goodland, KS? | Are there any plans to expand the skyview monitoring to other locations within Kansas, potentially in collaboration with regional conservation organizations?</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>View of the skies south of Frontier Ag Inc in Goodland Kansas. A community service from Frontier Ag Inc. https://frontieraginc.com/</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2025-12-17T05:50:00Z</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=xU7UDBXiAwA</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Skyview - North of Frontier Ag Inc - Goodland, KS</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>30</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Farmers, Agricultural enthusiasts</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>I'm curious to know if Frontier Ag Inc has considered partnering with local charities to use this skyview service for environmental monitoring or conservation efforts? | How does the community service aspect of this skyview project align with Frontier Ag Inc's overall corporate social responsibility goals, particularly in the Goodland Kansas area? | Are there any plans to use the footage from this skyview service to support educational initiatives or fundraising campaigns for local charities, such as those focused on agriculture or rural development?</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>View of the skies north of Frontier Ag Inc in Goodland Kansas. A community service from Frontier Ag Inc. https://frontieraginc.com/</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2025-12-17T05:50:00Z</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=70YcImm96ws</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Skyview - South of Frontier Ag Inc - Quinter, KS</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>30</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Farmers, Agricultural Professionals, or Local Community Members</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>I'm curious to know if the community service initiative by Frontier Ag Inc has led to any notable improvements in local weather monitoring or emergency response systems in Quinter, KS? | How does the view from Skyview contribute to the overall mission of Frontier Ag Inc, and are there plans to expand this community service to other locations? | Are there any partnerships or collaborations with local charities or organizations that Frontier Ag Inc is involved with, and how can viewers support these efforts?</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>View of the skies south of Frontier Ag Inc in Quinter Kansas. A community service from Frontier Ag Inc. https://frontieraginc.com/</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2026-03-13T19:45:00Z</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=NIGhF4jUja0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Skyview - West of Frontier Ag Inc - Quinter, KS</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>30</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Farmers, Agricultural Professionals, or Local Community Members</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>I'm curious to know if Frontier Ag Inc has considered partnering with local charities to use this skyview service for environmental monitoring or conservation efforts? | How does the community service aspect of this skyview initiative align with Frontier Ag Inc's overall corporate social responsibility goals, particularly in terms of supporting local Kansas communities? | Are there any plans to use the data collected from this skyview service to support precision agriculture practices or inform decision-making for sustainable farming methods in the Quinter area?</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>View of the skies west of Frontier Ag Inc in Quinter Kansas. A community service from Frontier Ag Inc. https://frontieraginc.com/</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2026-03-13T19:45:00Z</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=VbHOKakFTqo</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Skyview - North of Frontier Ag Inc - Quinter, KS</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>30</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Local farmer or agriculture enthusiast</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>I'm curious to know if the community service aspect of this project includes any educational programs for local kids about agriculture and sustainability, perhaps in partnership with a charity? | How does Frontier Ag Inc plan to utilize this skyview service to support local farmers and ranchers, and are there any plans to expand this initiative to other locations? | Are there any opportunities for viewers to get involved and support the community service efforts of Frontier Ag Inc, such as volunteering or donating to a related charity?</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>View of the skies north of Frontier Ag Inc in Quinter Kansas. A community service from Frontier Ag Inc. https://frontieraginc.com/</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2026-03-13T20:40:00Z</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=Sf7OzR_oVqs</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>How Philanthropy Can Feed Business</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>89</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Entrepreneurs, Business Owners, Philanthropists</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Non-Profit, Business</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Wafa, can you share an example of a company that's successfully integrated philanthropy into their business model, and how it's impacted their bottom line? | I'm curious to know more about the role of CSR in driving business growth - are there any specific industries where philanthropy has been a key differentiator? | How do you think businesses can balance the desire to 'do good' with the need to measure ROI on their philanthropic efforts, and what metrics should they be tracking?</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>What happens when philanthropy does more than fund programs—and starts helping businesses grow? Wafa Dinaro, Executive ...</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2026-07-21T16:27:04Z</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=JtGPVv218_s</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>🔴LIVE: Trading Bot Scalping✅Giving Code Away For FREE✅</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>75</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Individual traders or investors interested in day trading and automated trading bots</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Finance/Trading</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Curious to know how you handle slippage when scaling up your trading bot, especially during high-volatility moments in the S&amp;P 500 futures | What's your strategy for avoiding overfitting in the bot's code, and are you using any specific backtesting methods to validate its performance? | Have you considered donating a portion of your profits to charity once you reach your $100000 goal, potentially using your platform to raise awareness for a cause?</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>I live day trade S&amp;P 500 futures with the goal of reaching $100000 in profit. Sharing my journey in real-time with full transparency ...</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2026-07-21T16:16:16Z</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=LwTFHMRd5Jc</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Giving backshots for the greater good</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>75</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Young adults or teenagers interested in gaming or streaming content</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Gaming or Entertainment</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>How do you think 'backshots for the greater good' can be applied in a charity setting, particularly for fundraising events? | I'm curious to know if there are any specific strategies for maximizing the impact of backshots in charity work, such as partnering with influencers? | Can you share an example of a successful charity campaign that utilized backshots to raise awareness and drive donations?</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>You Should Subscribe for more.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2026-07-21T16:21:59Z</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=sEYC6fl6UfA</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/livestreams.xlsx
+++ b/data/livestreams.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O57"/>
+  <dimension ref="A1:O58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3164,11 +3164,53 @@
           <t>https://youtube.com/watch?v=sEYC6fl6UfA</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>SEO Charity Summer Edition 2026</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>90</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Marketing professionals, SEO specialists, and charity supporters</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Digital Marketing/Technology</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>How do you think the latest Google algorithm updates will impact charity website rankings, particularly for smaller non-profits with limited SEO resources? | What role do you see technical SEO playing in the charity sector, especially in terms of optimizing donation pages for better conversion rates? | Can you discuss any successful case studies of charities using long-tail keywords to reach specific donor demographics and increase online fundraising efforts?</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=aQZfRuMNc3k</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/livestreams.xlsx
+++ b/data/livestreams.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O58"/>
+  <dimension ref="A1:O59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3199,18 +3199,58 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>https://youtube.com/watch?v=aQZfRuMNc3k</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Youth Family Camp Morning 2 - Pastor Charity Kalstrup</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>8</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Family-oriented individuals, particularly those with a Christian background</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Religion</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Pastor Charity, how do you incorporate faith-based discussions into the family camp activities to promote spiritual growth among the youth? | I'm curious to know more about the community outreach programs you've implemented through the family camp, are there any plans to expand these initiatives to other locations? | What role do you think mentorship plays in the family camp setting, and how do you match youth with suitable mentors or role models?</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=Q_rsW8Dj5MI</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/livestreams.xlsx
+++ b/data/livestreams.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O59"/>
+  <dimension ref="A1:O78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3239,18 +3239,778 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>https://youtube.com/watch?v=Q_rsW8Dj5MI</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Techno &amp; Bass Music 24/7 🔴 Live Radio | Hard Techno, Bass House, Rave Music</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>150</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Electronic Dance Music (EDM) enthusiast</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Loving the energy of this Hard Techno set, what's the story behind the transition from Bass House to Rave Music in your live radio shows? | How do you balance the darker tones of Hard Techno with the more upbeat vibes of Bass House to keep the 24/7 live radio engaging? | Are there any plans to feature emerging artists in the Rave Music scene or collaborations with other DJs to mix things up in future live radio broadcasts?</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=xN0EMHEI2XQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>WE LOVE RAVE 🟢 24/7 Psytrance Community Radio | Festival Vibes, Trippy Art, High Energy Flow</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>98</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Raver</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Loving the high energy flow so far, how do you curate your 24/7 playlist to keep the psytrance vibes consistent? | What's the story behind the trippy art visuals - are they created in-house or do you collab with external artists? | Are there any plans to feature live DJ sets or interviews with prominent psytrance artists in the RAVE community?</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=uMvUKvmczpU</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>German TECHNO BUNKER 24/7 Deep Dark &amp; Hard Techno Underground Live Stream Rave</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>97</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Electronic Dance Music (EDM) enthusiast</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Loving the dark techno vibes, what's the story behind the curated tracklist for this 24/7 stream? | How do you balance the energy between deep and hard techno to keep the rave going non-stop? | Are there any plans to feature underground techno artists from Berlin in upcoming streams?</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=hSVSWFF1M6Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>NON STOP TECHNO RAVE RADIO 24/7 MIX</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>96</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Electronic Dance Music (EDM) enthusiast</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Loving the energy of this 24/7 mix, what's the secret to keeping the vibe consistent across different tracks and DJs? | Can we get a shoutout to the classic techno rave tracks that never get old, like those from Jeff Mills or Richie Hawtin? | How do you balance the mix between newer, experimental techno and the old-school rave anthems that get the crowd moving?</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=34H1XIjnfKM</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>TECHNO RADIO 💣 NON STOP RAVE</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>96</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Raver</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Loving the energy so far, what's the story behind the transition from techno to rave in the setlist? | How do you balance the tempo and beat to keep the non-stop rave vibe going without overwhelming the listeners? | Can you share some insights on how you curate your tracks to create that perfect rave atmosphere, like the one you're building up to now?</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=hXsca_iyieI</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>24/7 🎛 Techno Club Radio · Rave, Warehouse &amp; Hypnotic (Corgi Records)</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>95</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Electronic Dance Music (EDM) enthusiast</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Loving the hypnotic vibes so far, how do you balance the energy between warehouse and rave tracks in your sets? | What's the story behind featuring Corgi Records in this livestream, are they a new favorite label of yours? | The transitions between tracks have been seamless, can you walk us through your process for creating a cohesive flow in a 24/7 techno club radio setting?</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=RtLSe0syHVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>HARD RAVE TECHNO RADIO NON STOP 24/7 LIVE</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>95</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Raver</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Loving the energy of this set, what's the story behind the transition from hardcore to rave in the 90s that influenced your track selection? | Can you dive deeper into the production techniques used to create that iconic 'hoover' sound in classic rave tracks? | How do you balance the nostalgic vibe of old-school rave with modern production quality and techniques in your mixes?</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=AswR2woOGj0</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>🔴 LIVE 24/7 Goa Psytrance Radio 2026 | Ravecore Nation | Psychedelic Trance Stream</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>95</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Raver</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Loving the vibe of this stream, what's the story behind the Ravecore Nation name and how did you curate this epic playlist? | How do you balance the energy between classic psytrance tracks and newer releases in your 24/7 stream to keep the Ravecore Nation engaged? | Are there any plans to feature live DJ sets or collaborations with other psytrance artists in the stream, that would take the Rave to the next level?</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=_py4DTR8Gn4</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>🔴 LIVE 24/7 Hardcore Uptempo Gabber Radio 2026 | RaveCore Nation | Hard Techno Stream</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>95</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Raver</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Loving the energy on this stream, what's the story behind the RaveCore Nation name and how did it become synonymous with the hardcore uptempo scene? | Can we get a shoutout to the pioneers of gabber like Rotterdam Terror Corps and Miss K8, their influence on the genre is still felt today | How do you curate the tracklist for a 24/7 stream like this, do you take requests from the chat or is it all pre-programmed?</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=XeLnMn_WHmo</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>🔴 LIVE 24/7 Goa Psytrance #2 Radio 2026 | Ravecore Nation | Psychedelic Trance Stream</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>95</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Raver</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Loving the vibe on this stream, what's the story behind the Ravecore Nation name and how did it become a hub for psytrance fans? | Curious to know if you'll be featuring any artists from the old school Goa trance scene, like Hallucinogen or Ott, in upcoming sets? | How do you balance the energy between darker, more industrial psytrance tracks and the more uplifting, melodic ones to keep the stream engaging 24/7?</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=RW2BiYKDcDY</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Music Mix 2026 🔊 Party Club Dance 2026 🔥 Festival Party Energy MEGAMIX Nonstop</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>95</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>party-goer</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>entertainment</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Loving the energy of this MEGAMIX, how do you balance the transition between EDM and hip-hop tracks to keep the party vibe going? | What's the inspiration behind including nonstop festival party energy in this mix, are you drawing from specific festivals like Tomorrowland or Ultra? | The drop at 10 minutes in is insane, can you share your process for selecting and mixing those high-energy drops to get the crowd moving?</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=bIYQRlWlFNE</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Art of Minimal Techno 'Deep' Radio | Melodic Techno &amp; Progressive House 24/7 Live by Trippy Code</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>90</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Electronic Dance Music (EDM) enthusiast</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Loving the melodic techno vibes, Trippy Code - what's the story behind your track selection process for this 24/7 live set? | How do you balance the energy between melodic techno and progressive house to keep the flow going for a 24-hour stream? | Are you using any specific audio processing techniques to create that deep, immersive sound in your mixes, or is it all about the track choices?</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=UYOb37KRFqk</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>MINIMAL TECHNO PARTY RADIO by TRIPPY CAT MUSIC</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>90</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Electronic Dance Music Fans</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Trippy Cat, what inspired the tracklist for this Minimal Techno party, any new artists we should be looking out for? | Loving the vibe so far, how do you balance the energy between deeper cuts and more upbeat tracks in a set like this? | Curious about the production side, are you using any specific plugins or effects to achieve that signature Trippy Cat sound in your Minimal Techno sets?</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=TI2drL9AH5s</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Dark Minimal Techno NON STOP Radio Mix</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>90</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Electronic Dance Music (EDM) enthusiast</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Loving the transition into this Chris Liebing track, how do you curate your sets to maintain energy throughout a non-stop mix? | The use of industrial samples in these dark minimal techno tracks is really adding to the atmosphere, are there any specific artists or labels that inspire your selection? | I've noticed a lot of repetition in the kick drum patterns, do you find that this helps to hypnotize the listener or is it more about creating a sense of tension and release?</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=-vH9ZvAySi8</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Tomorrowland 2026 - David Guetta &amp; Alesso | EPIC Mainstage Live Set 🔥 | The ULTIMATE Festival Mix</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>95</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Electronic Dance Music (EDM) fans</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Loving the energy so far, how do you think David Guetta's recent collaboration with Bebe Rexha will influence his setlist tonight? | Alesso's progressive house style is gonna pair perfectly with the mainstage production, do you think we'll see any surprises like a Swedish House Mafia reunion? | The ULTIMATE Festival Mix always brings the heat, curious to see if they'll drop any of their unreleased IDs like Guetta's rumored track with Morten</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=lbyuS8XdD0g</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Dark Minimal Techno Trip Live Radio 24/7 mixed by RTTWLR</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>90</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Electronic Dance Music (EDM) enthusiast</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Loving the transition into this set, RTTWLR - what's the story behind the track selection for this particular mix? | Noticed a nice blend of old-school and modern dark minimal techno vibes, are there any upcoming artists or labels that you're excited to feature in future sets? | The way you're weaving in those haunting synths is giving me major rave flashbacks - can you share any favorite rave memories or what inspires your mixing style?</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=FOsRAs__6PM</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Minimal Techno Radio Non Stop 24/7</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>90</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Electronic Music Fan</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Loving the vibe, what's the secret to keeping a 24/7 radio stream engaging, do you have a set rotation or is it all live mixes? | How do you balance the energy between minimal techno tracks to keep the flow going, any favorite artists or labels that always bring the heat? | Curious about the tech side, what software or platform are you using to stream non-stop, is it a custom setup or something like Icecast or SHOUTcast?</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=oOcUoXipLDg</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>RELIVE Mainstage - Tomorrowland 2026 LIVE</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>95</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Electronic Dance Music (EDM) fans</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Loving the stage design this year, how do the production team decide on the theme and layout for each Mainstage performance? | What's the story behind the new LED wall setup, is it an upgrade from last year's model? | Curious to know if the live streaming tech has improved for better audio sync, noticed some delays in previous years</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=CVHFv2VOIBc</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>RELIVE Freedom Stage - Tomorrowland 2026 LIVE</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>95</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Electronic Dance Music (EDM) enthusiast</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Loving the stage design this year, how does the production team decide on the theme and aesthetic for Freedom Stage? | What's the story behind the LED mapping on the stage, is it all pre-programmed or are there any live elements controlled by the VJs? | Curious to know more about the audio setup, are they using a similar L-Acoustics system as previous years or have they upgraded to something new?</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=SaWV3uDOf8Q</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/livestreams.xlsx
+++ b/data/livestreams.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O78"/>
+  <dimension ref="A1:O88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3999,18 +3999,418 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>https://youtube.com/watch?v=SaWV3uDOf8Q</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Answering YOUR questions about the charity - Charity Checkup nr 1160</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>95</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Donor/Supporter</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Non-profit</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>What's the current process for addressing donor concerns about transparency in charity operations, and how does Charity Checkup ensure accountability? | Can you discuss any recent updates to the charity's grant-making strategy, particularly in regards to supporting local community projects? | How does Charity Checkup handle situations where a charity's goals align with the organization's mission, but their methods or outcomes are questionable?</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=LR93_N7IDT8</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Game Safe Charity Stream!</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>90</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Gamers and philanthropists</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>How will the funds raised from this stream be allocated to support gaming-related charities, and are there any specific initiatives you're looking to back? | I'd love to know more about the charity partners you're working with - are they focused on accessibility in gaming, or perhaps mental health support for gamers? | Will there be any opportunities for viewers to get involved in the charity efforts beyond donations, such as volunteer sign-ups or community drives?</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=-QwUSVTmBTc</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>ANNA 92 NEW STUDENT CHARITY MEMBER</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>90</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Philanthropist</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Non-Profit</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>What kind of community outreach programs will ANNA 92 be implementing as part of their new student charity membership? | How will the charity membership impact the student experience, specifically in terms of volunteer opportunities or fundraising events? | Are there plans to collaborate with existing charities or will ANNA 92 be establishing their own charitable initiatives?</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=JwpqPLPg_Hs</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Will Jordan be able to make it to the charity game?</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>80</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Philanthropist</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Entertainment</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Does Jordan's potential absence from the charity game impact the fundraising strategy, or are there backup plans in place? | How will the charity game's organizers ensure a smooth event if Jordan can't make it, considering his role in promoting the event? | Are there any contingency plans for replacing Jordan or adjusting the game format to still meet the charity's fundraising goals?</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=yDNPh-TA52k</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Will Jordan be able to make it to the charity game?</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>80</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Philanthropist</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Entertainment</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Do we know what Jordan's current injury status is and if it'll impact his participation in the charity game? | How will Jordan's potential absence affect the team's strategy and fundraising goals for the charity event? | Are there any backup plans or alternative players lined up in case Jordan can't make it to the charity game?</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=NDSZWiU6K8U</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Return to the Danger Room: A Broken Level 20 Charity Brawl</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>90</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Gamers and charity supporters</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>How do you plan to address the issue of team composition imbalance in the Level 20 Charity Brawl, considering the diverse range of characters and playstyles? | What strategies will you employ to counter the 'stall and hide' tactic that often emerges in high-stakes charity brawls, and how can viewers support the charity through donations or sharing the stream? | Will the charity brawl feature any special 'power play' rules or incentives to encourage risk-taking and aggressive gameplay, and if so, how will these be announced during the stream?</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=9_hqkUiPDmg</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>TV WEST LIVE: SISIIMUKA 23.07.2026 NA SISTER CHARITY | LUCKY KASANGAKI</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>90</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Philanthropist</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Non-Profit</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Lucky Kasangaki, can you share some insights on how Sister Charity's initiatives have impacted local communities, particularly in terms of education and healthcare? | I'd love to know more about the Sisiimuka event's objectives - are there any specific fundraising goals or awareness campaigns that Sister Charity is focusing on this year? | How does Sister Charity plan to leverage the Sisiimuka event to build partnerships with other organizations or stakeholders, potentially amplifying their charitable efforts?</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=7QyZOunC2Ck</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>🟢BEATING 430 LEVELS IN ONE STREAM.🟢 // GD Charity Event 2026 //</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>90</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Gamers and charity supporters</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>What's the strategy behind tackling the infamous level 321, and how do you plan to overcome its notorious difficulty spike? | Curious to know, are there any specific charity initiatives or organizations that will be benefiting from this GD Charity Event, and how can viewers contribute? | How do you handle mental fatigue during long streams like this, especially when encountering tough levels like 275-300, and what keeps you motivated to push through?</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=jz0F7BjrTR0</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Super Zeldathon - 7 Days of Zelda in Support of St. Jude - donate.zeldathon.com</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>90</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Gamers and fans of the Zelda series</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>How's the team planning to handle the Water Temple in Ocarina of Time, considering it's one of the most challenging parts of the game? | I've donated to St. Jude through donate.zeldathon.com - what's the current donation tally and are there any stretch goals for the remaining days? | Will you be doing any specific challenges or incentives during the Majora's Mask segment, like a 'mask collection' goal to encourage more donations?</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=lG_bumnfgaw</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>CAC Fundraising Livestream</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>90</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Philanthropist</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Non-Profit</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>What strategies have been most effective in reducing donor acquisition costs for CAC fundraising campaigns, particularly for smaller charities? | Can you discuss the role of social media in CAC fundraising, specifically how to leverage platforms like YouTube to increase donations and engagement? | How do you recommend charities balance the need for immediate funding with long-term donor relationship building in their CAC fundraising efforts?</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>CAC Fundraising Livestream  YouTube https://www.youtube.com › watch</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/livestreams.xlsx
+++ b/data/livestreams.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O88"/>
+  <dimension ref="A1:O93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4404,13 +4404,213 @@
           <t>CAC Fundraising Livestream  YouTube https://www.youtube.com › watch</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>SARAH 48 STUDENT CHARITY MEMBER</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>90</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Philanthropist</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Non-Profit</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>What inspired you to join the SARAH 48 student charity, and how do you think your experience will impact your future endeavors? | Can you share any specific challenges you've faced as a charity member, and how you overcame them? | How do you think the skills you're developing through SARAH 48 will translate to a career in nonprofit or philanthropy?</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=XITaRPcQuKI</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>JEVZ 26 CHARITY MEMBER</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>90</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Philanthropist</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Non-Profit</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>How does JEVZ 26 plan to utilize member contributions to support specific charity initiatives, and what's the expected impact on the community? | Can you share some insights on the membership structure and benefits for JEVZ 26 charity members, particularly in terms of volunteer opportunities? | What kind of transparency and reporting can JEVZ 26 charity members expect in terms of fund allocation and project outcomes?</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=aT1zY7xNHPQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>TRISHA 20: CHARITY MEMBER</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>90</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Philanthropist</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Non-Profit</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>What specific initiatives has Trisha 20 implemented to increase charity member engagement and retention? | Can you discuss how Trisha 20's charity membership model addresses issues of diversity and inclusion? | How does Trisha 20 measure the impact of its charity membership program on the communities it serves?</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=Dfn_ZpFuy2M</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>🔴 PLS DONATE LIVE | GIVING ROBUX TO VIEWERS</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>80</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Young gamers</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>How will the Robux donations be distributed among viewers, will it be random or based on engagement? | Are there any specific charity initiatives or causes that the stream is supporting with these donations? | Will the stream be tracking the total amount of Robux donated and setting a goal for the charity, like a fundraising target?</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=r2ZdIw01xWY</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Big Heart</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>90</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Philanthropist</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Non-Profit</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>How can we ensure that charitable initiatives like Big Heart are sustainable in the long term, beyond initial funding or donations? | I'd love to hear more about the specific strategies Big Heart is using to measure the impact of their charitable efforts, are they using any particular metrics or benchmarks? | Are there any plans for Big Heart to partner with other organizations or charities to amplify their reach and support a wider range of causes?</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=iEHU8Kiybdo</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/livestreams.xlsx
+++ b/data/livestreams.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O93"/>
+  <dimension ref="A1:O113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4599,18 +4599,1001 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
           <t>https://youtube.com/watch?v=iEHU8Kiybdo</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Rose#1 New Student Charity Member</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>90</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Philanthropist</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>What's the average financial burden that these students are facing, and how will the donated funds be allocated to support their college expenses? | Are there any specific college-related costs that this charity is focusing on, such as tuition, textbooks, or living expenses? | How will the charity ensure transparency and accountability in the distribution of funds to the students, and are there any plans for long-term support or mentorship programs?</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>this channel for charity student to helping they're financial in collenge pls help them thank you PAYPAL :charityphil26@gmail.com.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>2026-07-29T05:01:03Z</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=Vuu7R_wNNgQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>NEW DONATION GAME?! I&amp;#39;M BACK DONATING ROBUX TO LIVE VIEWERS 🔴 LIVE 🔴</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>90</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Young adults and teenagers</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>How do you decide who to donate Robux to during the livestream, is it completely random or are there specific criteria? | I've noticed some viewers are sharing their Robux wishlists in the Discord server, do you take those into consideration when donating? | Are you planning on doing any charity fundraisers or collaborations with other streamers in the future, perhaps for a specific Robux-driven charity event?</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>JOIN UP AND GET A LAUGH OR TWO :D Discord server: https://discord.gg/UDxuJfESc Game link: ...</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>2026-07-29T05:38:34Z</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=APismqX3YlI</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Trying to get a $5 Donation or any Donation</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>90</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Donor</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Non-Profit</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>I'm curious, have you considered partnering with a charity to amplify the impact of these $5 donations, perhaps a local food bank or education initiative? | For those donating via Venmo, will there be any public acknowledgement or leaderboard to encourage others to contribute, similar to a charity marathon? | Are there any plans to offer incentives or matching donations for certain milestones, like a $100 or $500 target, to motivate viewers to give?</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Donat apple pay:droninja3@gmail.com venmo: https://venmo.com/u/Droninja.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>2026-07-29T05:51:59Z</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=OFi3N-EGctQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>project live !  colleting 50 gift rasing and adding people in donation central #roblox #donating</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>85</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Gamers and philanthropists</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>How are you planning to track the 50 gift raisings in Donation Central, is there a specific leaderboard or dashboard you're using? | I'm curious, what kind of items are being donated in Roblox and how will they be distributed to those in need? | Are there any plans to collaborate with other Roblox streamers or charities to amplify the donation efforts and reach a wider audience?</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>This stream is created with #PRISMLiveStudio.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>2026-07-29T06:10:15Z</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=0_6pPoU3EPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Playing Donation Central Raising Stream</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>90</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>philanthropist</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>gaming</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>What's the average donor retention rate you've seen in charity streams like Donation Central, and how do you think we can improve it? | I'm curious about the tech behind Donation Central - are you using any specific plugins or integrations to facilitate donations and track engagement? | How do you handle transparency and accountability in charity streams, ensuring that donors know exactly where their funds are going and what impact they're having?</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>2026-07-29T06:14:11Z</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=YBpFBT9M9TU</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>VR chat fishing and chilling friends only !charity !stackup !calltoarm</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>80</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Gamers and donors</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>How does the Stack Up charity initiative plan to allocate the funds raised from this VR chat event, and what specific causes will they be supporting? | I'd love to know more about the Discord server's role in organizing this charity event - are there any specific channels or resources available for attendees to get involved? | Will there be any opportunities for viewers to participate in the VR chat fishing and chilling activities, or are they primarily for entertainment while we support the charity drive?</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>https://discord.gg/nQtrHEy https://www.twitch.tv/kibathebarbarian https://tiltify.com/@kibathebarbarian/kibathebarbarian Join our ...</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>2026-07-29T00:57:48Z</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=ftgdaKQOZuI</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>🔴Charity Gayle Christian Worship Songs 2025 - Best Praise and Worship Songs Of Charity Gayle</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>90</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Devout Christian</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Non-Profit</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>I'm curious to know if Charity Gayle's worship songs will be featured in any upcoming charity events or fundraisers, potentially raising awareness for social causes? | What's the story behind Charity Gayle's most popular praise song - is there a specific inspiration or experience that drove its creation? | Are there any plans to collaborate with other Christian worship artists or bands to create a charity album or single, with proceeds going to a notable cause?</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Charity Gayle Christian Worship Songs 2025 - Best Praise and Worship Songs Of Charity Gayle ▻Our main goal is to create a ...</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>2026-07-28T07:25:00Z</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=v2xlAaUvceI</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>CommuniKitty CATURDAY! Cutie Cats ~ Free Games: !FOOD !Charity !Throne !Tip !YT !Kick CatGPT: Mother</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>80</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Animal Lover</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Entertainment</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>How does the charity aspect of CommuniKitty CATURDAY work, are there specific organizations that benefit from the !Charity donations? | I'm curious about the !Throne game, is it a popular choice among viewers and does it have any impact on the charity donations throughout the stream? | Are there any plans to collaborate with other charity streams or organizations, perhaps through the !Discord hub, to amplify the fundraising efforts?</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Made with Restream. Livestream on 30+ platforms at once via https://restream.io VOTE !Angel Art: !Discord | !Hubby !Dix !Tip !</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>2026-07-29T04:28:18Z</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=eAv612q4p5A</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Welcome back Glasses 🤓 Fundraiser Cash App 925Rucas</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>90</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Donor</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Non-Profit</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>How does the Glasses fundraiser plan to utilize the Cash App donations, specifically with the code 925Rucas, to support their charitable causes? | Can you share some insights on the impact of using Cash App for fundraising, like the 925Rucas campaign, in terms of donor engagement and retention for charity events? | What kind of transparency and updates can donors expect regarding the allocation of funds raised through the 925Rucas Cash App code, and how will it be used to benefit the charity?</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>2026-07-29T05:55:31Z</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=ghCzZTmrGBk</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>live with mummy charity 💕 good morning my besties 💗 join my live</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>80</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Philanthropic Young Adult</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Non-Profit</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Love the charity focus today, Mummy! What inspired you to partner with this particular organization? | How do you plan to use the momentum from a viral video to drive donations and support for your chosen charity? | Will you be sharing any updates on the charity's current projects or initiatives that we can get involved with?</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>youtube #viralvideo.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>2026-07-29T06:03:42Z</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=LOLN_PqB_e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>NOVA TERMINATOR MODE! | Warzone Mayhem | Charity Stream  Can We Raise £5,000 For The Kids?</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>90</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>gamers and philanthropists</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>gaming</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>How's the donations tracker looking so far, are we on pace to hit that £5,000 goal for the kids by the end of the stream? | What's the plan for the Warzone gameplay, are you focusing on plunder or battle royale mode to maximize entertainment value for donors? | Will there be any special charity-themed gaming challenges or incentives for viewers to contribute during the stream, like a 'donate-to-lose' or 'donate-to-win' segment?</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>LIVE NOW:Tonight we're dropping into Call of Duty: Warzone to have some fun while raising money for an amazing cause.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2026-07-28T19:14:23Z</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=4lmMl9pJyFs</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>🔴Live | PLS Donate &amp;amp; Donate Plus | Donating ROBUX To Fans! #roblox #robux #donateplus #plsdonate</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>90</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Gamers, Roblox enthusiasts</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>How do you handle ROBUX distribution to ensure fairness among fans, especially with the new Donate Plus system? | What's the criteria for selecting winners for the ROBUX giveaways, is it based on donation amount or random selection? | Have you considered partnering with Roblox game devs to create charity-themed games that integrate with Donate Plus for a good cause?</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Join The New Dono Game! Donate Plus!! https://www.roblox.com/games/77403470693847/Donate-Plus ROBUX GIVEAWAYS ...</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>2026-07-29T04:01:05Z</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=_f5MJnFuyJE</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Streaming until I hit 500 subs and get my very first donation!</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>80</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>gamer/streamer</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>entertainment</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>What's the plan for the donation once you hit the 500 sub goal - will it be going to a specific charity or cause? | How do you think the energy of the stream will change once you reach your donation milestone - will you be doing anything special to celebrate? | Are you considering partnering with a charity for future streams, maybe doing a fundraiser or something similar to give back to the community?</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Have some popcorn, snacks with you to fully enjoy this cinema stream Don't forget to comments, Like &amp; subscribe or there will be ...</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>2026-07-28T00:26:04Z</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=j0E369VHZN0</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Giving up is not an option!!</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>75</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Individuals interested in financial education</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Education/Finance</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>What strategies can be applied to maintain perseverance in the face of regulatory hurdles, like those from SEBI, when working towards a charitable cause? | How do you think the educational content on this channel can be leveraged to support fundraising efforts for charities, particularly in the context of financial literacy? | Can you discuss any personal anecdotes or case studies where persistence, as emphasized in the title, led to a successful charitable initiative or campaign?</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>This channel is only for education purposes!! we are not SEBI registered.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>2026-07-29T03:43:57Z</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=do5Tl2QXM_A</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>GIVING AWAY ADMIN TREADMILL Roblox +1 Speed Keyboard Escape LIVE! #roblox  #trending  #fyp</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>75</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Young adults and teenagers</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>How does the +1 Speed Keyboard Escape impact gameplay, especially in admin treadmill Roblox? | Are you considering donating to a charity from the proceeds of the viral livestream, maybe something related to gaming communities? | Can you share any tips on how to optimize the Roblox experience with the given keyboard setup for a seamless livestream?</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>fyp #funny #foryoupage #live #livestream #viral #trending #shorts #roblox.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>2026-07-29T03:28:32Z</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=-devLYrSOB4</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>🔴 MARVEL RIVALS RANKED! 🔴 WE&amp;#39;RE NOT GIVING UP!!</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>75</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Gamers</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>What's the reasoning behind ranking Spider-Man above Doctor Strange, considering their recent performances in the MCU? | How do you think the rankings would change if we factored in the characters' abilities in a team-up scenario, like the Avengers? | Curious to know if you've considered creating a separate ranking for villains - would be interesting to see how Thanos stacks up against other notable Marvel baddies</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>2026-07-29T02:09:30Z</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=9EvUM9nkE5c</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>$1,775 to Talk to a Minister: Ottawa&amp;#39;s Fundraising Hypocrisy Exposed (LIVE) | Famelee TV</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>80</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Socially Conscious Individual</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Non-Profit</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>I'd love to know more about the specifics of Ottawa's fundraising laws and how they're being exploited - are there any particular loopholes that allow ministers to charge exorbitant fees for access? | How does this fundraising hypocrisy impact charitable organizations, like the ones I work with, who rely on government grants and support? | Can Riya and Sam discuss potential solutions to increase transparency in political fundraising, such as implementing stricter disclosure laws or donation caps?</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Riya and Sam are back — and this time they're roasting Ottawa's favourite pastime: political fundraising hypocrisy. From Mark ...</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>2026-07-28T22:03:36Z</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=JqYsfd1d7RQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>🔴 PLS DONATE LIVE GIVEAWAY | GIVING ROBUX TO VIEWERS! (Roblox Live) 💸</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>90</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Gamers, particularly Roblox players</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>How do you decide who to donate ROBUX to first in the PLS DONATE LIVE game mode? | Are you donating ROBUX to viewers who are actively participating in the stream, like commenting or engaging with the chat? | Do you think the PLS DONATE LIVE feature could be used to raise awareness or funds for real-life charities, similar to charity streams on other platforms?</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>In this stream I am playing PLS DONATE LIVE donating ROBUX to EVERYONE. I'll be going around donating to everyone in "PLS ...</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>2026-03-23T13:00:00Z</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=khu5WMfmpYQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>ABP Ganga LIVE: Pune Murder Case | Lucknow Fire |Ram Mandir Donation | Mumbai Monsoon |Bharat Tiwari</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>100</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>General Audience</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>News/Media</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>What's the latest update on the Ram Mandir donation drive and how can individuals contribute to this cause, especially in the context of charitable giving? | Bharat Tiwari, can you shed some light on how the recent Lucknow fire incident has affected local charities and what relief efforts are being made? | How do you think the current monsoon situation in Mumbai will impact charitable organizations' ability to provide aid and support to those in need?</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>ABP Ganga 24x7 LIVE: Pune Murder Case | Lucknow Fire |Ram Mandir Donation | Mumbai Monsoon |Bharat Tiwari हर बार ...</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>2026-03-27T07:04:15Z</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=EjvJGfo7RbY</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>(REAL) 🔴Pls Donate Robux Giveaway Live | Giving Robux In Pls Donate Live (Roblox Robux Giveaway)</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>80</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Roblox players</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>How do you plan to use the donated Robux to support charitable causes within the Roblox community? | What's the most creative way you've seen a Roblox user utilize their donated Robux to give back to others? | Will you be partnering with any specific Roblox groups or charities for this giveaway, or is it more of an individual effort?</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(REAL) Pls Donate Robux Giveaway Live | Giving Robux In Pls Donate Live (Roblox Robux Giveaway) #plsdonate ...</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>2026-06-15T22:10:00Z</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=n9U4z1JO824</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/livestreams.xlsx
+++ b/data/livestreams.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Livestreams" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Livestreams" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O113"/>
+  <dimension ref="A1:O130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -546,1488 +546,1500 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LinkedIn tôn trọng quyền riêng tư của bạn</t>
+          <t>Panel Discussion - The evolution of event fundraising</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Organization Manager</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Charity</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người?</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
-        <is>
-          <t>Location: Trạng thái là đang trực tuyến
-LinkedIn và các bên thứ 3 sử dụng các cookie cần thiết và không cần thiết để cung cấp, bảo mật, phân tích và cải thiện Dịch vụ của chúng tôi, đồng thời hiển thị cho bạn các quảng cáo có liên quan (bao gồm quảng cáo nghề nghiệp và việc làm) trên và ngoài LinkedIn. Tìm hiểu thêm trong Chính sách cookie của chúng tôi.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Thứ 4, 1 thg 7, 2026, (21:00 giờ địa phương của bạn)</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/events/7477663786670338050/</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>LinkedIn tôn trọng quyền riêng tư của bạn</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>15</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Location: Trạng thái là đang trực tuyến
-LinkedIn và các bên thứ 3 sử dụng các cookie cần thiết và không cần thiết để cung cấp, bảo mật, phân tích và cải thiện Dịch vụ của chúng tôi, đồng thời hiển thị cho bạn các quảng cáo có liên quan (bao gồm quảng cáo nghề nghiệp và việc làm) trên và ngoài LinkedIn. Tìm hiểu thêm trong Chính sách cookie của chúng tôi.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5ngày</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/events/7475911060516982785/</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>LinkedIn tôn trọng quyền riêng tư của bạn</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>26</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Location: Trạng thái là đang trực tuyến
-LinkedIn và các bên thứ 3 sử dụng các cookie cần thiết và không cần thiết để cung cấp, bảo mật, phân tích và cải thiện Dịch vụ của chúng tôi, đồng thời hiển thị cho bạn các quảng cáo có liên quan (bao gồm quảng cáo nghề nghiệp và việc làm) trên và ngoài LinkedIn. Tìm hiểu thêm trong Chính sách cookie của chúng tôi.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Thứ 3, 30 thg 6, 2026, (19:00 giờ địa phương của bạn)</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/events/7477575864034062336/</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Panel Discussion - The evolution of event fundraising</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>56</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Organization Manager</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Charity</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người?</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
         <is>
           <t>Panel Discussion - The evolution of event fundraising
 YouTube · Charity Digital
 &gt;20 lượt xem: · 1 năm trước</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Tokenization in Modern Finance: BOI-ITC Webinar</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B4" t="n">
         <v>63</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Asset Tokenization Business</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>How do you see tokenization impacting the regulatory landscape for asset-backed securities, particularly in regards to the SEC's current stance on digital asset offerings?</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Tokenization in Modern Finance: BOI-ITC Webinar
 LinkedIn · Chinonso Dike, CAMS, CFCS, CRC, CCFC, CKC, CDPO
 &gt;20 lượt thể hiện cảm xúc · 6 ngày trước</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>What is Livestream Fundraising? | Funraise Nonprofit ...</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B5" t="n">
         <v>71</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Organization Manager</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Charity</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người?</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>What is Livestream Fundraising? | Funraise Nonprofit ...
 YouTube · Funraise
 &gt;240 lượt xem: · 6 năm trước</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Tokenization in the UAE Webinar | Fasih S.</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B6" t="n">
         <v>63</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Asset Tokenization Business</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Fasih, you mentioned the importance of regulatory compliance in tokenization. Can you elaborate on how UAE's existing laws, such as the Federal Decree-Law No. 9 of 2021, will be adapted to accommodate tokenized assets?</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Tokenization in the UAE Webinar | Fasih S.
 LinkedIn · Fasih S.
 2 lượt bày tỏ cảm xúc · 2 tháng trước</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Tokenized Shares Webinar on May 12 2026</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B7" t="n">
         <v>48</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Asset Tokenization Business</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Have you considered the tax implications of tokenized shares on secondary markets, and how can issuers mitigate potential liabilities?</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Tokenized Shares Webinar on May 12 2026
 LinkedIn · Giuliano Tell
 &gt;20 lượt thể hiện cảm xúc · 2 tháng trước</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>STO Foundation Webinar Center Sneak Peek</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B8" t="n">
         <v>24</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>STO Foundation Webinar Center Sneak Peek
 LinkedIn · STO Foundation
 &gt;190 lượt thể hiện cảm xúc · 3 tuần trước</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Experts Share Insights on Future of Digital Assets</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B9" t="n">
         <v>78</v>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Asset Tokenization Business</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>How do the panelists envision the regulatory landscape for digital assets evolving in the next 2-3 years, and what implications does this have for asset tokenization adoption?</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Experts Share Insights on Future of Digital Assets
 LinkedIn · Cambridge Centre for Alternative Finance, Cambridge Judge Business School
 &gt;80 lượt thể hiện cảm xúc · 5 tháng trước</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Insights from Mark Williamson &amp; More | Cambridge Centre ...</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B10" t="n">
         <v>32</v>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Insights from Mark Williamson &amp; More | Cambridge Centre ...
 LinkedIn · Cambridge Centre for Alternative Finance, Cambridge Judge Business School
 &gt;30 lượt thể hiện cảm xúc · 4 tháng trước</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Fundraising Ideas for Live Streaming Online</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B11" t="n">
         <v>63</v>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Organization Manager</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Charity</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người?</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Fundraising Ideas for Live Streaming Online
 YouTube · PTZOptics
 &gt;350 lượt xem: · 1 năm trước</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>How Tokenisation Improves Financial Processes</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B12" t="n">
         <v>40</v>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Asset Tokenization Business</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>I'm curious to know how tokenization can help mitigate the risk of asset price volatility during the tokenization process, especially for illiquid assets like real estate.</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>How Tokenisation Improves Financial Processes
 LinkedIn
 https://www.linkedin.com › finance › h...</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Paris Blockchain Week's Post</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B13" t="n">
         <v>20</v>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Paris Blockchain Week's Post
 LinkedIn · Paris Blockchain Week
 &gt;20 lượt thể hiện cảm xúc · 3 tháng trước</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>SS&amp;C Technologies' Post</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B14" t="n">
         <v>16</v>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>SS&amp;C Technologies' Post
 LinkedIn · SS&amp;C Technologies
 &gt;10 lượt thể hiện cảm xúc · 1 ngày trước</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>How To Use Facebook Live For Fundraising Events</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B15" t="n">
         <v>63</v>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Organization Manager</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Charity</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Have you considered the impact of Facebook's algorithm changes on fundraising event visibility, and how can we adapt our strategies to maximize reach?</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>How To Use Facebook Live For Fundraising Events
 YouTube · Aplos
 &gt;1,5 N lượt xem: · 5 năm trước</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Tokenisation: Unlocking Liquidity and Efficiency</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="B16" t="n">
         <v>40</v>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Asset Tokenization Business</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>How do you see tokenization impacting the current regulatory landscape for asset-backed securities, particularly in regions with strict capital controls?</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Tokenisation: Unlocking Liquidity and Efficiency
 LinkedIn · Alex Playford
 2 lượt bày tỏ cảm xúc · 3 tuần trước</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Digital Assets, Tokenization, and Stablecoins</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B17" t="n">
         <v>63</v>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Tokenization</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>How do you see Chainlink's oracle services being integrated with tokenized assets to enhance price stability and accuracy?</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Digital Assets, Tokenization, and Stablecoins
 Chainlink
 https://chain.link › webinar › 2026-da...</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Online webinar. Tokenization beyond MiCA - Simplify Labs</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B18" t="n">
         <v>63</v>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Tokenization</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>How do you see the MiCA regulation influencing the adoption of tokenization in European fintechs, and what are the potential workarounds for smaller institutions?</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Online webinar. Tokenization beyond MiCA - Simplify Labs
 Livestorm
 https://app.livestorm.co › simplify-labs</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>How to do a virtual livestream fundraiser with Eventgroove ...</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="B19" t="n">
         <v>55</v>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Fundarising Live</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Have you considered integrating social proof elements, such as donor recognition or impact visuals, into the Eventgroove livestream to boost engagement and encourage more donations?</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>How to do a virtual livestream fundraiser with Eventgroove ...
 YouTube · Eventgroove
 &gt;160 lượt xem: · 4 năm trước</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>#tokenization #uae #digitalassets #blockchain #webinar</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="B20" t="n">
         <v>63</v>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Tokenization</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>How does the proposed tokenization framework address regulatory hurdles in the UAE, particularly with regards to the Central Bank's stance on digital assets?</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>#tokenization #uae #digitalassets #blockchain #webinar
 LinkedIn · DigiShares
 &gt;20 lượt thể hiện cảm xúc · 2 tháng trước</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>The New Telethon How Live Streaming Has Changed ...</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="B21" t="n">
         <v>2</v>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Marketing Professionals</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người?</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>The New Telethon How Live Streaming Has Changed ...
 YouTube · Neon One
 &gt;360 lượt xem: · 5 năm trước</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Livestream Fundraising — With Max (CEO) &amp; Tori (Customer ...</t>
         </is>
       </c>
-      <c r="B25" t="n">
+      <c r="B22" t="n">
         <v>71</v>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Founder, CEO</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Startup</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Max, can you speak to the ROI analysis you've done on integrating Givebutter with existing donor management systems?</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Livestream Fundraising — With Max (CEO) &amp; Tori (Customer ...
 YouTube · Givebutter
 &gt;1,8 N lượt xem: · 6 năm trước</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Tokenization of securities markets</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="B23" t="n">
         <v>63</v>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Tokenization</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người?</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Tokenization of securities markets
 ACSDA
 https://www.acsda.org › webinar › tok...</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Facebook Live Fundraising Best Practices for Nonprofits ...</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="B24" t="n">
         <v>71</v>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Organization Manager</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Charity</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Have you found that leveraging Facebook Live's built-in fundraising features, such as the 'Donate' button, has a significant impact on overall fundraising success for nonprofits?</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>Facebook Live Fundraising Best Practices for Nonprofits ...
 YouTube · MobileCause now GiveSmart
 &gt;2 N lượt xem: · 9 năm trước</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>AI, Tokenization, and the Future of Operations 2026 - FT Live ...</t>
         </is>
       </c>
-      <c r="B28" t="n">
+      <c r="B25" t="n">
         <v>55</v>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Tokenization</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người?</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>AI, Tokenization, and the Future of Operations 2026 - FT Live ...
 Financial Times
 https://aitokenization.live.ft.com</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>How to Increase Attendance at Your Next Fundraising Event ...</t>
         </is>
       </c>
-      <c r="B29" t="n">
+      <c r="B26" t="n">
         <v>48</v>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Organization Manager</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Charity</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Have you considered the impact of social media advertising on event attendance, and if so, what metrics do you recommend tracking to measure its effectiveness?</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>How to Increase Attendance at Your Next Fundraising Event ...
 YouTube · MobileCause now GiveSmart
 &gt;9,6 N lượt xem: · 6 năm trước</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>[webinar] Online Event Fundraiser: Lessons to Share</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="B27" t="n">
         <v>48</v>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Fundarise Livestream</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>For organizations with limited online presence, what strategies have you found most effective in leveraging social media to promote online events and drive ticket sales?</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>[webinar] Online Event Fundraiser: Lessons to Share
 Vimeo
 https://vimeo.com › ... › Videos</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Best 1 RWA tokenization platforms - S-PRO</t>
         </is>
       </c>
-      <c r="B31" t="n">
+      <c r="B28" t="n">
         <v>55</v>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Tokenization</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người?</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>Best 1 RWA tokenization platforms - S-PROS-PROhttps://s-pro.io › rwa-tokenization-platforms</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Tokenization Protocols - Meegle</t>
         </is>
       </c>
-      <c r="B32" t="n">
+      <c r="B29" t="n">
         <v>55</v>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Tokenization</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>Have you considered the implications of tokenization on data governance, particularly in regulated industries like finance where data residency and sovereignty are major concerns?</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Tokenization Protocols - MeegleMeeglehttps://www.meegle.com › en_us › topics › tokenization-...</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>[Webinar] Hit your fundraising goals without hosting another ...</t>
         </is>
       </c>
-      <c r="B33" t="n">
+      <c r="B30" t="n">
         <v>71</v>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Organization Manager</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Charity</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người?</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>[Webinar] Hit your fundraising goals without hosting another ...
 YouTube · Givebutter
 &gt;330 lượt xem: · 3 tháng trước</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Fund Tokenization: Building Bridges in Global Fund Distribution</t>
         </is>
       </c>
-      <c r="B34" t="n">
+      <c r="B31" t="n">
         <v>55</v>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Tokenization</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>How do you see tokenization addressing the issue of fragmented fund ownership structures, which can lead to inefficient distribution and high costs for investors?</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>Fund Tokenization: Building Bridges in Global Fund Distribution
 Nicsa
 https://nicsa.org › product › fund-tok...</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>🔴 LIVE | Fundraiser for Jantar Mantar Students | Every Donation Makes a Difference ❤️</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>165</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Gamers and philanthropists</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>How will the funds raised from this BGMI charity stream be allocated to support the students at Jantar Mantar, are there any specific programs or initiatives that will be prioritized? | I'd love to know more about the current challenges faced by the students at Jantar Mantar and how this charity stream aims to address them, are there any specific stories or examples you can share? | Will there be any opportunities for donors to get involved beyond just contributing financially, such as volunteering or mentoring the students at Jantar Mantar?</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>LIVE BGMI Charity Stream | Supporting Students at Jantar Mantar ❤️     Welcome to today's **BGMI LIVE Charity Stream!</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2026-07-21T15:33:34Z</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=djx068LuF4Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>LIVE Fundraiser Minecraft and Heal behind the scenes in real life of a nonprofit</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>145</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Philanthropist/Gamer</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Nonprofit</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>I'm curious to know how the Eudaimonia Project Film Festival plans to allocate the donated funds, will they be used for specific programs or general operational costs? | How does the nonprofit plan to measure the impact of the fundraiser, are there any specific metrics or outcomes they're hoping to achieve with the donations? | Are there any plans to collaborate with other nonprofits or organizations in the charity sector to amplify the effects of the fundraiser and the film festival?</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Please Donte https://live.givebutter.com/c/the-eudaimonia-project-film-festival-b2vu4h.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2026-07-21T13:33:44Z</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=OTqbl8UnInE</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>🔴 LIVE CHARITY STREAM | Save Little Krishna ❤️ Every Donation Can Save a Life 🙏</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>145</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Empathetic Donor</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Non-Profit/Healthcare</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>What's the current status of Little Krishna's treatment and how will the donations from this stream be allocated to support his medical expenses? | Are there any plans for long-term support or follow-up care for Little Krishna after the initial treatment, and how can we as a community continue to help? | Can you share more about the specific medical condition Little Krishna is facing and what the prognosis is with timely and proper treatment, so we can better understand the urgency of the situation?</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Please Help Save Little Krishna Little Krishna is fighting a serious medical condition and urgently needs support for treatment.</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026-07-21T15:35:00Z</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=I0yjeB8Tqf4</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>🔴 LIVE | Fundraiser for Jantar Mantar Students | Every Donation Makes a Difference ❤️</t>
+          <t>the andrew nocturnna and wEndy charity stream</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>165</v>
+        <v>110</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -2036,17 +2048,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Gamers and philanthropists</t>
+          <t>supporter/donor</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Gaming</t>
+          <t>gaming/charity</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>How will the funds raised from this BGMI charity stream be allocated to support the students at Jantar Mantar, are there any specific programs or initiatives that will be prioritized? | I'd love to know more about the current challenges faced by the students at Jantar Mantar and how this charity stream aims to address them, are there any specific stories or examples you can share? | Will there be any opportunities for donors to get involved beyond just contributing financially, such as volunteering or mentoring the students at Jantar Mantar?</t>
+          <t>Just donated to the GoFundMe campaign, hoping Andrew gets the support he needs - what's the current status on his housing situation? | How will the funds raised from this stream be allocated to support Andrew's rehabilitation and education? | Are there any plans for long-term support or mentorship programs for Andrew and others who've experienced similar situations, perhaps through partnerships with local charities?</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2056,28 +2068,28 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>LIVE BGMI Charity Stream | Supporting Students at Jantar Mantar ❤️     Welcome to today's **BGMI LIVE Charity Stream!</t>
+          <t>the gofundme fundraiser: https://www.gofundme.com/f/andrew-hospitalized-by-abusive-parents-now-homeless.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-07-21T15:33:34Z</t>
+          <t>2026-01-13T05:40:03Z</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=djx068LuF4Y</t>
+          <t>https://youtube.com/watch?v=tETQ11QlHGo</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>LIVE Fundraiser Minecraft and Heal behind the scenes in real life of a nonprofit</t>
+          <t>pls donate</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -2086,17 +2098,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Philanthropist/Gamer</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Nonprofit</t>
+          <t>Charity</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>I'm curious to know how the Eudaimonia Project Film Festival plans to allocate the donated funds, will they be used for specific programs or general operational costs? | How does the nonprofit plan to measure the impact of the fundraiser, are there any specific metrics or outcomes they're hoping to achieve with the donations? | Are there any plans to collaborate with other nonprofits or organizations in the charity sector to amplify the effects of the fundraiser and the film festival?</t>
+          <t>What's the primary cause that this charity is supporting, and how will the donated funds be allocated? | Are there any specific donation milestones or targets that we can help reach during this livestream? | Will there be any matching donations or sponsorships to amplify the impact of our contributions?</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2104,30 +2116,25 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Please Donte https://live.givebutter.com/c/the-eudaimonia-project-film-festival-b2vu4h.</t>
-        </is>
-      </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-07-21T13:33:44Z</t>
+          <t>2026-07-21T13:00:19Z</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=OTqbl8UnInE</t>
+          <t>https://youtube.com/watch?v=P3-fKqN2b8A</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>🔴 LIVE CHARITY STREAM | Save Little Krishna ❤️ Every Donation Can Save a Life 🙏</t>
+          <t>Wolf&amp;#39;s Den Takeover Tuesday of the AGB Charity channel on kick!! !AGB !face !AGB !face</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>145</v>
+        <v>80</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -2136,17 +2143,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Empathetic Donor</t>
+          <t>Gamers, particularly those interested in charity events and community engagement</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Non-Profit/Healthcare</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>What's the current status of Little Krishna's treatment and how will the donations from this stream be allocated to support his medical expenses? | Are there any plans for long-term support or follow-up care for Little Krishna after the initial treatment, and how can we as a community continue to help? | Can you share more about the specific medical condition Little Krishna is facing and what the prognosis is with timely and proper treatment, so we can better understand the urgency of the situation?</t>
+          <t>Love the gaming for a cause concept, how does the AGB Charity channel plan to allocate donations from tonight's stream? | MnK, what's your strategy for tackling tough levels in the games you're playing, and will you be taking donations for specific charity milestones? | Will the stream be featuring any charity-specific games or challenges, like a 'donate to skip' level or a 'charity boss fight'?</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2156,28 +2163,28 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Please Help Save Little Krishna Little Krishna is fighting a serious medical condition and urgently needs support for treatment.</t>
+          <t>MnK old Fart playing some Games.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-07-21T15:35:00Z</t>
+          <t>2026-07-21T13:52:24Z</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=I0yjeB8Tqf4</t>
+          <t>https://youtube.com/watch?v=uMuJEqYyFr0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>the andrew nocturnna and wEndy charity stream</t>
+          <t>deep focus lofi radio 🎯 24/7 charity beats for deep work (live now)</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -2186,17 +2193,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>supporter/donor</t>
+          <t>Students, programmers, and individuals seeking focus or relaxation</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>gaming/charity</t>
+          <t>Music/Entertainment</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Just donated to the GoFundMe campaign, hoping Andrew gets the support he needs - what's the current status on his housing situation? | How will the funds raised from this stream be allocated to support Andrew's rehabilitation and education? | Are there any plans for long-term support or mentorship programs for Andrew and others who've experienced similar situations, perhaps through partnerships with local charities?</t>
+          <t>I've noticed the lofi beats have a calming effect, do you think the same tracks could be used in therapy sessions for anxiety relief in homeless shelters? | How does the donation process work - is it a fixed amount per listener or based on the total hours streamed? | Are there any plans to collaborate with mental health professionals to create customized lofi playlists for specific conditions, like PTSD, which is common among the homeless population?</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2206,28 +2213,28 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>the gofundme fundraiser: https://www.gofundme.com/f/andrew-hospitalized-by-abusive-parents-now-homeless.</t>
+          <t>24/7 Lofi beats for deep focus, sleep, and anxiety relief. Every minute you listen helps provide real support for the homeless.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-01-13T05:40:03Z</t>
+          <t>2026-07-21T10:00:07Z</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=tETQ11QlHGo</t>
+          <t>https://youtube.com/watch?v=5vgTpAWTqy4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>pls donate</t>
+          <t>🔴CHARITY🔴DONATE = CHANGE THE GAME🔴GEOMETRY DASH TRIATHLON</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -2236,17 +2243,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Gamers, charity supporters</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Charity</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>What's the primary cause that this charity is supporting, and how will the donated funds be allocated? | Are there any specific donation milestones or targets that we can help reach during this livestream? | Will there be any matching donations or sponsorships to amplify the impact of our contributions?</t>
+          <t>How does the donation tier system work in terms of unlocking exclusive rewards in the Geometry Dash triathlon? | I'm curious to know if there are any specific charity initiatives or causes that the Globed Room 360648 is supporting through this event? | Are there any plans to offer additional challenges or bonus levels for donors who contribute above a certain amount, similar to the ones mentioned in the Challenge Info section?</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2254,21 +2261,26 @@
           <t>YouTube</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Donate here: https://charity.gd/gdce/ Globed Room: 360648 Challenge Info   Depending on the amount donated, you can buy ...</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-07-21T13:00:19Z</t>
+          <t>2026-07-21T13:00:00Z</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=P3-fKqN2b8A</t>
+          <t>https://youtube.com/watch?v=woFm1lBy8cE</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Wolf&amp;#39;s Den Takeover Tuesday of the AGB Charity channel on kick!! !AGB !face !AGB !face</t>
+          <t>God says&amp;quot; Today Marks the End of That Affliction | Evang Charity Odochi is live!</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -2281,17 +2293,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Gamers, particularly those interested in charity events and community engagement</t>
+          <t>Individuals seeking spiritual guidance or solace</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Gaming</t>
+          <t>Religion/Spirituality</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Love the gaming for a cause concept, how does the AGB Charity channel plan to allocate donations from tonight's stream? | MnK, what's your strategy for tackling tough levels in the games you're playing, and will you be taking donations for specific charity milestones? | Will the stream be featuring any charity-specific games or challenges, like a 'donate to skip' level or a 'charity boss fight'?</t>
+          <t>Evang Charity, what role do you believe faith-based organizations can play in addressing systemic afflictions, such as poverty and inequality, in our communities? | Can you share an example of a successful charity initiative that you've been involved with, and how it's helped alleviate affliction for a specific group of people? | How do you think we can balance spiritual guidance with tangible support in charity work, to ensure we're making a lasting impact on those we're trying to help?</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2301,24 +2313,24 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>MnK old Fart playing some Games.</t>
+          <t>God says" Today Marks the End of That Affliction | Evang Charity Odochi is live!</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-07-21T13:52:24Z</t>
+          <t>2026-07-21T13:35:36Z</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=uMuJEqYyFr0</t>
+          <t>https://youtube.com/watch?v=wVHnJwaSpWI</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>deep focus lofi radio 🎯 24/7 charity beats for deep work (live now)</t>
+          <t>Ready For Battle⚔️🛡️ || Kidz Family Camp 2026 || Pastor Charity Kalstrup</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2331,17 +2343,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Students, programmers, and individuals seeking focus or relaxation</t>
+          <t>Christian families with children</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Music/Entertainment</t>
+          <t>Religion</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>I've noticed the lofi beats have a calming effect, do you think the same tracks could be used in therapy sessions for anxiety relief in homeless shelters? | How does the donation process work - is it a fixed amount per listener or based on the total hours streamed? | Are there any plans to collaborate with mental health professionals to create customized lofi playlists for specific conditions, like PTSD, which is common among the homeless population?</t>
+          <t>Pastor Charity, how do you think the Kidz Family Camp 2026 can be used as a platform to raise awareness and funds for local charities, particularly those supporting underprivileged kids? | I'm curious to know more about the chooselife Kidz Ministry's outreach programs - are there any plans to collaborate with other organizations to amplify the impact of the Kidz Family Camp? | What role do you envision the church community playing in supporting the Kidz Family Camp, and are there opportunities for volunteers to get involved in the planning and execution process?</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2351,24 +2363,24 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>24/7 Lofi beats for deep focus, sleep, and anxiety relief. Every minute you listen helps provide real support for the homeless.</t>
+          <t>This message was recorded live at chooselife CHURCH in Hobbs, NM. For more information about Chooselife Kidz Ministry visit ...</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-07-21T10:00:07Z</t>
+          <t>2026-07-21T16:00:00Z</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=5vgTpAWTqy4</t>
+          <t>https://youtube.com/watch?v=pQS1z_hYIco</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>🔴CHARITY🔴DONATE = CHANGE THE GAME🔴GEOMETRY DASH TRIATHLON</t>
+          <t>Charity Cup Mini S-10</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -2381,7 +2393,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Gamers, charity supporters</t>
+          <t>Gamers, Esports enthusiasts</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2391,7 +2403,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>How does the donation tier system work in terms of unlocking exclusive rewards in the Geometry Dash triathlon? | I'm curious to know if there are any specific charity initiatives or causes that the Globed Room 360648 is supporting through this event? | Are there any plans to offer additional challenges or bonus levels for donors who contribute above a certain amount, similar to the ones mentioned in the Challenge Info section?</t>
+          <t>How does the Charity Cup Mini S-10 format impact donor engagement, particularly in terms of repeat participation? | What's the strategy behind using #PRISMLiveStudio for this event, and how does it enhance the overall charity experience? | Are there any plans to offer virtual participation options for the Charity Cup Mini S-10, to expand the reach and inclusivity of the event?</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2401,47 +2413,47 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Donate here: https://charity.gd/gdce/ Globed Room: 360648 Challenge Info   Depending on the amount donated, you can buy ...</t>
+          <t>This stream is created with #PRISMLiveStudio.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-07-21T13:00:00Z</t>
+          <t>2026-07-21T16:18:41Z</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=woFm1lBy8cE</t>
+          <t>https://youtube.com/watch?v=Mod7A6OTwZw</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>God says&amp;quot; Today Marks the End of That Affliction | Evang Charity Odochi is live!</t>
+          <t>Breaking News LIVE | Current Affairs News | CJP Protest | Headlines | Ram Mandir Donation</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Individuals seeking spiritual guidance or solace</t>
+          <t>Individuals interested in current events and news, particularly those from India or with an interest in Indian affairs</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Religion/Spirituality</t>
+          <t>News/Media</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Evang Charity, what role do you believe faith-based organizations can play in addressing systemic afflictions, such as poverty and inequality, in our communities? | Can you share an example of a successful charity initiative that you've been involved with, and how it's helped alleviate affliction for a specific group of people? | How do you think we can balance spiritual guidance with tangible support in charity work, to ensure we're making a lasting impact on those we're trying to help?</t>
+          <t>Curious to know how the Ram Mandir donation drive is impacting local communities, are there any plans to allocate funds to support social causes? | Can you provide an update on the CJP protest and its potential implications on the current political landscape, particularly in regards to charitable organizations? | How do you think the recent developments in the Ram Mandir donation campaign will influence philanthropic efforts in India, especially for charities focused on education and healthcare?</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2451,47 +2463,47 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>God says" Today Marks the End of That Affliction | Evang Charity Odochi is live!</t>
+          <t>Aaj Tak Breaking News LIVE | Current Affairs News | CJP Protest | Headlines | Ram Mandir Donation Aaj Tak LIVE – International ...</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-07-21T13:35:36Z</t>
+          <t>2026-07-21T12:30:00Z</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=wVHnJwaSpWI</t>
+          <t>https://youtube.com/watch?v=7rhl6BGcLUA</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Ready For Battle⚔️🛡️ || Kidz Family Camp 2026 || Pastor Charity Kalstrup</t>
+          <t>WE HAVE YOUR 6 JULY FUNDRAISING FOR REGIMENT is in full swing!!</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Christian families with children</t>
+          <t>gamers</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Religion</t>
+          <t>gaming</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Pastor Charity, how do you think the Kidz Family Camp 2026 can be used as a platform to raise awareness and funds for local charities, particularly those supporting underprivileged kids? | I'm curious to know more about the chooselife Kidz Ministry's outreach programs - are there any plans to collaborate with other organizations to amplify the impact of the Kidz Family Camp? | What role do you envision the church community playing in supporting the Kidz Family Camp, and are there opportunities for volunteers to get involved in the planning and execution process?</t>
+          <t>How does the Spearhead update impact the gameplay experience for Regiment players, and will the fundraising campaign offer exclusive in-game content? | What's the current progress on the WE HAVE YOUR 6 JULY FUNDRAISING campaign, and are there any specific charity initiatives that RegimentGG is supporting this month? | Will the Gray Zone Warfare 0.4 update include any new features that allow players to create custom charity events or tournaments within the game, similar to what we've seen in other gaming communities?</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2501,47 +2513,47 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>This message was recorded live at chooselife CHURCH in Hobbs, NM. For more information about Chooselife Kidz Ministry visit ...</t>
+          <t>LIVE NOW – Gray Zone Warfare 0.4 “SPEARHEAD” UPDATE!! ​ ⁨@madfingergames⁩ ⁨@RegimentGG⁩ The battlefield just ...</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-07-21T16:00:00Z</t>
+          <t>2026-07-21T00:06:27Z</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=pQS1z_hYIco</t>
+          <t>https://youtube.com/watch?v=d1TEM_LuSbo</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Charity Cup Mini S-10</t>
+          <t>Skyview - West of Frontier Ag Inc - Goodland, KS</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Gamers, Esports enthusiasts</t>
+          <t>Farmers, Agricultural Professionals, or Local Community Members</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Gaming</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>How does the Charity Cup Mini S-10 format impact donor engagement, particularly in terms of repeat participation? | What's the strategy behind using #PRISMLiveStudio for this event, and how does it enhance the overall charity experience? | Are there any plans to offer virtual participation options for the Charity Cup Mini S-10, to expand the reach and inclusivity of the event?</t>
+          <t>I'm curious to know if Frontier Ag Inc has considered partnering with local charities to use this skyview service for environmental monitoring or disaster response efforts? | How does the community service aspect of this skyview project align with Frontier Ag Inc's overall corporate social responsibility goals, particularly in terms of supporting local Kansas initiatives? | Are there any plans to use the footage from this skyview service to support educational programs or workshops, potentially in partnership with local non-profits or charities focused on agriculture or conservation?</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2551,47 +2563,47 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>This stream is created with #PRISMLiveStudio.</t>
+          <t>View of the skies west of Frontier Ag Inc in Goodland Kansas. A community service from Frontier Ag Inc. https://frontieraginc.com/</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-07-21T16:18:41Z</t>
+          <t>2025-12-17T05:45:00Z</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=Mod7A6OTwZw</t>
+          <t>https://youtube.com/watch?v=XjuKPeQx2V0</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Breaking News LIVE | Current Affairs News | CJP Protest | Headlines | Ram Mandir Donation</t>
+          <t>Skyview - East of Frontier Ag Inc - Goodland, KS</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Individuals interested in current events and news, particularly those from India or with an interest in Indian affairs</t>
+          <t>Farmers, Agricultural Professionals, or Local Community Members</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>News/Media</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Curious to know how the Ram Mandir donation drive is impacting local communities, are there any plans to allocate funds to support social causes? | Can you provide an update on the CJP protest and its potential implications on the current political landscape, particularly in regards to charitable organizations? | How do you think the recent developments in the Ram Mandir donation campaign will influence philanthropic efforts in India, especially for charities focused on education and healthcare?</t>
+          <t>I'm curious to know if Frontier Ag Inc has considered partnering with local charities to utilize this skyview for environmental monitoring or conservation efforts? | How does the community service aspect of this skyview project align with Frontier Ag Inc's overall corporate social responsibility initiatives? | Are there any plans to use this skyview to support disaster relief or emergency response efforts in the Goodland, KS area, potentially in collaboration with local non-profits?</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2601,47 +2613,47 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Aaj Tak Breaking News LIVE | Current Affairs News | CJP Protest | Headlines | Ram Mandir Donation Aaj Tak LIVE – International ...</t>
+          <t>View of the skies east of Frontier Ag Inc in Goodland Kansas. A community service from Frontier Ag Inc. https://frontieraginc.com/</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-07-21T12:30:00Z</t>
+          <t>2025-12-17T05:50:00Z</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=7rhl6BGcLUA</t>
+          <t>https://youtube.com/watch?v=PrqfpZq4ERI</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>WE HAVE YOUR 6 JULY FUNDRAISING FOR REGIMENT is in full swing!!</t>
+          <t>Skyview - South of Frontier Ag Inc - Goodland, KS</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>gamers</t>
+          <t>Farmers, Agricultural professionals, or individuals interested in weather conditions</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>gaming</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>How does the Spearhead update impact the gameplay experience for Regiment players, and will the fundraising campaign offer exclusive in-game content? | What's the current progress on the WE HAVE YOUR 6 JULY FUNDRAISING campaign, and are there any specific charity initiatives that RegimentGG is supporting this month? | Will the Gray Zone Warfare 0.4 update include any new features that allow players to create custom charity events or tournaments within the game, similar to what we've seen in other gaming communities?</t>
+          <t>I'm curious to know if the community service initiative by Frontier Ag Inc has led to any notable improvements in local air quality monitoring, given the proximity to agricultural areas? | Has Frontier Ag Inc considered partnering with local charities or environmental groups to further amplify the impact of their community service efforts in Goodland, KS? | Are there any plans to expand the skyview monitoring to other locations within Kansas, potentially in collaboration with regional conservation organizations?</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2651,24 +2663,24 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>LIVE NOW – Gray Zone Warfare 0.4 “SPEARHEAD” UPDATE!! ​ ⁨@madfingergames⁩ ⁨@RegimentGG⁩ The battlefield just ...</t>
+          <t>View of the skies south of Frontier Ag Inc in Goodland Kansas. A community service from Frontier Ag Inc. https://frontieraginc.com/</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-07-21T00:06:27Z</t>
+          <t>2025-12-17T05:50:00Z</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=d1TEM_LuSbo</t>
+          <t>https://youtube.com/watch?v=xU7UDBXiAwA</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Skyview - West of Frontier Ag Inc - Goodland, KS</t>
+          <t>Skyview - North of Frontier Ag Inc - Goodland, KS</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -2681,7 +2693,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Farmers, Agricultural Professionals, or Local Community Members</t>
+          <t>Farmers, Agricultural enthusiasts</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2691,7 +2703,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>I'm curious to know if Frontier Ag Inc has considered partnering with local charities to use this skyview service for environmental monitoring or disaster response efforts? | How does the community service aspect of this skyview project align with Frontier Ag Inc's overall corporate social responsibility goals, particularly in terms of supporting local Kansas initiatives? | Are there any plans to use the footage from this skyview service to support educational programs or workshops, potentially in partnership with local non-profits or charities focused on agriculture or conservation?</t>
+          <t>I'm curious to know if Frontier Ag Inc has considered partnering with local charities to use this skyview service for environmental monitoring or conservation efforts? | How does the community service aspect of this skyview project align with Frontier Ag Inc's overall corporate social responsibility goals, particularly in the Goodland Kansas area? | Are there any plans to use the footage from this skyview service to support educational initiatives or fundraising campaigns for local charities, such as those focused on agriculture or rural development?</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2701,24 +2713,24 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>View of the skies west of Frontier Ag Inc in Goodland Kansas. A community service from Frontier Ag Inc. https://frontieraginc.com/</t>
+          <t>View of the skies north of Frontier Ag Inc in Goodland Kansas. A community service from Frontier Ag Inc. https://frontieraginc.com/</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2025-12-17T05:45:00Z</t>
+          <t>2025-12-17T05:50:00Z</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=XjuKPeQx2V0</t>
+          <t>https://youtube.com/watch?v=70YcImm96ws</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Skyview - East of Frontier Ag Inc - Goodland, KS</t>
+          <t>Skyview - South of Frontier Ag Inc - Quinter, KS</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2741,7 +2753,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>I'm curious to know if Frontier Ag Inc has considered partnering with local charities to utilize this skyview for environmental monitoring or conservation efforts? | How does the community service aspect of this skyview project align with Frontier Ag Inc's overall corporate social responsibility initiatives? | Are there any plans to use this skyview to support disaster relief or emergency response efforts in the Goodland, KS area, potentially in collaboration with local non-profits?</t>
+          <t>I'm curious to know if the community service initiative by Frontier Ag Inc has led to any notable improvements in local weather monitoring or emergency response systems in Quinter, KS? | How does the view from Skyview contribute to the overall mission of Frontier Ag Inc, and are there plans to expand this community service to other locations? | Are there any partnerships or collaborations with local charities or organizations that Frontier Ag Inc is involved with, and how can viewers support these efforts?</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2751,24 +2763,24 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>View of the skies east of Frontier Ag Inc in Goodland Kansas. A community service from Frontier Ag Inc. https://frontieraginc.com/</t>
+          <t>View of the skies south of Frontier Ag Inc in Quinter Kansas. A community service from Frontier Ag Inc. https://frontieraginc.com/</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2025-12-17T05:50:00Z</t>
+          <t>2026-03-13T19:45:00Z</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=PrqfpZq4ERI</t>
+          <t>https://youtube.com/watch?v=NIGhF4jUja0</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Skyview - South of Frontier Ag Inc - Goodland, KS</t>
+          <t>Skyview - West of Frontier Ag Inc - Quinter, KS</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -2781,7 +2793,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Farmers, Agricultural professionals, or individuals interested in weather conditions</t>
+          <t>Farmers, Agricultural Professionals, or Local Community Members</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2791,7 +2803,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>I'm curious to know if the community service initiative by Frontier Ag Inc has led to any notable improvements in local air quality monitoring, given the proximity to agricultural areas? | Has Frontier Ag Inc considered partnering with local charities or environmental groups to further amplify the impact of their community service efforts in Goodland, KS? | Are there any plans to expand the skyview monitoring to other locations within Kansas, potentially in collaboration with regional conservation organizations?</t>
+          <t>I'm curious to know if Frontier Ag Inc has considered partnering with local charities to use this skyview service for environmental monitoring or conservation efforts? | How does the community service aspect of this skyview initiative align with Frontier Ag Inc's overall corporate social responsibility goals, particularly in terms of supporting local Kansas communities? | Are there any plans to use the data collected from this skyview service to support precision agriculture practices or inform decision-making for sustainable farming methods in the Quinter area?</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2801,24 +2813,24 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>View of the skies south of Frontier Ag Inc in Goodland Kansas. A community service from Frontier Ag Inc. https://frontieraginc.com/</t>
+          <t>View of the skies west of Frontier Ag Inc in Quinter Kansas. A community service from Frontier Ag Inc. https://frontieraginc.com/</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2025-12-17T05:50:00Z</t>
+          <t>2026-03-13T19:45:00Z</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=xU7UDBXiAwA</t>
+          <t>https://youtube.com/watch?v=VbHOKakFTqo</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Skyview - North of Frontier Ag Inc - Goodland, KS</t>
+          <t>Skyview - North of Frontier Ag Inc - Quinter, KS</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2831,7 +2843,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Farmers, Agricultural enthusiasts</t>
+          <t>Local farmer or agriculture enthusiast</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2841,7 +2853,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>I'm curious to know if Frontier Ag Inc has considered partnering with local charities to use this skyview service for environmental monitoring or conservation efforts? | How does the community service aspect of this skyview project align with Frontier Ag Inc's overall corporate social responsibility goals, particularly in the Goodland Kansas area? | Are there any plans to use the footage from this skyview service to support educational initiatives or fundraising campaigns for local charities, such as those focused on agriculture or rural development?</t>
+          <t>I'm curious to know if the community service aspect of this project includes any educational programs for local kids about agriculture and sustainability, perhaps in partnership with a charity? | How does Frontier Ag Inc plan to utilize this skyview service to support local farmers and ranchers, and are there any plans to expand this initiative to other locations? | Are there any opportunities for viewers to get involved and support the community service efforts of Frontier Ag Inc, such as volunteering or donating to a related charity?</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2851,47 +2863,47 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>View of the skies north of Frontier Ag Inc in Goodland Kansas. A community service from Frontier Ag Inc. https://frontieraginc.com/</t>
+          <t>View of the skies north of Frontier Ag Inc in Quinter Kansas. A community service from Frontier Ag Inc. https://frontieraginc.com/</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2025-12-17T05:50:00Z</t>
+          <t>2026-03-13T20:40:00Z</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=70YcImm96ws</t>
+          <t>https://youtube.com/watch?v=Sf7OzR_oVqs</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Skyview - South of Frontier Ag Inc - Quinter, KS</t>
+          <t>How Philanthropy Can Feed Business</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>30</v>
+        <v>89</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Farmers, Agricultural Professionals, or Local Community Members</t>
+          <t>Entrepreneurs, Business Owners, Philanthropists</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Non-Profit, Business</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>I'm curious to know if the community service initiative by Frontier Ag Inc has led to any notable improvements in local weather monitoring or emergency response systems in Quinter, KS? | How does the view from Skyview contribute to the overall mission of Frontier Ag Inc, and are there plans to expand this community service to other locations? | Are there any partnerships or collaborations with local charities or organizations that Frontier Ag Inc is involved with, and how can viewers support these efforts?</t>
+          <t>Wafa, can you share an example of a company that's successfully integrated philanthropy into their business model, and how it's impacted their bottom line? | I'm curious to know more about the role of CSR in driving business growth - are there any specific industries where philanthropy has been a key differentiator? | How do you think businesses can balance the desire to 'do good' with the need to measure ROI on their philanthropic efforts, and what metrics should they be tracking?</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2901,47 +2913,47 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>View of the skies south of Frontier Ag Inc in Quinter Kansas. A community service from Frontier Ag Inc. https://frontieraginc.com/</t>
+          <t>What happens when philanthropy does more than fund programs—and starts helping businesses grow? Wafa Dinaro, Executive ...</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-03-13T19:45:00Z</t>
+          <t>2026-07-21T16:27:04Z</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=NIGhF4jUja0</t>
+          <t>https://youtube.com/watch?v=JtGPVv218_s</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Skyview - West of Frontier Ag Inc - Quinter, KS</t>
+          <t>🔴LIVE: Trading Bot Scalping✅Giving Code Away For FREE✅</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Farmers, Agricultural Professionals, or Local Community Members</t>
+          <t>Individual traders or investors interested in day trading and automated trading bots</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Finance/Trading</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>I'm curious to know if Frontier Ag Inc has considered partnering with local charities to use this skyview service for environmental monitoring or conservation efforts? | How does the community service aspect of this skyview initiative align with Frontier Ag Inc's overall corporate social responsibility goals, particularly in terms of supporting local Kansas communities? | Are there any plans to use the data collected from this skyview service to support precision agriculture practices or inform decision-making for sustainable farming methods in the Quinter area?</t>
+          <t>Curious to know how you handle slippage when scaling up your trading bot, especially during high-volatility moments in the S&amp;P 500 futures | What's your strategy for avoiding overfitting in the bot's code, and are you using any specific backtesting methods to validate its performance? | Have you considered donating a portion of your profits to charity once you reach your $100000 goal, potentially using your platform to raise awareness for a cause?</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2951,47 +2963,47 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>View of the skies west of Frontier Ag Inc in Quinter Kansas. A community service from Frontier Ag Inc. https://frontieraginc.com/</t>
+          <t>I live day trade S&amp;P 500 futures with the goal of reaching $100000 in profit. Sharing my journey in real-time with full transparency ...</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-03-13T19:45:00Z</t>
+          <t>2026-07-21T16:16:16Z</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=VbHOKakFTqo</t>
+          <t>https://youtube.com/watch?v=LwTFHMRd5Jc</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Skyview - North of Frontier Ag Inc - Quinter, KS</t>
+          <t>Giving backshots for the greater good</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Local farmer or agriculture enthusiast</t>
+          <t>Young adults or teenagers interested in gaming or streaming content</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Gaming or Entertainment</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>I'm curious to know if the community service aspect of this project includes any educational programs for local kids about agriculture and sustainability, perhaps in partnership with a charity? | How does Frontier Ag Inc plan to utilize this skyview service to support local farmers and ranchers, and are there any plans to expand this initiative to other locations? | Are there any opportunities for viewers to get involved and support the community service efforts of Frontier Ag Inc, such as volunteering or donating to a related charity?</t>
+          <t>How do you think 'backshots for the greater good' can be applied in a charity setting, particularly for fundraising events? | I'm curious to know if there are any specific strategies for maximizing the impact of backshots in charity work, such as partnering with influencers? | Can you share an example of a successful charity campaign that utilized backshots to raise awareness and drive donations?</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3001,28 +3013,28 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>View of the skies north of Frontier Ag Inc in Quinter Kansas. A community service from Frontier Ag Inc. https://frontieraginc.com/</t>
+          <t>You Should Subscribe for more.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-03-13T20:40:00Z</t>
+          <t>2026-07-21T16:21:59Z</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=Sf7OzR_oVqs</t>
+          <t>https://youtube.com/watch?v=sEYC6fl6UfA</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>How Philanthropy Can Feed Business</t>
+          <t>SEO Charity Summer Edition 2026</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -3031,17 +3043,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Entrepreneurs, Business Owners, Philanthropists</t>
+          <t>Marketing professionals, SEO specialists, and charity supporters</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Non-Profit, Business</t>
+          <t>Digital Marketing/Technology</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Wafa, can you share an example of a company that's successfully integrated philanthropy into their business model, and how it's impacted their bottom line? | I'm curious to know more about the role of CSR in driving business growth - are there any specific industries where philanthropy has been a key differentiator? | How do you think businesses can balance the desire to 'do good' with the need to measure ROI on their philanthropic efforts, and what metrics should they be tracking?</t>
+          <t>How do you think the latest Google algorithm updates will impact charity website rankings, particularly for smaller non-profits with limited SEO resources? | What role do you see technical SEO playing in the charity sector, especially in terms of optimizing donation pages for better conversion rates? | Can you discuss any successful case studies of charities using long-tail keywords to reach specific donor demographics and increase online fundraising efforts?</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3049,49 +3061,39 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>What happens when philanthropy does more than fund programs—and starts helping businesses grow? Wafa Dinaro, Executive ...</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2026-07-21T16:27:04Z</t>
-        </is>
-      </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=JtGPVv218_s</t>
+          <t>https://youtube.com/watch?v=aQZfRuMNc3k</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>🔴LIVE: Trading Bot Scalping✅Giving Code Away For FREE✅</t>
+          <t>Youth Family Camp Morning 2 - Pastor Charity Kalstrup</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>75</v>
+        <v>8</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Individual traders or investors interested in day trading and automated trading bots</t>
+          <t>Family-oriented individuals, particularly those with a Christian background</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Finance/Trading</t>
+          <t>Religion</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Curious to know how you handle slippage when scaling up your trading bot, especially during high-volatility moments in the S&amp;P 500 futures | What's your strategy for avoiding overfitting in the bot's code, and are you using any specific backtesting methods to validate its performance? | Have you considered donating a portion of your profits to charity once you reach your $100000 goal, potentially using your platform to raise awareness for a cause?</t>
+          <t>Pastor Charity, how do you incorporate faith-based discussions into the family camp activities to promote spiritual growth among the youth? | I'm curious to know more about the community outreach programs you've implemented through the family camp, are there any plans to expand these initiatives to other locations? | What role do you think mentorship plays in the family camp setting, and how do you match youth with suitable mentors or role models?</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3099,49 +3101,39 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>I live day trade S&amp;P 500 futures with the goal of reaching $100000 in profit. Sharing my journey in real-time with full transparency ...</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>2026-07-21T16:16:16Z</t>
-        </is>
-      </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=LwTFHMRd5Jc</t>
+          <t>https://youtube.com/watch?v=Q_rsW8Dj5MI</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Giving backshots for the greater good</t>
+          <t>Techno &amp; Bass Music 24/7 🔴 Live Radio | Hard Techno, Bass House, Rave Music</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Young adults or teenagers interested in gaming or streaming content</t>
+          <t>Electronic Dance Music (EDM) enthusiast</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Gaming or Entertainment</t>
+          <t>Music</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>How do you think 'backshots for the greater good' can be applied in a charity setting, particularly for fundraising events? | I'm curious to know if there are any specific strategies for maximizing the impact of backshots in charity work, such as partnering with influencers? | Can you share an example of a successful charity campaign that utilized backshots to raise awareness and drive donations?</t>
+          <t>Loving the energy of this Hard Techno set, what's the story behind the transition from Bass House to Rave Music in your live radio shows? | How do you balance the darker tones of Hard Techno with the more upbeat vibes of Bass House to keep the 24/7 live radio engaging? | Are there any plans to feature emerging artists in the Rave Music scene or collaborations with other DJs to mix things up in future live radio broadcasts?</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3149,30 +3141,20 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>You Should Subscribe for more.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>2026-07-21T16:21:59Z</t>
-        </is>
-      </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=sEYC6fl6UfA</t>
+          <t>https://youtube.com/watch?v=xN0EMHEI2XQ</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SEO Charity Summer Edition 2026</t>
+          <t>WE LOVE RAVE 🟢 24/7 Psytrance Community Radio | Festival Vibes, Trippy Art, High Energy Flow</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -3181,17 +3163,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Marketing professionals, SEO specialists, and charity supporters</t>
+          <t>Raver</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Digital Marketing/Technology</t>
+          <t>Music</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>How do you think the latest Google algorithm updates will impact charity website rankings, particularly for smaller non-profits with limited SEO resources? | What role do you see technical SEO playing in the charity sector, especially in terms of optimizing donation pages for better conversion rates? | Can you discuss any successful case studies of charities using long-tail keywords to reach specific donor demographics and increase online fundraising efforts?</t>
+          <t>Loving the high energy flow so far, how do you curate your 24/7 playlist to keep the psytrance vibes consistent? | What's the story behind the trippy art visuals - are they created in-house or do you collab with external artists? | Are there any plans to feature live DJ sets or interviews with prominent psytrance artists in the RAVE community?</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3201,37 +3183,37 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=aQZfRuMNc3k</t>
+          <t>https://youtube.com/watch?v=uMvUKvmczpU</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Youth Family Camp Morning 2 - Pastor Charity Kalstrup</t>
+          <t>German TECHNO BUNKER 24/7 Deep Dark &amp; Hard Techno Underground Live Stream Rave</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>8</v>
+        <v>97</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Family-oriented individuals, particularly those with a Christian background</t>
+          <t>Electronic Dance Music (EDM) enthusiast</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Religion</t>
+          <t>Music</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pastor Charity, how do you incorporate faith-based discussions into the family camp activities to promote spiritual growth among the youth? | I'm curious to know more about the community outreach programs you've implemented through the family camp, are there any plans to expand these initiatives to other locations? | What role do you think mentorship plays in the family camp setting, and how do you match youth with suitable mentors or role models?</t>
+          <t>Loving the dark techno vibes, what's the story behind the curated tracklist for this 24/7 stream? | How do you balance the energy between deep and hard techno to keep the rave going non-stop? | Are there any plans to feature underground techno artists from Berlin in upcoming streams?</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3241,18 +3223,18 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=Q_rsW8Dj5MI</t>
+          <t>https://youtube.com/watch?v=hSVSWFF1M6Q</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Techno &amp; Bass Music 24/7 🔴 Live Radio | Hard Techno, Bass House, Rave Music</t>
+          <t>NON STOP TECHNO RAVE RADIO 24/7 MIX</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>150</v>
+        <v>96</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -3271,7 +3253,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Loving the energy of this Hard Techno set, what's the story behind the transition from Bass House to Rave Music in your live radio shows? | How do you balance the darker tones of Hard Techno with the more upbeat vibes of Bass House to keep the 24/7 live radio engaging? | Are there any plans to feature emerging artists in the Rave Music scene or collaborations with other DJs to mix things up in future live radio broadcasts?</t>
+          <t>Loving the energy of this 24/7 mix, what's the secret to keeping the vibe consistent across different tracks and DJs? | Can we get a shoutout to the classic techno rave tracks that never get old, like those from Jeff Mills or Richie Hawtin? | How do you balance the mix between newer, experimental techno and the old-school rave anthems that get the crowd moving?</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3281,18 +3263,18 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=xN0EMHEI2XQ</t>
+          <t>https://youtube.com/watch?v=34H1XIjnfKM</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>WE LOVE RAVE 🟢 24/7 Psytrance Community Radio | Festival Vibes, Trippy Art, High Energy Flow</t>
+          <t>TECHNO RADIO 💣 NON STOP RAVE</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -3311,7 +3293,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Loving the high energy flow so far, how do you curate your 24/7 playlist to keep the psytrance vibes consistent? | What's the story behind the trippy art visuals - are they created in-house or do you collab with external artists? | Are there any plans to feature live DJ sets or interviews with prominent psytrance artists in the RAVE community?</t>
+          <t>Loving the energy so far, what's the story behind the transition from techno to rave in the setlist? | How do you balance the tempo and beat to keep the non-stop rave vibe going without overwhelming the listeners? | Can you share some insights on how you curate your tracks to create that perfect rave atmosphere, like the one you're building up to now?</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3321,18 +3303,18 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=uMvUKvmczpU</t>
+          <t>https://youtube.com/watch?v=hXsca_iyieI</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>German TECHNO BUNKER 24/7 Deep Dark &amp; Hard Techno Underground Live Stream Rave</t>
+          <t>24/7 🎛 Techno Club Radio · Rave, Warehouse &amp; Hypnotic (Corgi Records)</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -3351,7 +3333,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Loving the dark techno vibes, what's the story behind the curated tracklist for this 24/7 stream? | How do you balance the energy between deep and hard techno to keep the rave going non-stop? | Are there any plans to feature underground techno artists from Berlin in upcoming streams?</t>
+          <t>Loving the hypnotic vibes so far, how do you balance the energy between warehouse and rave tracks in your sets? | What's the story behind featuring Corgi Records in this livestream, are they a new favorite label of yours? | The transitions between tracks have been seamless, can you walk us through your process for creating a cohesive flow in a 24/7 techno club radio setting?</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3361,18 +3343,18 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=hSVSWFF1M6Q</t>
+          <t>https://youtube.com/watch?v=RtLSe0syHVI</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>NON STOP TECHNO RAVE RADIO 24/7 MIX</t>
+          <t>HARD RAVE TECHNO RADIO NON STOP 24/7 LIVE</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -3381,7 +3363,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Electronic Dance Music (EDM) enthusiast</t>
+          <t>Raver</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3391,7 +3373,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Loving the energy of this 24/7 mix, what's the secret to keeping the vibe consistent across different tracks and DJs? | Can we get a shoutout to the classic techno rave tracks that never get old, like those from Jeff Mills or Richie Hawtin? | How do you balance the mix between newer, experimental techno and the old-school rave anthems that get the crowd moving?</t>
+          <t>Loving the energy of this set, what's the story behind the transition from hardcore to rave in the 90s that influenced your track selection? | Can you dive deeper into the production techniques used to create that iconic 'hoover' sound in classic rave tracks? | How do you balance the nostalgic vibe of old-school rave with modern production quality and techniques in your mixes?</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3401,18 +3383,18 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=34H1XIjnfKM</t>
+          <t>https://youtube.com/watch?v=AswR2woOGj0</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TECHNO RADIO 💣 NON STOP RAVE</t>
+          <t>🔴 LIVE 24/7 Goa Psytrance Radio 2026 | Ravecore Nation | Psychedelic Trance Stream</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -3431,7 +3413,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Loving the energy so far, what's the story behind the transition from techno to rave in the setlist? | How do you balance the tempo and beat to keep the non-stop rave vibe going without overwhelming the listeners? | Can you share some insights on how you curate your tracks to create that perfect rave atmosphere, like the one you're building up to now?</t>
+          <t>Loving the vibe of this stream, what's the story behind the Ravecore Nation name and how did you curate this epic playlist? | How do you balance the energy between classic psytrance tracks and newer releases in your 24/7 stream to keep the Ravecore Nation engaged? | Are there any plans to feature live DJ sets or collaborations with other psytrance artists in the stream, that would take the Rave to the next level?</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3441,14 +3423,14 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=hXsca_iyieI</t>
+          <t>https://youtube.com/watch?v=_py4DTR8Gn4</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>24/7 🎛 Techno Club Radio · Rave, Warehouse &amp; Hypnotic (Corgi Records)</t>
+          <t>🔴 LIVE 24/7 Hardcore Uptempo Gabber Radio 2026 | RaveCore Nation | Hard Techno Stream</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3461,7 +3443,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Electronic Dance Music (EDM) enthusiast</t>
+          <t>Raver</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3471,7 +3453,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Loving the hypnotic vibes so far, how do you balance the energy between warehouse and rave tracks in your sets? | What's the story behind featuring Corgi Records in this livestream, are they a new favorite label of yours? | The transitions between tracks have been seamless, can you walk us through your process for creating a cohesive flow in a 24/7 techno club radio setting?</t>
+          <t>Loving the energy on this stream, what's the story behind the RaveCore Nation name and how did it become synonymous with the hardcore uptempo scene? | Can we get a shoutout to the pioneers of gabber like Rotterdam Terror Corps and Miss K8, their influence on the genre is still felt today | How do you curate the tracklist for a 24/7 stream like this, do you take requests from the chat or is it all pre-programmed?</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3481,14 +3463,14 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=RtLSe0syHVI</t>
+          <t>https://youtube.com/watch?v=XeLnMn_WHmo</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>HARD RAVE TECHNO RADIO NON STOP 24/7 LIVE</t>
+          <t>🔴 LIVE 24/7 Goa Psytrance #2 Radio 2026 | Ravecore Nation | Psychedelic Trance Stream</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -3511,7 +3493,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Loving the energy of this set, what's the story behind the transition from hardcore to rave in the 90s that influenced your track selection? | Can you dive deeper into the production techniques used to create that iconic 'hoover' sound in classic rave tracks? | How do you balance the nostalgic vibe of old-school rave with modern production quality and techniques in your mixes?</t>
+          <t>Loving the vibe on this stream, what's the story behind the Ravecore Nation name and how did it become a hub for psytrance fans? | Curious to know if you'll be featuring any artists from the old school Goa trance scene, like Hallucinogen or Ott, in upcoming sets? | How do you balance the energy between darker, more industrial psytrance tracks and the more uplifting, melodic ones to keep the stream engaging 24/7?</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3521,14 +3503,14 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=AswR2woOGj0</t>
+          <t>https://youtube.com/watch?v=RW2BiYKDcDY</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>🔴 LIVE 24/7 Goa Psytrance Radio 2026 | Ravecore Nation | Psychedelic Trance Stream</t>
+          <t>Music Mix 2026 🔊 Party Club Dance 2026 🔥 Festival Party Energy MEGAMIX Nonstop</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3541,17 +3523,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Raver</t>
+          <t>party-goer</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Music</t>
+          <t>entertainment</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Loving the vibe of this stream, what's the story behind the Ravecore Nation name and how did you curate this epic playlist? | How do you balance the energy between classic psytrance tracks and newer releases in your 24/7 stream to keep the Ravecore Nation engaged? | Are there any plans to feature live DJ sets or collaborations with other psytrance artists in the stream, that would take the Rave to the next level?</t>
+          <t>Loving the energy of this MEGAMIX, how do you balance the transition between EDM and hip-hop tracks to keep the party vibe going? | What's the inspiration behind including nonstop festival party energy in this mix, are you drawing from specific festivals like Tomorrowland or Ultra? | The drop at 10 minutes in is insane, can you share your process for selecting and mixing those high-energy drops to get the crowd moving?</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3561,18 +3543,18 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=_py4DTR8Gn4</t>
+          <t>https://youtube.com/watch?v=bIYQRlWlFNE</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>🔴 LIVE 24/7 Hardcore Uptempo Gabber Radio 2026 | RaveCore Nation | Hard Techno Stream</t>
+          <t>Art of Minimal Techno 'Deep' Radio | Melodic Techno &amp; Progressive House 24/7 Live by Trippy Code</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -3581,7 +3563,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Raver</t>
+          <t>Electronic Dance Music (EDM) enthusiast</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3591,7 +3573,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Loving the energy on this stream, what's the story behind the RaveCore Nation name and how did it become synonymous with the hardcore uptempo scene? | Can we get a shoutout to the pioneers of gabber like Rotterdam Terror Corps and Miss K8, their influence on the genre is still felt today | How do you curate the tracklist for a 24/7 stream like this, do you take requests from the chat or is it all pre-programmed?</t>
+          <t>Loving the melodic techno vibes, Trippy Code - what's the story behind your track selection process for this 24/7 live set? | How do you balance the energy between melodic techno and progressive house to keep the flow going for a 24-hour stream? | Are you using any specific audio processing techniques to create that deep, immersive sound in your mixes, or is it all about the track choices?</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3601,18 +3583,18 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=XeLnMn_WHmo</t>
+          <t>https://youtube.com/watch?v=UYOb37KRFqk</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>🔴 LIVE 24/7 Goa Psytrance #2 Radio 2026 | Ravecore Nation | Psychedelic Trance Stream</t>
+          <t>MINIMAL TECHNO PARTY RADIO by TRIPPY CAT MUSIC</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -3621,7 +3603,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Raver</t>
+          <t>Electronic Dance Music Fans</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3631,7 +3613,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Loving the vibe on this stream, what's the story behind the Ravecore Nation name and how did it become a hub for psytrance fans? | Curious to know if you'll be featuring any artists from the old school Goa trance scene, like Hallucinogen or Ott, in upcoming sets? | How do you balance the energy between darker, more industrial psytrance tracks and the more uplifting, melodic ones to keep the stream engaging 24/7?</t>
+          <t>Trippy Cat, what inspired the tracklist for this Minimal Techno party, any new artists we should be looking out for? | Loving the vibe so far, how do you balance the energy between deeper cuts and more upbeat tracks in a set like this? | Curious about the production side, are you using any specific plugins or effects to achieve that signature Trippy Cat sound in your Minimal Techno sets?</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -3641,18 +3623,18 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=RW2BiYKDcDY</t>
+          <t>https://youtube.com/watch?v=TI2drL9AH5s</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Music Mix 2026 🔊 Party Club Dance 2026 🔥 Festival Party Energy MEGAMIX Nonstop</t>
+          <t>Dark Minimal Techno NON STOP Radio Mix</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -3661,17 +3643,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>party-goer</t>
+          <t>Electronic Dance Music (EDM) enthusiast</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>entertainment</t>
+          <t>Music</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Loving the energy of this MEGAMIX, how do you balance the transition between EDM and hip-hop tracks to keep the party vibe going? | What's the inspiration behind including nonstop festival party energy in this mix, are you drawing from specific festivals like Tomorrowland or Ultra? | The drop at 10 minutes in is insane, can you share your process for selecting and mixing those high-energy drops to get the crowd moving?</t>
+          <t>Loving the transition into this Chris Liebing track, how do you curate your sets to maintain energy throughout a non-stop mix? | The use of industrial samples in these dark minimal techno tracks is really adding to the atmosphere, are there any specific artists or labels that inspire your selection? | I've noticed a lot of repetition in the kick drum patterns, do you find that this helps to hypnotize the listener or is it more about creating a sense of tension and release?</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3681,18 +3663,18 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=bIYQRlWlFNE</t>
+          <t>https://youtube.com/watch?v=-vH9ZvAySi8</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Art of Minimal Techno 'Deep' Radio | Melodic Techno &amp; Progressive House 24/7 Live by Trippy Code</t>
+          <t>Tomorrowland 2026 - David Guetta &amp; Alesso | EPIC Mainstage Live Set 🔥 | The ULTIMATE Festival Mix</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -3701,7 +3683,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Electronic Dance Music (EDM) enthusiast</t>
+          <t>Electronic Dance Music (EDM) fans</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3711,7 +3693,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Loving the melodic techno vibes, Trippy Code - what's the story behind your track selection process for this 24/7 live set? | How do you balance the energy between melodic techno and progressive house to keep the flow going for a 24-hour stream? | Are you using any specific audio processing techniques to create that deep, immersive sound in your mixes, or is it all about the track choices?</t>
+          <t>Loving the energy so far, how do you think David Guetta's recent collaboration with Bebe Rexha will influence his setlist tonight? | Alesso's progressive house style is gonna pair perfectly with the mainstage production, do you think we'll see any surprises like a Swedish House Mafia reunion? | The ULTIMATE Festival Mix always brings the heat, curious to see if they'll drop any of their unreleased IDs like Guetta's rumored track with Morten</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -3721,14 +3703,14 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=UYOb37KRFqk</t>
+          <t>https://youtube.com/watch?v=lbyuS8XdD0g</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MINIMAL TECHNO PARTY RADIO by TRIPPY CAT MUSIC</t>
+          <t>Dark Minimal Techno Trip Live Radio 24/7 mixed by RTTWLR</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -3741,7 +3723,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Electronic Dance Music Fans</t>
+          <t>Electronic Dance Music (EDM) enthusiast</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3751,7 +3733,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Trippy Cat, what inspired the tracklist for this Minimal Techno party, any new artists we should be looking out for? | Loving the vibe so far, how do you balance the energy between deeper cuts and more upbeat tracks in a set like this? | Curious about the production side, are you using any specific plugins or effects to achieve that signature Trippy Cat sound in your Minimal Techno sets?</t>
+          <t>Loving the transition into this set, RTTWLR - what's the story behind the track selection for this particular mix? | Noticed a nice blend of old-school and modern dark minimal techno vibes, are there any upcoming artists or labels that you're excited to feature in future sets? | The way you're weaving in those haunting synths is giving me major rave flashbacks - can you share any favorite rave memories or what inspires your mixing style?</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -3761,14 +3743,14 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=TI2drL9AH5s</t>
+          <t>https://youtube.com/watch?v=FOsRAs__6PM</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Dark Minimal Techno NON STOP Radio Mix</t>
+          <t>Minimal Techno Radio Non Stop 24/7</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3781,7 +3763,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Electronic Dance Music (EDM) enthusiast</t>
+          <t>Electronic Music Fan</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3791,7 +3773,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Loving the transition into this Chris Liebing track, how do you curate your sets to maintain energy throughout a non-stop mix? | The use of industrial samples in these dark minimal techno tracks is really adding to the atmosphere, are there any specific artists or labels that inspire your selection? | I've noticed a lot of repetition in the kick drum patterns, do you find that this helps to hypnotize the listener or is it more about creating a sense of tension and release?</t>
+          <t>Loving the vibe, what's the secret to keeping a 24/7 radio stream engaging, do you have a set rotation or is it all live mixes? | How do you balance the energy between minimal techno tracks to keep the flow going, any favorite artists or labels that always bring the heat? | Curious about the tech side, what software or platform are you using to stream non-stop, is it a custom setup or something like Icecast or SHOUTcast?</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -3801,14 +3783,14 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=-vH9ZvAySi8</t>
+          <t>https://youtube.com/watch?v=oOcUoXipLDg</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Tomorrowland 2026 - David Guetta &amp; Alesso | EPIC Mainstage Live Set 🔥 | The ULTIMATE Festival Mix</t>
+          <t>RELIVE Mainstage - Tomorrowland 2026 LIVE</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -3831,7 +3813,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Loving the energy so far, how do you think David Guetta's recent collaboration with Bebe Rexha will influence his setlist tonight? | Alesso's progressive house style is gonna pair perfectly with the mainstage production, do you think we'll see any surprises like a Swedish House Mafia reunion? | The ULTIMATE Festival Mix always brings the heat, curious to see if they'll drop any of their unreleased IDs like Guetta's rumored track with Morten</t>
+          <t>Loving the stage design this year, how do the production team decide on the theme and layout for each Mainstage performance? | What's the story behind the new LED wall setup, is it an upgrade from last year's model? | Curious to know if the live streaming tech has improved for better audio sync, noticed some delays in previous years</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3841,18 +3823,18 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=lbyuS8XdD0g</t>
+          <t>https://youtube.com/watch?v=CVHFv2VOIBc</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Dark Minimal Techno Trip Live Radio 24/7 mixed by RTTWLR</t>
+          <t>RELIVE Freedom Stage - Tomorrowland 2026 LIVE</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -3871,7 +3853,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Loving the transition into this set, RTTWLR - what's the story behind the track selection for this particular mix? | Noticed a nice blend of old-school and modern dark minimal techno vibes, are there any upcoming artists or labels that you're excited to feature in future sets? | The way you're weaving in those haunting synths is giving me major rave flashbacks - can you share any favorite rave memories or what inspires your mixing style?</t>
+          <t>Loving the stage design this year, how does the production team decide on the theme and aesthetic for Freedom Stage? | What's the story behind the LED mapping on the stage, is it all pre-programmed or are there any live elements controlled by the VJs? | Curious to know more about the audio setup, are they using a similar L-Acoustics system as previous years or have they upgraded to something new?</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3881,18 +3863,18 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=FOsRAs__6PM</t>
+          <t>https://youtube.com/watch?v=SaWV3uDOf8Q</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Minimal Techno Radio Non Stop 24/7</t>
+          <t>Answering YOUR questions about the charity - Charity Checkup nr 1160</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -3901,17 +3883,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Electronic Music Fan</t>
+          <t>Donor/Supporter</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Music</t>
+          <t>Non-profit</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Loving the vibe, what's the secret to keeping a 24/7 radio stream engaging, do you have a set rotation or is it all live mixes? | How do you balance the energy between minimal techno tracks to keep the flow going, any favorite artists or labels that always bring the heat? | Curious about the tech side, what software or platform are you using to stream non-stop, is it a custom setup or something like Icecast or SHOUTcast?</t>
+          <t>What's the current process for addressing donor concerns about transparency in charity operations, and how does Charity Checkup ensure accountability? | Can you discuss any recent updates to the charity's grant-making strategy, particularly in regards to supporting local community projects? | How does Charity Checkup handle situations where a charity's goals align with the organization's mission, but their methods or outcomes are questionable?</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3921,18 +3903,18 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=oOcUoXipLDg</t>
+          <t>https://youtube.com/watch?v=LR93_N7IDT8</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>RELIVE Mainstage - Tomorrowland 2026 LIVE</t>
+          <t>Game Safe Charity Stream!</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -3941,17 +3923,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Electronic Dance Music (EDM) fans</t>
+          <t>Gamers and philanthropists</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Music</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Loving the stage design this year, how do the production team decide on the theme and layout for each Mainstage performance? | What's the story behind the new LED wall setup, is it an upgrade from last year's model? | Curious to know if the live streaming tech has improved for better audio sync, noticed some delays in previous years</t>
+          <t>How will the funds raised from this stream be allocated to support gaming-related charities, and are there any specific initiatives you're looking to back? | I'd love to know more about the charity partners you're working with - are they focused on accessibility in gaming, or perhaps mental health support for gamers? | Will there be any opportunities for viewers to get involved in the charity efforts beyond donations, such as volunteer sign-ups or community drives?</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3961,18 +3943,18 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=CVHFv2VOIBc</t>
+          <t>https://youtube.com/watch?v=-QwUSVTmBTc</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>RELIVE Freedom Stage - Tomorrowland 2026 LIVE</t>
+          <t>ANNA 92 NEW STUDENT CHARITY MEMBER</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3981,17 +3963,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Electronic Dance Music (EDM) enthusiast</t>
+          <t>Philanthropist</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Music</t>
+          <t>Non-Profit</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Loving the stage design this year, how does the production team decide on the theme and aesthetic for Freedom Stage? | What's the story behind the LED mapping on the stage, is it all pre-programmed or are there any live elements controlled by the VJs? | Curious to know more about the audio setup, are they using a similar L-Acoustics system as previous years or have they upgraded to something new?</t>
+          <t>What kind of community outreach programs will ANNA 92 be implementing as part of their new student charity membership? | How will the charity membership impact the student experience, specifically in terms of volunteer opportunities or fundraising events? | Are there plans to collaborate with existing charities or will ANNA 92 be establishing their own charitable initiatives?</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4001,18 +3983,18 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=SaWV3uDOf8Q</t>
+          <t>https://youtube.com/watch?v=JwpqPLPg_Hs</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Answering YOUR questions about the charity - Charity Checkup nr 1160</t>
+          <t>Will Jordan be able to make it to the charity game?</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -4021,17 +4003,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Donor/Supporter</t>
+          <t>Philanthropist</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Non-profit</t>
+          <t>Entertainment</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>What's the current process for addressing donor concerns about transparency in charity operations, and how does Charity Checkup ensure accountability? | Can you discuss any recent updates to the charity's grant-making strategy, particularly in regards to supporting local community projects? | How does Charity Checkup handle situations where a charity's goals align with the organization's mission, but their methods or outcomes are questionable?</t>
+          <t>Does Jordan's potential absence from the charity game impact the fundraising strategy, or are there backup plans in place? | How will the charity game's organizers ensure a smooth event if Jordan can't make it, considering his role in promoting the event? | Are there any contingency plans for replacing Jordan or adjusting the game format to still meet the charity's fundraising goals?</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4041,18 +4023,18 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=LR93_N7IDT8</t>
+          <t>https://youtube.com/watch?v=yDNPh-TA52k</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Game Safe Charity Stream!</t>
+          <t>Will Jordan be able to make it to the charity game?</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -4061,17 +4043,17 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Gamers and philanthropists</t>
+          <t>Philanthropist</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Gaming</t>
+          <t>Entertainment</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>How will the funds raised from this stream be allocated to support gaming-related charities, and are there any specific initiatives you're looking to back? | I'd love to know more about the charity partners you're working with - are they focused on accessibility in gaming, or perhaps mental health support for gamers? | Will there be any opportunities for viewers to get involved in the charity efforts beyond donations, such as volunteer sign-ups or community drives?</t>
+          <t>Do we know what Jordan's current injury status is and if it'll impact his participation in the charity game? | How will Jordan's potential absence affect the team's strategy and fundraising goals for the charity event? | Are there any backup plans or alternative players lined up in case Jordan can't make it to the charity game?</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4081,14 +4063,14 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=-QwUSVTmBTc</t>
+          <t>https://youtube.com/watch?v=NDSZWiU6K8U</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ANNA 92 NEW STUDENT CHARITY MEMBER</t>
+          <t>Return to the Danger Room: A Broken Level 20 Charity Brawl</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -4101,17 +4083,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Philanthropist</t>
+          <t>Gamers and charity supporters</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Non-Profit</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>What kind of community outreach programs will ANNA 92 be implementing as part of their new student charity membership? | How will the charity membership impact the student experience, specifically in terms of volunteer opportunities or fundraising events? | Are there plans to collaborate with existing charities or will ANNA 92 be establishing their own charitable initiatives?</t>
+          <t>How do you plan to address the issue of team composition imbalance in the Level 20 Charity Brawl, considering the diverse range of characters and playstyles? | What strategies will you employ to counter the 'stall and hide' tactic that often emerges in high-stakes charity brawls, and how can viewers support the charity through donations or sharing the stream? | Will the charity brawl feature any special 'power play' rules or incentives to encourage risk-taking and aggressive gameplay, and if so, how will these be announced during the stream?</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4121,18 +4103,18 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=JwpqPLPg_Hs</t>
+          <t>https://youtube.com/watch?v=9_hqkUiPDmg</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Will Jordan be able to make it to the charity game?</t>
+          <t>TV WEST LIVE: SISIIMUKA 23.07.2026 NA SISTER CHARITY | LUCKY KASANGAKI</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -4146,12 +4128,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Entertainment</t>
+          <t>Non-Profit</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Does Jordan's potential absence from the charity game impact the fundraising strategy, or are there backup plans in place? | How will the charity game's organizers ensure a smooth event if Jordan can't make it, considering his role in promoting the event? | Are there any contingency plans for replacing Jordan or adjusting the game format to still meet the charity's fundraising goals?</t>
+          <t>Lucky Kasangaki, can you share some insights on how Sister Charity's initiatives have impacted local communities, particularly in terms of education and healthcare? | I'd love to know more about the Sisiimuka event's objectives - are there any specific fundraising goals or awareness campaigns that Sister Charity is focusing on this year? | How does Sister Charity plan to leverage the Sisiimuka event to build partnerships with other organizations or stakeholders, potentially amplifying their charitable efforts?</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4161,18 +4143,18 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=yDNPh-TA52k</t>
+          <t>https://youtube.com/watch?v=7QyZOunC2Ck</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Will Jordan be able to make it to the charity game?</t>
+          <t>🟢BEATING 430 LEVELS IN ONE STREAM.🟢 // GD Charity Event 2026 //</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -4181,17 +4163,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Philanthropist</t>
+          <t>Gamers and charity supporters</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Entertainment</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Do we know what Jordan's current injury status is and if it'll impact his participation in the charity game? | How will Jordan's potential absence affect the team's strategy and fundraising goals for the charity event? | Are there any backup plans or alternative players lined up in case Jordan can't make it to the charity game?</t>
+          <t>What's the strategy behind tackling the infamous level 321, and how do you plan to overcome its notorious difficulty spike? | Curious to know, are there any specific charity initiatives or organizations that will be benefiting from this GD Charity Event, and how can viewers contribute? | How do you handle mental fatigue during long streams like this, especially when encountering tough levels like 275-300, and what keeps you motivated to push through?</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4201,14 +4183,14 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=NDSZWiU6K8U</t>
+          <t>https://youtube.com/watch?v=jz0F7BjrTR0</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Return to the Danger Room: A Broken Level 20 Charity Brawl</t>
+          <t>Super Zeldathon - 7 Days of Zelda in Support of St. Jude - donate.zeldathon.com</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -4221,7 +4203,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Gamers and charity supporters</t>
+          <t>Gamers and fans of the Zelda series</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4231,7 +4213,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>How do you plan to address the issue of team composition imbalance in the Level 20 Charity Brawl, considering the diverse range of characters and playstyles? | What strategies will you employ to counter the 'stall and hide' tactic that often emerges in high-stakes charity brawls, and how can viewers support the charity through donations or sharing the stream? | Will the charity brawl feature any special 'power play' rules or incentives to encourage risk-taking and aggressive gameplay, and if so, how will these be announced during the stream?</t>
+          <t>How's the team planning to handle the Water Temple in Ocarina of Time, considering it's one of the most challenging parts of the game? | I've donated to St. Jude through donate.zeldathon.com - what's the current donation tally and are there any stretch goals for the remaining days? | Will you be doing any specific challenges or incentives during the Majora's Mask segment, like a 'mask collection' goal to encourage more donations?</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -4241,14 +4223,14 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=9_hqkUiPDmg</t>
+          <t>https://youtube.com/watch?v=lG_bumnfgaw</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>TV WEST LIVE: SISIIMUKA 23.07.2026 NA SISTER CHARITY | LUCKY KASANGAKI</t>
+          <t>CAC Fundraising Livestream</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -4271,24 +4253,24 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lucky Kasangaki, can you share some insights on how Sister Charity's initiatives have impacted local communities, particularly in terms of education and healthcare? | I'd love to know more about the Sisiimuka event's objectives - are there any specific fundraising goals or awareness campaigns that Sister Charity is focusing on this year? | How does Sister Charity plan to leverage the Sisiimuka event to build partnerships with other organizations or stakeholders, potentially amplifying their charitable efforts?</t>
+          <t>What strategies have been most effective in reducing donor acquisition costs for CAC fundraising campaigns, particularly for smaller charities? | Can you discuss the role of social media in CAC fundraising, specifically how to leverage platforms like YouTube to increase donations and engagement? | How do you recommend charities balance the need for immediate funding with long-term donor relationship building in their CAC fundraising efforts?</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>YouTube</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>https://youtube.com/watch?v=7QyZOunC2Ck</t>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>CAC Fundraising Livestream  YouTube https://www.youtube.com › watch</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>🟢BEATING 430 LEVELS IN ONE STREAM.🟢 // GD Charity Event 2026 //</t>
+          <t>SARAH 48 STUDENT CHARITY MEMBER</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -4301,17 +4283,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Gamers and charity supporters</t>
+          <t>Philanthropist</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Gaming</t>
+          <t>Non-Profit</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>What's the strategy behind tackling the infamous level 321, and how do you plan to overcome its notorious difficulty spike? | Curious to know, are there any specific charity initiatives or organizations that will be benefiting from this GD Charity Event, and how can viewers contribute? | How do you handle mental fatigue during long streams like this, especially when encountering tough levels like 275-300, and what keeps you motivated to push through?</t>
+          <t>What inspired you to join the SARAH 48 student charity, and how do you think your experience will impact your future endeavors? | Can you share any specific challenges you've faced as a charity member, and how you overcame them? | How do you think the skills you're developing through SARAH 48 will translate to a career in nonprofit or philanthropy?</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -4321,14 +4303,14 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=jz0F7BjrTR0</t>
+          <t>https://youtube.com/watch?v=XITaRPcQuKI</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Super Zeldathon - 7 Days of Zelda in Support of St. Jude - donate.zeldathon.com</t>
+          <t>JEVZ 26 CHARITY MEMBER</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4341,17 +4323,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Gamers and fans of the Zelda series</t>
+          <t>Philanthropist</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Gaming</t>
+          <t>Non-Profit</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>How's the team planning to handle the Water Temple in Ocarina of Time, considering it's one of the most challenging parts of the game? | I've donated to St. Jude through donate.zeldathon.com - what's the current donation tally and are there any stretch goals for the remaining days? | Will you be doing any specific challenges or incentives during the Majora's Mask segment, like a 'mask collection' goal to encourage more donations?</t>
+          <t>How does JEVZ 26 plan to utilize member contributions to support specific charity initiatives, and what's the expected impact on the community? | Can you share some insights on the membership structure and benefits for JEVZ 26 charity members, particularly in terms of volunteer opportunities? | What kind of transparency and reporting can JEVZ 26 charity members expect in terms of fund allocation and project outcomes?</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -4361,14 +4343,14 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=lG_bumnfgaw</t>
+          <t>https://youtube.com/watch?v=aT1zY7xNHPQ</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CAC Fundraising Livestream</t>
+          <t>TRISHA 20: CHARITY MEMBER</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -4391,28 +4373,28 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>What strategies have been most effective in reducing donor acquisition costs for CAC fundraising campaigns, particularly for smaller charities? | Can you discuss the role of social media in CAC fundraising, specifically how to leverage platforms like YouTube to increase donations and engagement? | How do you recommend charities balance the need for immediate funding with long-term donor relationship building in their CAC fundraising efforts?</t>
+          <t>What specific initiatives has Trisha 20 implemented to increase charity member engagement and retention? | Can you discuss how Trisha 20's charity membership model addresses issues of diversity and inclusion? | How does Trisha 20 measure the impact of its charity membership program on the communities it serves?</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>CAC Fundraising Livestream  YouTube https://www.youtube.com › watch</t>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=Dfn_ZpFuy2M</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SARAH 48 STUDENT CHARITY MEMBER</t>
+          <t>🔴 PLS DONATE LIVE | GIVING ROBUX TO VIEWERS</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -4421,17 +4403,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Philanthropist</t>
+          <t>Young gamers</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Non-Profit</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>What inspired you to join the SARAH 48 student charity, and how do you think your experience will impact your future endeavors? | Can you share any specific challenges you've faced as a charity member, and how you overcame them? | How do you think the skills you're developing through SARAH 48 will translate to a career in nonprofit or philanthropy?</t>
+          <t>How will the Robux donations be distributed among viewers, will it be random or based on engagement? | Are there any specific charity initiatives or causes that the stream is supporting with these donations? | Will the stream be tracking the total amount of Robux donated and setting a goal for the charity, like a fundraising target?</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -4441,14 +4423,14 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=XITaRPcQuKI</t>
+          <t>https://youtube.com/watch?v=r2ZdIw01xWY</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>JEVZ 26 CHARITY MEMBER</t>
+          <t>Big Heart</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -4471,7 +4453,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>How does JEVZ 26 plan to utilize member contributions to support specific charity initiatives, and what's the expected impact on the community? | Can you share some insights on the membership structure and benefits for JEVZ 26 charity members, particularly in terms of volunteer opportunities? | What kind of transparency and reporting can JEVZ 26 charity members expect in terms of fund allocation and project outcomes?</t>
+          <t>How can we ensure that charitable initiatives like Big Heart are sustainable in the long term, beyond initial funding or donations? | I'd love to hear more about the specific strategies Big Heart is using to measure the impact of their charitable efforts, are they using any particular metrics or benchmarks? | Are there any plans for Big Heart to partner with other organizations or charities to amplify their reach and support a wider range of causes?</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -4481,14 +4463,14 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=aT1zY7xNHPQ</t>
+          <t>https://youtube.com/watch?v=iEHU8Kiybdo</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>TRISHA 20: CHARITY MEMBER</t>
+          <t>Rose#1 New Student Charity Member</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4506,12 +4488,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Non-Profit</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>What specific initiatives has Trisha 20 implemented to increase charity member engagement and retention? | Can you discuss how Trisha 20's charity membership model addresses issues of diversity and inclusion? | How does Trisha 20 measure the impact of its charity membership program on the communities it serves?</t>
+          <t>What's the average financial burden that these students are facing, and how will the donated funds be allocated to support their college expenses? | Are there any specific college-related costs that this charity is focusing on, such as tuition, textbooks, or living expenses? | How will the charity ensure transparency and accountability in the distribution of funds to the students, and are there any plans for long-term support or mentorship programs?</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -4519,20 +4501,30 @@
           <t>YouTube</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>this channel for charity student to helping they're financial in collenge pls help them thank you PAYPAL :charityphil26@gmail.com.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>2026-07-29T05:01:03Z</t>
+        </is>
+      </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=Dfn_ZpFuy2M</t>
+          <t>https://youtube.com/watch?v=Vuu7R_wNNgQ</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>🔴 PLS DONATE LIVE | GIVING ROBUX TO VIEWERS</t>
+          <t>NEW DONATION GAME?! I&amp;#39;M BACK DONATING ROBUX TO LIVE VIEWERS 🔴 LIVE 🔴</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -4541,7 +4533,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Young gamers</t>
+          <t>Young adults and teenagers</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -4551,7 +4543,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>How will the Robux donations be distributed among viewers, will it be random or based on engagement? | Are there any specific charity initiatives or causes that the stream is supporting with these donations? | Will the stream be tracking the total amount of Robux donated and setting a goal for the charity, like a fundraising target?</t>
+          <t>How do you decide who to donate Robux to during the livestream, is it completely random or are there specific criteria? | I've noticed some viewers are sharing their Robux wishlists in the Discord server, do you take those into consideration when donating? | Are you planning on doing any charity fundraisers or collaborations with other streamers in the future, perhaps for a specific Robux-driven charity event?</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -4559,16 +4551,26 @@
           <t>YouTube</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>JOIN UP AND GET A LAUGH OR TWO :D Discord server: https://discord.gg/UDxuJfESc Game link: ...</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>2026-07-29T05:38:34Z</t>
+        </is>
+      </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=r2ZdIw01xWY</t>
+          <t>https://youtube.com/watch?v=APismqX3YlI</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Big Heart</t>
+          <t>Trying to get a $5 Donation or any Donation</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4581,7 +4583,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Philanthropist</t>
+          <t>Donor</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -4591,7 +4593,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>How can we ensure that charitable initiatives like Big Heart are sustainable in the long term, beyond initial funding or donations? | I'd love to hear more about the specific strategies Big Heart is using to measure the impact of their charitable efforts, are they using any particular metrics or benchmarks? | Are there any plans for Big Heart to partner with other organizations or charities to amplify their reach and support a wider range of causes?</t>
+          <t>I'm curious, have you considered partnering with a charity to amplify the impact of these $5 donations, perhaps a local food bank or education initiative? | For those donating via Venmo, will there be any public acknowledgement or leaderboard to encourage others to contribute, similar to a charity marathon? | Are there any plans to offer incentives or matching donations for certain milestones, like a $100 or $500 target, to motivate viewers to give?</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -4599,20 +4601,30 @@
           <t>YouTube</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Donat apple pay:droninja3@gmail.com venmo: https://venmo.com/u/Droninja.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>2026-07-29T05:51:59Z</t>
+        </is>
+      </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=iEHU8Kiybdo</t>
+          <t>https://youtube.com/watch?v=OFi3N-EGctQ</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Rose#1 New Student Charity Member</t>
+          <t>project live !  colleting 50 gift rasing and adding people in donation central #roblox #donating</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -4621,17 +4633,17 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Philanthropist</t>
+          <t>Gamers and philanthropists</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>What's the average financial burden that these students are facing, and how will the donated funds be allocated to support their college expenses? | Are there any specific college-related costs that this charity is focusing on, such as tuition, textbooks, or living expenses? | How will the charity ensure transparency and accountability in the distribution of funds to the students, and are there any plans for long-term support or mentorship programs?</t>
+          <t>How are you planning to track the 50 gift raisings in Donation Central, is there a specific leaderboard or dashboard you're using? | I'm curious, what kind of items are being donated in Roblox and how will they be distributed to those in need? | Are there any plans to collaborate with other Roblox streamers or charities to amplify the donation efforts and reach a wider audience?</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -4641,24 +4653,24 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>this channel for charity student to helping they're financial in collenge pls help them thank you PAYPAL :charityphil26@gmail.com.</t>
+          <t>This stream is created with #PRISMLiveStudio.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2026-07-29T05:01:03Z</t>
+          <t>2026-07-29T06:10:15Z</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=Vuu7R_wNNgQ</t>
+          <t>https://youtube.com/watch?v=0_6pPoU3EPM</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>NEW DONATION GAME?! I&amp;#39;M BACK DONATING ROBUX TO LIVE VIEWERS 🔴 LIVE 🔴</t>
+          <t>Playing Donation Central Raising Stream</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4671,17 +4683,17 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Young adults and teenagers</t>
+          <t>philanthropist</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Gaming</t>
+          <t>gaming</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>How do you decide who to donate Robux to during the livestream, is it completely random or are there specific criteria? | I've noticed some viewers are sharing their Robux wishlists in the Discord server, do you take those into consideration when donating? | Are you planning on doing any charity fundraisers or collaborations with other streamers in the future, perhaps for a specific Robux-driven charity event?</t>
+          <t>What's the average donor retention rate you've seen in charity streams like Donation Central, and how do you think we can improve it? | I'm curious about the tech behind Donation Central - are you using any specific plugins or integrations to facilitate donations and track engagement? | How do you handle transparency and accountability in charity streams, ensuring that donors know exactly where their funds are going and what impact they're having?</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -4689,30 +4701,25 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>JOIN UP AND GET A LAUGH OR TWO :D Discord server: https://discord.gg/UDxuJfESc Game link: ...</t>
-        </is>
-      </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>2026-07-29T05:38:34Z</t>
+          <t>2026-07-29T06:14:11Z</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=APismqX3YlI</t>
+          <t>https://youtube.com/watch?v=YBpFBT9M9TU</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Trying to get a $5 Donation or any Donation</t>
+          <t>VR chat fishing and chilling friends only !charity !stackup !calltoarm</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -4721,17 +4728,17 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Donor</t>
+          <t>Gamers and donors</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Non-Profit</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>I'm curious, have you considered partnering with a charity to amplify the impact of these $5 donations, perhaps a local food bank or education initiative? | For those donating via Venmo, will there be any public acknowledgement or leaderboard to encourage others to contribute, similar to a charity marathon? | Are there any plans to offer incentives or matching donations for certain milestones, like a $100 or $500 target, to motivate viewers to give?</t>
+          <t>How does the Stack Up charity initiative plan to allocate the funds raised from this VR chat event, and what specific causes will they be supporting? | I'd love to know more about the Discord server's role in organizing this charity event - are there any specific channels or resources available for attendees to get involved? | Will there be any opportunities for viewers to participate in the VR chat fishing and chilling activities, or are they primarily for entertainment while we support the charity drive?</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -4741,28 +4748,28 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Donat apple pay:droninja3@gmail.com venmo: https://venmo.com/u/Droninja.</t>
+          <t>https://discord.gg/nQtrHEy https://www.twitch.tv/kibathebarbarian https://tiltify.com/@kibathebarbarian/kibathebarbarian Join our ...</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>2026-07-29T05:51:59Z</t>
+          <t>2026-07-29T00:57:48Z</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=OFi3N-EGctQ</t>
+          <t>https://youtube.com/watch?v=ftgdaKQOZuI</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>project live !  colleting 50 gift rasing and adding people in donation central #roblox #donating</t>
+          <t>🔴Charity Gayle Christian Worship Songs 2025 - Best Praise and Worship Songs Of Charity Gayle</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -4771,17 +4778,17 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Gamers and philanthropists</t>
+          <t>Devout Christian</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Gaming</t>
+          <t>Non-Profit</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>How are you planning to track the 50 gift raisings in Donation Central, is there a specific leaderboard or dashboard you're using? | I'm curious, what kind of items are being donated in Roblox and how will they be distributed to those in need? | Are there any plans to collaborate with other Roblox streamers or charities to amplify the donation efforts and reach a wider audience?</t>
+          <t>I'm curious to know if Charity Gayle's worship songs will be featured in any upcoming charity events or fundraisers, potentially raising awareness for social causes? | What's the story behind Charity Gayle's most popular praise song - is there a specific inspiration or experience that drove its creation? | Are there any plans to collaborate with other Christian worship artists or bands to create a charity album or single, with proceeds going to a notable cause?</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -4791,28 +4798,28 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>This stream is created with #PRISMLiveStudio.</t>
+          <t>Charity Gayle Christian Worship Songs 2025 - Best Praise and Worship Songs Of Charity Gayle ▻Our main goal is to create a ...</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2026-07-29T06:10:15Z</t>
+          <t>2026-07-28T07:25:00Z</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=0_6pPoU3EPM</t>
+          <t>https://youtube.com/watch?v=v2xlAaUvceI</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Playing Donation Central Raising Stream</t>
+          <t>CommuniKitty CATURDAY! Cutie Cats ~ Free Games: !FOOD !Charity !Throne !Tip !YT !Kick CatGPT: Mother</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -4821,17 +4828,17 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>philanthropist</t>
+          <t>Animal Lover</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>gaming</t>
+          <t>Entertainment</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>What's the average donor retention rate you've seen in charity streams like Donation Central, and how do you think we can improve it? | I'm curious about the tech behind Donation Central - are you using any specific plugins or integrations to facilitate donations and track engagement? | How do you handle transparency and accountability in charity streams, ensuring that donors know exactly where their funds are going and what impact they're having?</t>
+          <t>How does the charity aspect of CommuniKitty CATURDAY work, are there specific organizations that benefit from the !Charity donations? | I'm curious about the !Throne game, is it a popular choice among viewers and does it have any impact on the charity donations throughout the stream? | Are there any plans to collaborate with other charity streams or organizations, perhaps through the !Discord hub, to amplify the fundraising efforts?</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -4839,25 +4846,30 @@
           <t>YouTube</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Made with Restream. Livestream on 30+ platforms at once via https://restream.io VOTE !Angel Art: !Discord | !Hubby !Dix !Tip !</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2026-07-29T06:14:11Z</t>
+          <t>2026-07-29T04:28:18Z</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=YBpFBT9M9TU</t>
+          <t>https://youtube.com/watch?v=eAv612q4p5A</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>VR chat fishing and chilling friends only !charity !stackup !calltoarm</t>
+          <t>Welcome back Glasses 🤓 Fundraiser Cash App 925Rucas</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -4866,17 +4878,17 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Gamers and donors</t>
+          <t>Donor</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Gaming</t>
+          <t>Non-Profit</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>How does the Stack Up charity initiative plan to allocate the funds raised from this VR chat event, and what specific causes will they be supporting? | I'd love to know more about the Discord server's role in organizing this charity event - are there any specific channels or resources available for attendees to get involved? | Will there be any opportunities for viewers to participate in the VR chat fishing and chilling activities, or are they primarily for entertainment while we support the charity drive?</t>
+          <t>How does the Glasses fundraiser plan to utilize the Cash App donations, specifically with the code 925Rucas, to support their charitable causes? | Can you share some insights on the impact of using Cash App for fundraising, like the 925Rucas campaign, in terms of donor engagement and retention for charity events? | What kind of transparency and updates can donors expect regarding the allocation of funds raised through the 925Rucas Cash App code, and how will it be used to benefit the charity?</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -4884,30 +4896,25 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>https://discord.gg/nQtrHEy https://www.twitch.tv/kibathebarbarian https://tiltify.com/@kibathebarbarian/kibathebarbarian Join our ...</t>
-        </is>
-      </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>2026-07-29T00:57:48Z</t>
+          <t>2026-07-29T05:55:31Z</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=ftgdaKQOZuI</t>
+          <t>https://youtube.com/watch?v=ghCzZTmrGBk</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>🔴Charity Gayle Christian Worship Songs 2025 - Best Praise and Worship Songs Of Charity Gayle</t>
+          <t>live with mummy charity 💕 good morning my besties 💗 join my live</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -4916,7 +4923,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Devout Christian</t>
+          <t>Philanthropic Young Adult</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4926,7 +4933,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>I'm curious to know if Charity Gayle's worship songs will be featured in any upcoming charity events or fundraisers, potentially raising awareness for social causes? | What's the story behind Charity Gayle's most popular praise song - is there a specific inspiration or experience that drove its creation? | Are there any plans to collaborate with other Christian worship artists or bands to create a charity album or single, with proceeds going to a notable cause?</t>
+          <t>Love the charity focus today, Mummy! What inspired you to partner with this particular organization? | How do you plan to use the momentum from a viral video to drive donations and support for your chosen charity? | Will you be sharing any updates on the charity's current projects or initiatives that we can get involved with?</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -4936,28 +4943,28 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Charity Gayle Christian Worship Songs 2025 - Best Praise and Worship Songs Of Charity Gayle ▻Our main goal is to create a ...</t>
+          <t>youtube #viralvideo.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2026-07-28T07:25:00Z</t>
+          <t>2026-07-29T06:03:42Z</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=v2xlAaUvceI</t>
+          <t>https://youtube.com/watch?v=LOLN_PqB_e4</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>CommuniKitty CATURDAY! Cutie Cats ~ Free Games: !FOOD !Charity !Throne !Tip !YT !Kick CatGPT: Mother</t>
+          <t>NOVA TERMINATOR MODE! | Warzone Mayhem | Charity Stream  Can We Raise £5,000 For The Kids?</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -4966,17 +4973,17 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Animal Lover</t>
+          <t>gamers and philanthropists</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Entertainment</t>
+          <t>gaming</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>How does the charity aspect of CommuniKitty CATURDAY work, are there specific organizations that benefit from the !Charity donations? | I'm curious about the !Throne game, is it a popular choice among viewers and does it have any impact on the charity donations throughout the stream? | Are there any plans to collaborate with other charity streams or organizations, perhaps through the !Discord hub, to amplify the fundraising efforts?</t>
+          <t>How's the donations tracker looking so far, are we on pace to hit that £5,000 goal for the kids by the end of the stream? | What's the plan for the Warzone gameplay, are you focusing on plunder or battle royale mode to maximize entertainment value for donors? | Will there be any special charity-themed gaming challenges or incentives for viewers to contribute during the stream, like a 'donate-to-lose' or 'donate-to-win' segment?</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -4986,24 +4993,24 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Made with Restream. Livestream on 30+ platforms at once via https://restream.io VOTE !Angel Art: !Discord | !Hubby !Dix !Tip !</t>
+          <t>LIVE NOW:Tonight we're dropping into Call of Duty: Warzone to have some fun while raising money for an amazing cause.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>2026-07-29T04:28:18Z</t>
+          <t>2026-07-28T19:14:23Z</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=eAv612q4p5A</t>
+          <t>https://youtube.com/watch?v=4lmMl9pJyFs</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Welcome back Glasses 🤓 Fundraiser Cash App 925Rucas</t>
+          <t>🔴Live | PLS Donate &amp;amp; Donate Plus | Donating ROBUX To Fans! #roblox #robux #donateplus #plsdonate</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -5016,17 +5023,17 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Donor</t>
+          <t>Gamers, Roblox enthusiasts</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Non-Profit</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>How does the Glasses fundraiser plan to utilize the Cash App donations, specifically with the code 925Rucas, to support their charitable causes? | Can you share some insights on the impact of using Cash App for fundraising, like the 925Rucas campaign, in terms of donor engagement and retention for charity events? | What kind of transparency and updates can donors expect regarding the allocation of funds raised through the 925Rucas Cash App code, and how will it be used to benefit the charity?</t>
+          <t>How do you handle ROBUX distribution to ensure fairness among fans, especially with the new Donate Plus system? | What's the criteria for selecting winners for the ROBUX giveaways, is it based on donation amount or random selection? | Have you considered partnering with Roblox game devs to create charity-themed games that integrate with Donate Plus for a good cause?</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -5034,21 +5041,26 @@
           <t>YouTube</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Join The New Dono Game! Donate Plus!! https://www.roblox.com/games/77403470693847/Donate-Plus ROBUX GIVEAWAYS ...</t>
+        </is>
+      </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>2026-07-29T05:55:31Z</t>
+          <t>2026-07-29T04:01:05Z</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=ghCzZTmrGBk</t>
+          <t>https://youtube.com/watch?v=_f5MJnFuyJE</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>live with mummy charity 💕 good morning my besties 💗 join my live</t>
+          <t>Streaming until I hit 500 subs and get my very first donation!</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -5061,17 +5073,17 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Philanthropic Young Adult</t>
+          <t>gamer/streamer</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Non-Profit</t>
+          <t>entertainment</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Love the charity focus today, Mummy! What inspired you to partner with this particular organization? | How do you plan to use the momentum from a viral video to drive donations and support for your chosen charity? | Will you be sharing any updates on the charity's current projects or initiatives that we can get involved with?</t>
+          <t>What's the plan for the donation once you hit the 500 sub goal - will it be going to a specific charity or cause? | How do you think the energy of the stream will change once you reach your donation milestone - will you be doing anything special to celebrate? | Are you considering partnering with a charity for future streams, maybe doing a fundraiser or something similar to give back to the community?</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -5081,47 +5093,47 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>youtube #viralvideo.</t>
+          <t>Have some popcorn, snacks with you to fully enjoy this cinema stream Don't forget to comments, Like &amp; subscribe or there will be ...</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2026-07-29T06:03:42Z</t>
+          <t>2026-07-28T00:26:04Z</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=LOLN_PqB_e4</t>
+          <t>https://youtube.com/watch?v=j0E369VHZN0</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>NOVA TERMINATOR MODE! | Warzone Mayhem | Charity Stream  Can We Raise £5,000 For The Kids?</t>
+          <t>Giving up is not an option!!</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>gamers and philanthropists</t>
+          <t>Individuals interested in financial education</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>gaming</t>
+          <t>Education/Finance</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>How's the donations tracker looking so far, are we on pace to hit that £5,000 goal for the kids by the end of the stream? | What's the plan for the Warzone gameplay, are you focusing on plunder or battle royale mode to maximize entertainment value for donors? | Will there be any special charity-themed gaming challenges or incentives for viewers to contribute during the stream, like a 'donate-to-lose' or 'donate-to-win' segment?</t>
+          <t>What strategies can be applied to maintain perseverance in the face of regulatory hurdles, like those from SEBI, when working towards a charitable cause? | How do you think the educational content on this channel can be leveraged to support fundraising efforts for charities, particularly in the context of financial literacy? | Can you discuss any personal anecdotes or case studies where persistence, as emphasized in the title, led to a successful charitable initiative or campaign?</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -5131,37 +5143,37 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>LIVE NOW:Tonight we're dropping into Call of Duty: Warzone to have some fun while raising money for an amazing cause.</t>
+          <t>This channel is only for education purposes!! we are not SEBI registered.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2026-07-28T19:14:23Z</t>
+          <t>2026-07-29T03:43:57Z</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=4lmMl9pJyFs</t>
+          <t>https://youtube.com/watch?v=do5Tl2QXM_A</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>🔴Live | PLS Donate &amp;amp; Donate Plus | Donating ROBUX To Fans! #roblox #robux #donateplus #plsdonate</t>
+          <t>GIVING AWAY ADMIN TREADMILL Roblox +1 Speed Keyboard Escape LIVE! #roblox  #trending  #fyp</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Gamers, Roblox enthusiasts</t>
+          <t>Young adults and teenagers</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -5171,7 +5183,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>How do you handle ROBUX distribution to ensure fairness among fans, especially with the new Donate Plus system? | What's the criteria for selecting winners for the ROBUX giveaways, is it based on donation amount or random selection? | Have you considered partnering with Roblox game devs to create charity-themed games that integrate with Donate Plus for a good cause?</t>
+          <t>How does the +1 Speed Keyboard Escape impact gameplay, especially in admin treadmill Roblox? | Are you considering donating to a charity from the proceeds of the viral livestream, maybe something related to gaming communities? | Can you share any tips on how to optimize the Roblox experience with the given keyboard setup for a seamless livestream?</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -5181,47 +5193,47 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Join The New Dono Game! Donate Plus!! https://www.roblox.com/games/77403470693847/Donate-Plus ROBUX GIVEAWAYS ...</t>
+          <t>fyp #funny #foryoupage #live #livestream #viral #trending #shorts #roblox.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2026-07-29T04:01:05Z</t>
+          <t>2026-07-29T03:28:32Z</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=_f5MJnFuyJE</t>
+          <t>https://youtube.com/watch?v=-devLYrSOB4</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Streaming until I hit 500 subs and get my very first donation!</t>
+          <t>🔴 MARVEL RIVALS RANKED! 🔴 WE&amp;#39;RE NOT GIVING UP!!</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>gamer/streamer</t>
+          <t>Gamers</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>entertainment</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>What's the plan for the donation once you hit the 500 sub goal - will it be going to a specific charity or cause? | How do you think the energy of the stream will change once you reach your donation milestone - will you be doing anything special to celebrate? | Are you considering partnering with a charity for future streams, maybe doing a fundraiser or something similar to give back to the community?</t>
+          <t>What's the reasoning behind ranking Spider-Man above Doctor Strange, considering their recent performances in the MCU? | How do you think the rankings would change if we factored in the characters' abilities in a team-up scenario, like the Avengers? | Curious to know if you've considered creating a separate ranking for villains - would be interesting to see how Thanos stacks up against other notable Marvel baddies</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -5229,49 +5241,44 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Have some popcorn, snacks with you to fully enjoy this cinema stream Don't forget to comments, Like &amp; subscribe or there will be ...</t>
-        </is>
-      </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2026-07-28T00:26:04Z</t>
+          <t>2026-07-29T02:09:30Z</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=j0E369VHZN0</t>
+          <t>https://youtube.com/watch?v=9EvUM9nkE5c</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Giving up is not an option!!</t>
+          <t>$1,775 to Talk to a Minister: Ottawa&amp;#39;s Fundraising Hypocrisy Exposed (LIVE) | Famelee TV</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Individuals interested in financial education</t>
+          <t>Socially Conscious Individual</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Education/Finance</t>
+          <t>Non-Profit</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>What strategies can be applied to maintain perseverance in the face of regulatory hurdles, like those from SEBI, when working towards a charitable cause? | How do you think the educational content on this channel can be leveraged to support fundraising efforts for charities, particularly in the context of financial literacy? | Can you discuss any personal anecdotes or case studies where persistence, as emphasized in the title, led to a successful charitable initiative or campaign?</t>
+          <t>I'd love to know more about the specifics of Ottawa's fundraising laws and how they're being exploited - are there any particular loopholes that allow ministers to charge exorbitant fees for access? | How does this fundraising hypocrisy impact charitable organizations, like the ones I work with, who rely on government grants and support? | Can Riya and Sam discuss potential solutions to increase transparency in political fundraising, such as implementing stricter disclosure laws or donation caps?</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -5281,37 +5288,37 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>This channel is only for education purposes!! we are not SEBI registered.</t>
+          <t>Riya and Sam are back — and this time they're roasting Ottawa's favourite pastime: political fundraising hypocrisy. From Mark ...</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2026-07-29T03:43:57Z</t>
+          <t>2026-07-28T22:03:36Z</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=do5Tl2QXM_A</t>
+          <t>https://youtube.com/watch?v=JqYsfd1d7RQ</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>GIVING AWAY ADMIN TREADMILL Roblox +1 Speed Keyboard Escape LIVE! #roblox  #trending  #fyp</t>
+          <t>🔴 PLS DONATE LIVE GIVEAWAY | GIVING ROBUX TO VIEWERS! (Roblox Live) 💸</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Young adults and teenagers</t>
+          <t>Gamers, particularly Roblox players</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -5321,7 +5328,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>How does the +1 Speed Keyboard Escape impact gameplay, especially in admin treadmill Roblox? | Are you considering donating to a charity from the proceeds of the viral livestream, maybe something related to gaming communities? | Can you share any tips on how to optimize the Roblox experience with the given keyboard setup for a seamless livestream?</t>
+          <t>How do you decide who to donate ROBUX to first in the PLS DONATE LIVE game mode? | Are you donating ROBUX to viewers who are actively participating in the stream, like commenting or engaging with the chat? | Do you think the PLS DONATE LIVE feature could be used to raise awareness or funds for real-life charities, similar to charity streams on other platforms?</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -5331,47 +5338,47 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>fyp #funny #foryoupage #live #livestream #viral #trending #shorts #roblox.</t>
+          <t>In this stream I am playing PLS DONATE LIVE donating ROBUX to EVERYONE. I'll be going around donating to everyone in "PLS ...</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2026-07-29T03:28:32Z</t>
+          <t>2026-03-23T13:00:00Z</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=-devLYrSOB4</t>
+          <t>https://youtube.com/watch?v=khu5WMfmpYQ</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>🔴 MARVEL RIVALS RANKED! 🔴 WE&amp;#39;RE NOT GIVING UP!!</t>
+          <t>ABP Ganga LIVE: Pune Murder Case | Lucknow Fire |Ram Mandir Donation | Mumbai Monsoon |Bharat Tiwari</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Gamers</t>
+          <t>General Audience</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Gaming</t>
+          <t>News/Media</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>What's the reasoning behind ranking Spider-Man above Doctor Strange, considering their recent performances in the MCU? | How do you think the rankings would change if we factored in the characters' abilities in a team-up scenario, like the Avengers? | Curious to know if you've considered creating a separate ranking for villains - would be interesting to see how Thanos stacks up against other notable Marvel baddies</t>
+          <t>What's the latest update on the Ram Mandir donation drive and how can individuals contribute to this cause, especially in the context of charitable giving? | Bharat Tiwari, can you shed some light on how the recent Lucknow fire incident has affected local charities and what relief efforts are being made? | How do you think the current monsoon situation in Mumbai will impact charitable organizations' ability to provide aid and support to those in need?</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -5379,21 +5386,26 @@
           <t>YouTube</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>ABP Ganga 24x7 LIVE: Pune Murder Case | Lucknow Fire |Ram Mandir Donation | Mumbai Monsoon |Bharat Tiwari हर बार ...</t>
+        </is>
+      </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>2026-07-29T02:09:30Z</t>
+          <t>2026-03-27T07:04:15Z</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=9EvUM9nkE5c</t>
+          <t>https://youtube.com/watch?v=EjvJGfo7RbY</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>$1,775 to Talk to a Minister: Ottawa&amp;#39;s Fundraising Hypocrisy Exposed (LIVE) | Famelee TV</t>
+          <t>(REAL) 🔴Pls Donate Robux Giveaway Live | Giving Robux In Pls Donate Live (Roblox Robux Giveaway)</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -5406,17 +5418,17 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Socially Conscious Individual</t>
+          <t>Roblox players</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Non-Profit</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>I'd love to know more about the specifics of Ottawa's fundraising laws and how they're being exploited - are there any particular loopholes that allow ministers to charge exorbitant fees for access? | How does this fundraising hypocrisy impact charitable organizations, like the ones I work with, who rely on government grants and support? | Can Riya and Sam discuss potential solutions to increase transparency in political fundraising, such as implementing stricter disclosure laws or donation caps?</t>
+          <t>How do you plan to use the donated Robux to support charitable causes within the Roblox community? | What's the most creative way you've seen a Roblox user utilize their donated Robux to give back to others? | Will you be partnering with any specific Roblox groups or charities for this giveaway, or is it more of an individual effort?</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -5426,28 +5438,28 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Riya and Sam are back — and this time they're roasting Ottawa's favourite pastime: political fundraising hypocrisy. From Mark ...</t>
+          <t>(REAL) Pls Donate Robux Giveaway Live | Giving Robux In Pls Donate Live (Roblox Robux Giveaway) #plsdonate ...</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>2026-07-28T22:03:36Z</t>
+          <t>2026-06-15T22:10:00Z</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=JqYsfd1d7RQ</t>
+          <t>https://youtube.com/watch?v=n9U4z1JO824</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>🔴 PLS DONATE LIVE GIVEAWAY | GIVING ROBUX TO VIEWERS! (Roblox Live) 💸</t>
+          <t>🔥 Stock clearance sale on Designer Suits | Wholesale Prices | Instyle Fashion Delhi</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>90</v>
+        <v>235</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -5456,17 +5468,17 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Gamers, particularly Roblox players</t>
+          <t>Fashion-conscious women</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Gaming</t>
+          <t>Fashion</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>How do you decide who to donate ROBUX to first in the PLS DONATE LIVE game mode? | Are you donating ROBUX to viewers who are actively participating in the stream, like commenting or engaging with the chat? | Do you think the PLS DONATE LIVE feature could be used to raise awareness or funds for real-life charities, similar to charity streams on other platforms?</t>
+          <t>For the wholesale prices on these designer suits, what's the typical MOQ look like, especially if we're interested in mixing and matching across the clearance range? Trying to get a sense of minimum buy-in. | Really interested in the 'best seller suits' mentioned – are these specific styles typically included in clearance events, or is this a unique opportunity for current best-sellers to be offered at wholesale? | Given it's a 'stock clearance,' will there be a good range of sizes available across the 'ladies suits collection,' or should we expect more limited sizing, especially for popular designs or the 'new...' additions? Trying to plan our inventory.</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -5476,28 +5488,28 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>In this stream I am playing PLS DONATE LIVE donating ROBUX to EVERYONE. I'll be going around donating to everyone in "PLS ...</t>
+          <t>Welcome to Instyle Fashion Delhi — wholesale &amp; retail ladies suits collection. Today we are showing: ✓ Best seller suits ✓ New ...</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>2026-03-23T13:00:00Z</t>
+          <t>2026-08-10T06:55:28Z</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=khu5WMfmpYQ</t>
+          <t>https://youtube.com/watch?v=dwRXCRnW95A</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ABP Ganga LIVE: Pune Murder Case | Lucknow Fire |Ram Mandir Donation | Mumbai Monsoon |Bharat Tiwari</t>
+          <t>🔴 LIVE: 14th August Preparations Flash Sale | Exclusive Discount Offer | 7th August | BuyPass TV</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>100</v>
+        <v>225</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -5506,17 +5518,17 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>General Audience</t>
+          <t>Individuals seeking home decor, cleaning products, and household items, particularly those interested in deals and discounts for festive occasions like Independence Day (14th August in Pakistan). Shoppers looking to refresh or transform their living spaces.</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>News/Media</t>
+          <t>Home Decor &amp; Goods</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>What's the latest update on the Ram Mandir donation drive and how can individuals contribute to this cause, especially in the context of charitable giving? | Bharat Tiwari, can you shed some light on how the recent Lucknow fire incident has affected local charities and what relief efforts are being made? | How do you think the current monsoon situation in Mumbai will impact charitable organizations' ability to provide aid and support to those in need?</t>
+          <t>Loving the focus on #RoomTransformation for 14th August! What's one key decor item from the flash sale that gives the biggest patriotic impact without a full overhaul? | Great to see #CleaningTips mentioned! What's a game-changer product from the flash sale that helps tackle a #MessyRoom specifically for these 14th Aug preparations? | Really appreciate the #GharSinghar vibe! For #HomeDecorPakistan and the 14th August celebrations, which specific discount item do you think will be the *first* to sell out because it perfectly captures that festive national spirit?</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -5526,28 +5538,28 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>ABP Ganga 24x7 LIVE: Pune Murder Case | Lucknow Fire |Ram Mandir Donation | Mumbai Monsoon |Bharat Tiwari हर बार ...</t>
+          <t>GharSinghar #LiveShow #14thaugustcelebration #RoomTransformation #HomeDecorPakistan #CleaningTips #MessyRoom ...</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>2026-03-27T07:04:15Z</t>
+          <t>2026-08-07T11:05:00Z</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=EjvJGfo7RbY</t>
+          <t>https://youtube.com/watch?v=-ufGfr4_zIU</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>(REAL) 🔴Pls Donate Robux Giveaway Live | Giving Robux In Pls Donate Live (Roblox Robux Giveaway)</t>
+          <t>mixed collection #clearance sale #kushifashions 7660991994 #viral #trending #offers #banarasi</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>80</v>
+        <v>220</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -5556,17 +5568,17 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Roblox players</t>
+          <t>Customers interested in discounted Indian ethnic wear, particularly Banarasi sarees and garments, seeking value and promotional offers.</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Gaming</t>
+          <t>Fashion / Apparel / Retail</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>How do you plan to use the donated Robux to support charitable causes within the Roblox community? | What's the most creative way you've seen a Roblox user utilize their donated Robux to give back to others? | Will you be partnering with any specific Roblox groups or charities for this giveaway, or is it more of an individual effort?</t>
+          <t>Are there any specific Banarasi silk sarees included in this 'mixed collection' clearance, or is it more focused on dress materials? | Curious about the best way to snag these clearance offers. Is there a direct purchase link available, or is it primarily through live chat interaction for items from the mixed collection? | For the Banarasi pieces in this clearance, are there options for customization (like blouse stitching) or are they strictly sold as-is? Just trying to plan my purchase!</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -5576,24 +5588,859 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(REAL) Pls Donate Robux Giveaway Live | Giving Robux In Pls Donate Live (Roblox Robux Giveaway) #plsdonate ...</t>
+          <t>mixed collection #clearance sale #kushifashions 7660991994 #viral #trending #offers #banarasi.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>2026-06-15T22:10:00Z</t>
+          <t>2026-08-10T07:57:24Z</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=n9U4z1JO824</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
-      <c r="O113" t="inlineStr"/>
+          <t>https://youtube.com/watch?v=1lhWUQ9DegY</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Flash Sale Special Agustus‼️Kemeja Sarung Batik #KemejaBatik #BatikFashion #IndonesianStyle</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>215</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Individuals interested in Indonesian batik fashion, seeking promotional deals, and comfortable with WhatsApp-based ordering for direct purchases.</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Min, kemeja sarung batik motif Parang Rusak yang tadi di-showcase itu bahan nya apa ya? Kayaknya adem banget buat acara siang. | Untuk flash sale Agustus ini, apakah ada diskon tambahan kalau beli lebih dari 2 pcs? Lumayan banget buat seragam kantor. | Kalau saya screenshot dan order via WA Admin sekarang, estimasi pengiriman ke Surabaya berapa hari ya? Mumpung lagi flash sale.</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>CARA ORDER 1️⃣ Screenshot produk yang ingin Anda beli. 2️⃣ Kirim foto screenshot tersebut ke WhatsApp Admin.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>2026-08-10T08:01:04Z</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=VJgTr1rBjLw</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>🎁 स्पेशल रक्षा बंधन Mega Sale | Heavy Discount on Premium Suits | Limited Stock #VaikunthCollection</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>185</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Women (or gift-givers for women) aged 25-55 interested in premium ethnic wear (suits, sarees, dress material) for festive occasions like Raksha Bandhan, seeking heavy discounts and exclusive live shopping deals.</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Apparel / Women's Ethnic Wear</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>The 'heavy discount' on #VaikunthCollection premium suits is great! Can you highlight if specific designs or sizes tend to sell out fastest with 'limited stock' for Rakhi? | You mentioned Sarees and Dress Material in the description. For this Raksha Bandhan Mega Sale, will we also see some premium options from the #VaikunthCollection in those categories today? | For these Premium Suits from the #VaikunthCollection, what's a key detail (like handwork or unique fabric) that really sets them apart, especially with the 'heavy discount' for Rakhi?</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Vaikunth Collection | Ladies Suits, Sarees, Dress Material &amp; Live Shopping Our women's clothing store offers a curated selection ...</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>2026-08-10T08:04:56Z</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=qpvIiF4c8d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>FLIPKART FREEDOM SALE Early Access Price REVEAL🔥iPhone, Samsung DDR4/DDR5 RAM Deals Live!</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>180</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Bargain hunters, tech enthusiasts, smartphone buyers, PC builders, individuals looking for electronics deals during major sale events, early access shoppers.</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>E-commerce, Consumer Electronics</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Will the iPhone deals include any discounts on the latest iPhone models with DDR5 RAM, or are those excluded from the sale? | Can you confirm if the Samsung deals will offer any bundle discounts when paired with a DDR4 RAM upgrade, similar to last year's sale? | Are there any specific bank offers or cashback deals available for customers purchasing during the early access period, especially for high-value items like iPhones?</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Flipkart Freedom Sale Live Now Price Reveal Price Drop. The biggest Amazon Great Freedom Sale 2026 and Flipkart Freedom ...</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>2026-08-07T07:00:49Z</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=ZnSu9pLfuJ8</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>CHANEL Store Shopping Music Mix 2026 | Deep House Fashion Playlist (Store Music for Stores)</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>155</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Retail store owners, shop managers, business owners seeking background music solutions, music licensing clients, brand experience managers</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Retail Music Services</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Love the focus on Deep House for CHANEL. Are you finding this specific sub-genre really elevates the perceived exclusivity or rather encourages longer dwell times in luxury retail environments? | Curious about the '2026' in the title – what specific retail or consumer trend insights are driving the track selection for this future-forward CHANEL mix? | Thinking about the practical application: have you seen this kind of curated Deep House blend specifically impact customer flow or even the average item value in premium fashion stores?</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>MusicForShops #ShopVibes #retailshopmusic CHANEL Store Shopping Music Mix 2026 | Deep House Fashion Playlist (Store ...</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>2026-04-03T17:13:58Z</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=WDb6Z6Yv708</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Market prise 2500 Shop discount 80%sale#9652939111</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>155</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Women interested in fashion and accessories, value-conscious shoppers looking for significant discounts, comfortable engaging via WhatsApp for shopping and deals.</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Fashion/Apparel (Women's Retail)</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>For the items that typically retail around the 2500 market price, are these specific pieces or a general category being discounted by 80% today? | Loving the collection! Quick question on joining the Ladies Emporium Group2 via the WhatsApp link – is that the best place to see all available items from this 80% sale or just the daily highlights? | The 80% off on that 2500 market price is incredible! Is there a cutoff time today to lock in that discount, or do orders placed through the #9652939111 number qualify all day?</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>https://chat.whatsapp.com/Jfkapom7JVr7JwTC48Q5ad?s=cl&amp;p=a&amp;mlu=3 Ladies emporium group2 ...</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>2026-08-09T11:53:13Z</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=3mSrZw-3bDo</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Clearance sale is live!</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>155</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Bargain hunters, price-sensitive shoppers, value seekers, existing customers looking for deals</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Hey team, excited for this! Are there any specific categories or product lines that are seeing the deepest discounts today, or should we just keep an eye on everything as it's shown? | Quick question about the sale mechanics: how long is this clearance running for, and are items being added in batches, or is it a one-time drop for everything available? | For anyone looking to grab a few items from the clearance, could you clarify if there are any specific shipping thresholds for free delivery, or perhaps any bundles that might emerge during the stream?</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>2026-08-10T07:31:50Z</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=o_0tl2x9zPA</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Sarees clearance sale</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>155</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Value-conscious women interested in traditional Indian wear (sarees, kurtis), comfortable with online purchases and strict clearance sale terms.</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>With the 'no return/no exchange' policy, could you share how sizing typically runs for the Kurtis – are they true to size or do they tend to run smaller/larger? Trying to avoid surprises! | Are we seeing a mix of fabrics today, or mostly specific types of sarees in this clearance lot? Always looking for those unique cotton blends! | Just to clarify on the 'parcel opening video' rule: if a genuine defect *is* found during that video, does that fall under a specific exception for resolution, given the 'no return' rule?</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Gan Gan Ganat Bote Kurti n sarees Rules 1-No return no exchange 2-Parcel opening video is must. 3- Return shipping charges to ...</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>2026-08-10T08:16:39Z</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=WMycBSHDBUA</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>🔥 Independence Day Special Live Sale! 🔥 Huge Discount on Trending T-shirts &amp;amp; Cord Sets 🇮🇳</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>155</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Value-conscious Indian consumers, interested in trending casual wear (T-shirts) and coordinated outfits (cord sets), likely patriotic and seeking discounts, potentially local to the Howrah area.</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Fashion, Apparel, Retail</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Hey! For the 'Huge Discount' on cord sets, what's the return or exchange policy like, especially if I'm planning a few bulk purchases for gifting? | Can you give us a quick rundown on the fabric blends for the 'Trending T-shirts' being featured? Trying to decide which ones would hold up best after multiple washes. | Just to clarify on the 'Independence Day Special' offer, does the discount apply uniformly across all items shown, or are certain styles like specific graphic tees excluded? Thinking of swinging by the Shibpur store.</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Booking No: 7980836639 Store Address: 55 Rammohan Mukherjee Lane, Near Shibpur Mandirtala, Shibpur, Howrah- 711102 ...</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>2026-08-10T08:21:12Z</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=uOk-nMAKwI4</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>🔥 LIVE iPhone &amp;amp; Android Sale | Casify B2B 📱 Best Mobile Deals Today Deals</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>155</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Business/Individual looking for mobile deals</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Hey team, Casify B2B ke liye kya special deals hain latest iPhone 15 series aur Samsung S24 models pe? Looking at options for our sales team. | Bulk orders ke liye deployment support ya extended warranty options kya hain? We usually get a mix of models for different departments. | Any special payment terms or credit options available for new B2B partners, especially for large volume purchases? Trying to streamline our procurement.</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>LIVE iPhone &amp; Android Sale | Casify B2B Best Mobile Deals Today Deals Casify B2B LIVE me aapka swagat hai! Aaj ki live ...</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>2026-08-10T08:25:27Z</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=8P4l1H72tZs</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>🌸 Sg kurtiz Special Live Sale | New Arrivals &amp;amp; Best Deals 💖</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>155</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Women interested in Asian clothing</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>What's the discount on the new Western Wear collection, are there any bundle deals available? | Can you show us some of the Daily Wear Suits and how they can be styled for a formal event? | Are there any limited edition Kurtis that will be available only during this live sale, and what's the price range for those?</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Welcome to SG Kurtiz Live Sale Discover the latest collection of Western Wear, Daily Wear Suits &amp; Stylish Kurtis at unbeatable ...</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>2026-08-10T08:30:01Z</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=LPn1wPZn7eM</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Small mistake boutique style sarees  clearance sale</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>155</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Women interested in traditional Indian clothing</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Could you maybe show an example of one of the 'small mistakes' on a saree, just so we get a better sense of how minor they usually are? Super interested in the boutique styles! | Love these unique designs! For the boutique styles, are we seeing mostly silks or more contemporary blends in this clearance batch? Trying to figure out which ones to grab. | For the pieces with minor imperfections, will the specific flaw be highlighted in the listing or mentioned when you show it? Just trying to make a quick decision if I see one I love!</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>2026-08-10T08:37:29Z</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=VYBSTeE14nE</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>🔴 Live Flash Sale Adenium Bunga Tumpuk Dan Karakter (7 Agustus 2026)#rachmannursery #adenium</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>155</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>plant collector or enthusiast</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>horticulture</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Apakah ada diskon khusus untuk pembelian Adenium Bunga Tumpuk Dan Karakter dalam jumlah banyak? | Berapa lama waktu pengiriman untuk wilayah luar Jawa, dan apakah ada biaya tambahan? | Apakah Adenium yang dijual sudah termasuk pot dan media tanam, atau harus dibeli terpisah?</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Yang Minat Tambah Koleksi Adeniumnya Info Order Hubungi Real WhatsApp Info Order Via WhatsApp 083875975911 ...</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:57:48Z</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=kYqnHekC2FQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>🔴 Live Flash Sale Adenium Bunga Tumpuk Dan Karakter (8 Agustus 2026)#rachmannursery #adenium</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>155</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>plant collector or enthusiast</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>horticulture</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Apakah ada diskon khusus untuk pembelian Adenium Bunga Tumpuk Dan Karakter dalam jumlah banyak? | Berapa lama waktu pengiriman untuk wilayah luar Jawa jika saya melakukan pemesanan hari ini? | Apakah ada garansi kesehatan tanaman untuk Adenium yang dibeli selama flash sale ini?</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Yang Minat Tambah Koleksi Adeniumnya Info Order Hubungi Real WhatsApp Info Order Via WhatsApp 083875975911 ...</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>2026-08-08T12:59:56Z</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=TQhOAgnX01s</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>🔴 Live Flash Sale Adenium Bunga Tumpuk Dan Karakter (9 Agustus 2026)#rachmannursery #adenium</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>155</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>plant collector or enthusiast</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>horticulture</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Apakah ada diskon khusus untuk pembelian Adenium Bunga Tumpuk Dan Karakter dalam jumlah banyak? | Berapa lama waktu pengiriman untuk Adenium yang dibeli selama flash sale ini? | Apakah ada garansi kesehatan tanaman untuk Adenium yang dibeli dari @rachmannursery?</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Yang Minat Tambah Koleksi Adeniumnya Info Order Hubungi Real WhatsApp @rachmannursery ⚫ Hanya ada 2 nomer Wa.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>2026-08-09T07:15:23Z</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=sKWhotY6F5U</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Var_sha&amp;#39;s Fashion Botique is live📩 Wholesale Order साठी DM करा#Saree#Dress#Fashion #Shorts#Vairal</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>150</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Individual or business looking for wholesale fashion products</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>What's the MOQ for wholesale orders of sarees and do you offer any discounts for bulk purchases? | Can you share some details about the fabric quality and designs available for the shorts and dresses? | Do you have a catalog or lookbook that I can refer to for placing a wholesale order, especially for the vairal collection?</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Var_sha's Fashion Botique is live   Wholesale Order साठी DM करा#Saree#Dress#Fashion #Shorts#Vairal ...</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>2026-08-10T07:29:00Z</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=NaBV3KsHi0E</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>🔴 LIVE: 🎁 100% FREE Women&amp;#39;s Fashion Products! 😍 Limited Time Offer</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>150</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Women interested in fashion</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>What's the process for claiming the free women's fashion products, is it a first-come-first-served basis or a random giveaway? | Are the free products from a specific collection or a mix of various Velvet Vogue lines, like the recently launched summer collection? | How do you plan to handle shipping and sizing for the free products, will there be an option for exchanges if the fit isn't right?</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Welcome to Velvet Vogue — Where Style Meets Confidence. ✨ ‎ ‎This channel is your ultimate destination for women's fashion ...</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:45:49Z</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=_1nJDgbhTWs</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>🔴 LIVE: 🎁 100% FREE Women&amp;#39;s Fashion Products! 😍 Limited Time Offer</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>150</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Women interested in fashion</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>What's the process for claiming the free women's fashion products, is it a first-come-first-served basis or a random giveaway? | Are the free products from a specific collection or a mix of different lines, like the Velvet Vogue Essentials or the Luxury Edit? | Will there be a discount code provided during the livestream for viewers who want to purchase additional items beyond the free products?</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Welcome to Velvet Vogue — Where Style Meets Confidence. ✨ ‎ ‎This channel is your ultimate destination for women's fashion ...</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>2026-08-07T13:04:42Z</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=RG8ymPMQ_Jw</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/livestreams.xlsx
+++ b/data/livestreams.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O401"/>
+  <dimension ref="A1:O442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18648,7 +18648,6 @@
           <t>General</t>
         </is>
       </c>
-      <c r="F401" t="inlineStr"/>
       <c r="G401" t="inlineStr">
         <is>
           <t>Meetup</t>
@@ -18665,16 +18664,1605 @@
           <t>Wed, Aug 5 · 7:00 PM ICT</t>
         </is>
       </c>
-      <c r="J401" t="inlineStr"/>
       <c r="K401" t="inlineStr">
         <is>
           <t>https://www.meetup.com/product-and-beyond-saigon/events/315505691/</t>
         </is>
       </c>
-      <c r="L401" t="inlineStr"/>
-      <c r="M401" t="inlineStr"/>
-      <c r="N401" t="inlineStr"/>
-      <c r="O401" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Charity Livestream for World Cancer Research Fund ...</t>
+        </is>
+      </c>
+      <c r="B402" t="n">
+        <v>63</v>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Organization Manager</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>Charity</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>I'd love to know more about the specific research projects that will be funded by this charity livestream - are there any updates on the current fundraising goals?</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>Charity Livestream for World Cancer Research Fund ...
+YouTube · Colour with Claire
+&gt;1,8 N lượt xem: · 5 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Online charity &amp; causes conferences</t>
+        </is>
+      </c>
+      <c r="B403" t="n">
+        <v>71</v>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Organization Manager</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>Charity</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>Have you considered exploring the intersection of online conferences and grassroots fundraising strategies, especially for smaller charities with limited resources?</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>Online charity &amp; causes conferences
+Eventbrite
+https://www.eventbrite.com › online › charity-and-caus...</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>AI on Local Hardware: What Works, What Doesn’t, and Why (Guest Speaker)</t>
+        </is>
+      </c>
+      <c r="B404" t="n">
+        <v>12</v>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>Meetup</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Organizer: Advanced AI Concepts-Ho Chi Minh City
+Attendees: </t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>Sat, Aug 1 · 9:00 PM ICT</t>
+        </is>
+      </c>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/advanced-ai-concepts-ho-chi-minh-city/events/315687404/</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Diaspora Charity Webinar Tickets, Saturday 25 July</t>
+        </is>
+      </c>
+      <c r="B405" t="n">
+        <v>86</v>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Organization Manager</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>Charity</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>How do you plan to measure the long-term impact of the charity initiatives supported by this webinar?</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>Diaspora Charity Webinar Tickets, Saturday 25 July
+Eventbrite
+https://www.eventbrite.com › diaspora...</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>IECF 2026 Policy &amp; Philanthropy Summit: All Together</t>
+        </is>
+      </c>
+      <c r="B406" t="n">
+        <v>86</v>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Recruiter, HR Manager</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>Recruitment</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>How do you see the intersection of policy and philanthropy influencing the allocation of funds for social impact initiatives in the next 2-3 years?</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>IECF 2026 Policy &amp; Philanthropy Summit: All Together
+Eventbrite
+https://www.eventbrite.com › iecf-202...</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026 Power of Philanthropy Summit</t>
+        </is>
+      </c>
+      <c r="B407" t="n">
+        <v>86</v>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Recruiter, HR Manager</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>Recruitment</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>How do you see the intersection of impact investing and traditional philanthropy evolving in the next 5 years, given the increasing focus on measurable outcomes?</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>2026 Power of Philanthropy Summit
+Eventbrite
+https://www.eventbrite.com › 2026-p...</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Philanthropy Summit: The Power of Community, Collaboration ...</t>
+        </is>
+      </c>
+      <c r="B408" t="n">
+        <v>90</v>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Non-profit professionals, Philanthropists</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>Non-profit, Philanthropy</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>How do organizations balance community engagement with the need for measurable impact in their philanthropic efforts?</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>Philanthropy Summit: The Power of Community, Collaboration ...
+YouTube · The Non Profit Podcast Network
+&gt;40 lượt xem: · 8 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>International Aid events Online - Charity &amp; Causes</t>
+        </is>
+      </c>
+      <c r="B409" t="n">
+        <v>90</v>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Philanthropist</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>Non-Profit</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>What strategies can organizations use to effectively measure the long-term impact of their online fundraising campaigns, especially when it comes to reaching underserved communities?</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>International Aid events Online - Charity &amp; Causes
+Eventbrite
+https://www.eventbrite.com › ... › Charity &amp; Causes</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>[Webinar] Making sense of 2026: Fundraising trends ...</t>
+        </is>
+      </c>
+      <c r="B410" t="n">
+        <v>80</v>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Fundraising professionals</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>Non-profit fundraising</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>I'm curious to know how the shift towards digital fundraising will impact smaller non-profits with limited resources, and what strategies can be employed to level the playing field.</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>[Webinar] Making sense of 2026: Fundraising trends ...
+YouTube · Givebutter
+&gt;530 lượt xem: · 5 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Empowering Nonprofits: Fundraising in a Cashless World ...</t>
+        </is>
+      </c>
+      <c r="B411" t="n">
+        <v>95</v>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>non-profit organizations</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>non-profit</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>How do you recommend nonprofits balance the shift to digital fundraising with the need to maintain relationships with long-time donors who may be hesitant to adopt new payment methods?</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>Empowering Nonprofits: Fundraising in a Cashless World ...
+YouTube · Alterna Savings
+&gt;30 lượt xem: · 1 năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Nonprofit Guide to Peer to Peer Fundraising 2026</t>
+        </is>
+      </c>
+      <c r="B412" t="n">
+        <v>95</v>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Non-profit organization</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>Non-profit</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>Have you considered how to incentivize repeat donors to participate in P2P campaigns, and what strategies Mightycause has seen work best in encouraging this behavior?</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>Nonprofit Guide to Peer to Peer Fundraising 2026
+YouTube · Mightycause
+&gt;70 lượt xem: · 1 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Nonprofit holding 3rd annual fundraising event at Top Golf</t>
+        </is>
+      </c>
+      <c r="B413" t="n">
+        <v>95</v>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Philanthropist or supporter of non-profit organizations</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>Non-profit</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>Have you considered partnering with local businesses like Top Golf to offer exclusive sponsorship packages for your fundraising event?</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>Nonprofit holding 3rd annual fundraising event at Top Golf
+YouTube · KRQE
+&gt;50 lượt xem: · 4 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>[Webinar] Top strategies for mastering fundraising events</t>
+        </is>
+      </c>
+      <c r="B414" t="n">
+        <v>95</v>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Fundraising professionals, Non-profit event planners</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>Non-profit</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>How do you balance the need for personal connections with donors at events while also ensuring a smooth and efficient check-in process for a large number of attendees?</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>[Webinar] Top strategies for mastering fundraising events
+YouTube · Givebutter
+&gt;940 lượt xem: · 2 năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>A Glimpse into Excellence: Global CSR &amp; Philanthropy ...</t>
+        </is>
+      </c>
+      <c r="B415" t="n">
+        <v>80</v>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Academic or University audience</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>How do you think CSR initiatives can effectively address the water scarcity issue in rural India, given the complex interplay between government policies, community engagement, and technological innovations?</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>A Glimpse into Excellence: Global CSR &amp; Philanthropy ...
+YouTube · Ganpat University, GUNI, Gujarat, India
+&gt;170 lượt xem: · 3 tuần trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>🌍 English Club at Myths Cafe – Every Tuesday!</t>
+        </is>
+      </c>
+      <c r="B416" t="n">
+        <v>23</v>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>Meetup</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Organizer: HCMC - Myths community
+Attendees: </t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>Tue, Jul 21 · 7:00 PM ICT</t>
+        </is>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/hcmc-myths-community/events/315545540/</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Perfume &amp; Fragrance Craft Workshop</t>
+        </is>
+      </c>
+      <c r="B417" t="n">
+        <v>16</v>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>Meetup</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Organizer: HCMC - Myths community
+Attendees: </t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>Fri, Jul 24 · 7:00 PM ICT</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/hcmc-myths-community/events/315545727/</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>🌍 English Club at Myths Cafe – Every Tuesday!</t>
+        </is>
+      </c>
+      <c r="B418" t="n">
+        <v>23</v>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>Meetup</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Organizer: HCMC - Myths community
+Attendees: </t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>Tue, Jul 28 · 7:00 PM ICT</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/hcmc-myths-community/events/315545541/</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Charities Aid Foundation</t>
+        </is>
+      </c>
+      <c r="B419" t="n">
+        <v>40</v>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>Charity Webinar</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>I'd love to hear more about how CAF is addressing the issue of donor fatigue in the UK, given the current economic climate.</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>Charities Aid Foundation
+YouTube
+https://www.youtube.com › videos</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>🎮 LIVE Minecraft for Assam Flood Relief ❤️🌊 | Charity Stream | Help Assam</t>
+        </is>
+      </c>
+      <c r="B420" t="n">
+        <v>90</v>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Socially conscious gamer</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>Non-profit</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>Thank you for streaming for a great cause! Every donation counts in helping those affected by the Assam floods.</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=KHEJdMItGbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>The Great LEGO London Challenge LIVE FOR CHARITY!</t>
+        </is>
+      </c>
+      <c r="B421" t="n">
+        <v>90</v>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Family-oriented, philanthropic individuals</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>Entertainment</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>Exciting to see LEGO enthusiasts coming together for a great cause! What's your favorite LEGO creation?</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=eOgiZjCHZlI</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>🔴 LIVE NOW | Meru County  Join us as we follow the Tharaka University 530 KM Charity Walk for the E</t>
+        </is>
+      </c>
+      <c r="B422" t="n">
+        <v>140</v>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>2026-08-04T17:07:57Z</t>
+        </is>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=B5Mx9I9uyMQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Diabetes Awareness &amp;amp; Fundraising Event Adelaide</t>
+        </is>
+      </c>
+      <c r="B423" t="n">
+        <v>135</v>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>LIVE NOW! We're Happy to bring you Here! Streaming live from The Palms Banquet Hall Adelaide, 5 Famechon Cres, Modbury ...</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>2025-02-08T11:11:42Z</t>
+        </is>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=dwmWxqfIbSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>TDC Australi Fundraising Event Melbourne</t>
+        </is>
+      </c>
+      <c r="B424" t="n">
+        <v>135</v>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>LIVE NOW! We're Happy to bring you Here Streaming live from Mulgrave Community Centre 355 Wellington Rd, Mulgrave VIC ...</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>2024-03-30T08:29:24Z</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=hVsl7RBQZUk</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>🔴[DC ] CHARITY WEDS DUNCAN [8/8/2026]</t>
+        </is>
+      </c>
+      <c r="B425" t="n">
+        <v>90</v>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>2026-08-08T07:42:44Z</t>
+        </is>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=Z8MC_lXRbdQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Delma #21 student charity member</t>
+        </is>
+      </c>
+      <c r="B426" t="n">
+        <v>90</v>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>this channel for charity student to helping they're financial in collenge pls help them thank you PAYPAL :charityphil26@gmail.com.</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>2026-08-08T06:01:44Z</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=suYrAr1shRc</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Flood relief charity stream Assam</t>
+        </is>
+      </c>
+      <c r="B427" t="n">
+        <v>80</v>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>Flood relief charity stream Assam.</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>2026-08-08T10:01:59Z</t>
+        </is>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=bzgsGfgnkHQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>เตะเพื่อน้อง Counterpain Charity Cup 4 เส้าการกุศล</t>
+        </is>
+      </c>
+      <c r="B428" t="n">
+        <v>80</v>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>เตะเพื่อน้อง Counterpain Charity Cup 4 เส้าการกุศล VIP เมืองกาญจน์เวชภัณฑ์ พบ KING BULL FC VIP กาญจนบุรี พบ บอยท่าพระจันทร์ FC ...</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>2026-08-08T09:16:00Z</t>
+        </is>
+      </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=Z1OhnhuwMqQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>LEY 75 NEW STUDENT CHARITY MEMBER</t>
+        </is>
+      </c>
+      <c r="B429" t="n">
+        <v>80</v>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>LIVE , DANCING,MUSIC, STUDENT LIVE STREAMER TO HELP THEY'RE STUDY PLS HELP US THANK YOU SO MUCH.</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>2026-08-08T09:15:20Z</t>
+        </is>
+      </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=3NXu-XjjElU</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Environmental Volunteers Live Stream</t>
+        </is>
+      </c>
+      <c r="B430" t="n">
+        <v>77</v>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:29:54Z</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=o4sS0OJO75o</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Aaj Ki Taza Khabren LIVE: Weather Update | Ranchi Student Protest  | Badrinath Donation Scam</t>
+        </is>
+      </c>
+      <c r="B431" t="n">
+        <v>75</v>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>Aaj Ki Taza Khabren LIVE: Weather Update | Ranchi Student Protest | Badrinath Donation Scam दिल्ली में टूटा 15 ...</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>2026-08-08T01:00:23Z</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=oWf1_OqLwsg</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>(REAL) 🔴 PLS DONATE LIVE | GIVING ROBUX TO VIEWERS! (Roblox Giveaway) 💰</t>
+        </is>
+      </c>
+      <c r="B432" t="n">
+        <v>75</v>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>freerobux #plsdonate #robux #freerobux #plsdonate #robux In this stream I am playing PLS DONATE LIVE donating ROBUX to ...</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>2026-06-15T22:18:32Z</t>
+        </is>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=a6ju_zwS_fY</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>🔴 #HELLDIVERS2 : Giving em HELL on HELLMIRE</t>
+        </is>
+      </c>
+      <c r="B433" t="n">
+        <v>75</v>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>Support me at Kofi: https://ko-fi.com/tana_sukke/goal?g=0 . Follow me on other platforms .</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>2026-08-08T03:03:17Z</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=X5Gvog88-rU</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>🔴 Giving Seeds to Every Viewer LIVE! (Grow A Garden 2 Live) Free Pets Giveaway</t>
+        </is>
+      </c>
+      <c r="B434" t="n">
+        <v>75</v>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>Welcome to the stream! Today I am giving away Seeds &amp; Pets to Every Viewer LIVE! This is the biggest Grow A Garden 2 ...</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>2026-07-22T23:03:43Z</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=wtfxUyPWE_M</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Live on Donut Smp |Rating bases,giving money|loot drop|JOIN NOW!!!</t>
+        </is>
+      </c>
+      <c r="B435" t="n">
+        <v>75</v>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>LIVE ON DONUT SMP!** Today we're going all out on **Donut SMP**! Rating YOUR bases Giving away money Loot ...</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>2026-08-08T09:28:10Z</t>
+        </is>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=IIXHj4Ej8zI</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Fortnite Playing w/ subs &amp;amp; giving away sprites| USE CODE: NXBYT</t>
+        </is>
+      </c>
+      <c r="B436" t="n">
+        <v>75</v>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>2026-08-08T07:00:41Z</t>
+        </is>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=YU6u754KeXs</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>🔴BLOX FRUITS PERM DRAGON FRUIT GIVEAWAY | GIVING AWAY FREE FRUITS LIVE!</t>
+        </is>
+      </c>
+      <c r="B437" t="n">
+        <v>75</v>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>BLOX FRUITS PERM DRAGON FRUIT GIVEAWAY! #bloxfruitslive #bloxfruitslive #bloxfruitsroblox #bloxfruitsgiveaway ...</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>2026-01-06T06:20:09Z</t>
+        </is>
+      </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=L3hgmgoMqQQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>I&amp;#39;m streaming until I beat EVERY Sonic Game... please help. (DAY 3)</t>
+        </is>
+      </c>
+      <c r="B438" t="n">
+        <v>65</v>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>DONATE 2 CHARITY HERE: https://tilt.fyi/6VEystKlyl LEADERBOARD: https://tilt.fyi/UZ2WslUx1B Donation Incentives: $50 NUKE ...</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>2026-08-07T20:40:37Z</t>
+        </is>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=l8weFEfHUm8</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>FINAL Pokopia Bubbly Basin CHARITY Stream, @SU2C</t>
+        </is>
+      </c>
+      <c r="B439" t="n">
+        <v>90</v>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Gamers and philanthropists</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>Thank you for supporting a great cause! Your donations will help make a difference in the fight against cancer.</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=2Yu86v3LGLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>EP 25. Sulphur and Testing [!hardmode 25x] | Extra Life Charity Stream</t>
+        </is>
+      </c>
+      <c r="B440" t="n">
+        <v>90</v>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Gamers and philanthropists</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>Thanks for streaming for a great cause! Good luck with your gaming challenges and I hope you reach your charity goals.</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=WvA2AH7u3KQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>mummy charity ufomba is live!</t>
+        </is>
+      </c>
+      <c r="B441" t="n">
+        <v>90</v>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>Philanthropist</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>Non-Profit</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>Thank you for supporting a great cause! What will the donations from this livestream be used for?</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=7uGPoDc90T4</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>The 1st Annual Misti Media Book Fair</t>
+        </is>
+      </c>
+      <c r="B442" t="n">
+        <v>60</v>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Book lovers, Students, Educators</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>Education/Entertainment</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>Excited for the book fair! Will any proceeds be going to support a charitable cause?</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr"/>
+      <c r="I442" t="inlineStr"/>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=wub4C1yzbKY</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr"/>
+      <c r="L442" t="inlineStr"/>
+      <c r="M442" t="inlineStr"/>
+      <c r="N442" t="inlineStr"/>
+      <c r="O442" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/livestreams.xlsx
+++ b/data/livestreams.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Livestreams" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Livestreams" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O130"/>
+  <dimension ref="A1:O137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6442,6 +6442,188 @@
         </is>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>🔥MENHELYEN JÁRTAM🔥PÉNTEKTŐL VASÁRNAPIG CHARITY STREAM🔥 I JUST CHATTING</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>90</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=rpckPiTWTSU</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>monday morning hardcore [ minecraft | bedrock | hardcore | !legends ] !charity</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>80</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=Bc4hyMI5Jn4</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>LEGO Charizard Build Livestream for Charity!</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>80</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=O4O7wik4ynk</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>satkartar satsang ghar charitable society is live!</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>56</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=uqX2-mzcmSQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Jesus Protects You, Eliminates Evil &amp; Brings Healing, Peace &amp; Miracles Into Your Life Instantly</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>41</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=uDgzWqNstjI</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Beaver Cam</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>34</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=zkTaY9OQM2A</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>WORDFEST 2026 || DAY 2|| EVENING SERVICE || REV MARTIN || TILL NO. 837898 || 10.08.026</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>34</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=lrXDSoEvtBo</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/livestreams.xlsx
+++ b/data/livestreams.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O137"/>
+  <dimension ref="A1:O174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6606,23 +6606,1423 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
           <t>YouTube</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr"/>
-      <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr">
         <is>
           <t>https://youtube.com/watch?v=lrXDSoEvtBo</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Live streaming of RADHA GAMING</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>205</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Gamer</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>What's the strategy behind RADHA GAMING's controller layout, are they using a custom design or sticking to traditional layouts? | How does RADHA GAMING plan to address issues like lag and server overload during high-traffic gaming sessions? | Can you discuss the esports potential of RADHA GAMING, are there any plans for competitive tournaments or sponsorships?</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=jEWOj-4trqI</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>[EN-C] Aurora Gaming vs. GamerLegion - The International 2026 - Group Stage - Round 1</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>145</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Gamer</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>How do you think Aurora Gaming's recent roster changes will impact their strategy against GamerLegion, esp with their new mid laner? | Will GamerLegion's experience in high-pressure tournaments give them an edge in the group stage, or can Aurora's youthful energy disrupt their momentum? | Curious to see if Aurora Gaming will stick with their signature Phantom Assassin pick or try to catch GamerLegion off guard with an unconventional hero</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=2Cl9jwviUfQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>what's up gamers... overworked, underpayed, but still GAMING</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>145</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Gamer</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>I'm curious, how do you balance gaming with a heavy workload - do you have any strategies for managing burnout? | What's the most challenging part of being an underpaid gamer - is it the lack of recognition or the struggle to afford new gear? | Do you think the gaming community can come together to advocate for better working conditions and fair pay, or is that a pipe dream?</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=43flKqeolO0</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Free Fire Esports Tournament Practice Live with SHADOW GAMING UNIVERSE #freefire #esports #grind</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>145</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Gamer</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>What's the strategy behind SHADOW GAMING UNIVERSE's map control in Bermuda, do they focus on high-ground or flanking routes? | How does the team handle resource distribution, especially when it comes to ammo and medkits, during intense clashes? | Are they experimenting with any new character combos, like Chrono and Kelly, to gain an edge in the tournament?</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=uPMf6werd-o</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Unstoppable &amp; Unbelievable M24 Gameplay Live 💥 | GT KNIFE GAMING |</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>135</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Gamer</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>What's your strategy for handling those tough M24 no-scopes, do you prioritize map awareness or quick reflexes? | I've been having trouble with the KNIFE GAMING controller setup, how do you customize your buttons for optimal M24 gameplay? | Can you walk us through your thought process when deciding whether to push or play defensively with the M24 in a competitive match?</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=rK18wPjBOis</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Nithya Gaming🤍🔥||GIRLGAMER|| LIVESTREAM||FREEFIRE</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>135</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Gamer</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Nithya, what's your go-to strategy for clutching up in Free Fire's final circles? | How do you handle smurfing in ranked matches, do you have any tips for dealing with experienced players? | Do you think the latest Free Fire update has improved the game's balance, especially with the new weapon additions?</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=-RIUZU5xkYU</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Syifa sahil sedang live Games Ball Run sekarang! #games #gaming #gameplay</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>135</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Gamer</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Apa strategi yang Syifa gunakan untuk melewati level 5 di Games Ball Run? | Bagaimana cara mengatasi glitch yang sering terjadi di level 3, apakah ada tips khusus? | Apakah Games Ball Run akan memiliki update baru untuk menambahkan fitur multiplayer, Syifa?</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=sVLRLfj5NUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>[EN-A] Team Spirit vs. Xtreme Gaming - The International 2026 - Group Stage - Round 1</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>95</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Gamer</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Esports</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>How do you think Team Spirit's recent roster changes will impact their laning phase strategy against Xtreme Gaming? | Will Xtreme Gaming's aggressive playstyle be able to counter Team Spirit's strong defensive capabilities, especially in the context of the current meta? | Do you think the patch updates will give Team Spirit an edge in terms of itemization and hero picks, potentially swinging the match in their favor?</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=nU5mLup2s7Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>[ES-A] Team Spirit vs. Xtreme Gaming - The International 2026 - Fase de Grupos - Ronda 1</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>95</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Gamer</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Esports</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>How do you think Team Spirit's aggressive laning phase will match up against Xtreme Gaming's more defensive approach, esp in the bot lane? | Curious to see if Xtreme Gaming will stick with their signature Phantom Assassin pick or try to catch Team Spirit off guard with a different carry hero | Will the new patch changes to the Roshan respawn timer affect Team Spirit's usual strategy of taking early objectives, or will they adapt to a more passive game plan?</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=ePARKLerYAw</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>[EN-B] Team Liquid vs. Vici Gaming - The International 2026 - Group Stage - Round 1</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>100</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Gamer</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Esports</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>How do you think Team Liquid's recent roster changes will impact their laning phase strategy against Vici Gaming? | Will Vici Gaming's experience in the Chinese Dota scene give them an edge in terms of execution on the new 7.32 patch? | Do you think the current meta favors Team Liquid's aggressive playstyle or will Vici Gaming's more defensive approach pay off in this matchup?</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=VaZpuoMhjmg</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>FC 26 EA Sports || World Cup 2026 || Live L A S E R Gaming Op ⚽ #shortsfeed #shortslive #shorts</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>95</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Gamer</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>How's the new laser gaming op setup handling lag in high-intensity matches like the World Cup 2026? | Curious to know if the FC 26 EA Sports update includes any tweaks to player stats or team dynamics, specifically for teams like Brazil or Argentina? | Does the livestream's focus on World Cup 2026 mean we can expect any special gaming modes or challenges, like a 'Road to the Final' tournament?</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=U3Krg7l0iOI</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>😎1 CHICKEN = 5000 rs CHALLENGE 🔥| BGMI LIVE ‪‪@LoLzZzGaming</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>95</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Gamer</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>What's your strategy for rotating to the next circle in BGMI when you're in a crowded area like Pochinki? | How do you handle campers in the 1 chicken = 5000 rs challenge, do you try to flush them out or play stealthy? | Are you using any specific sensitivity settings or gyroscope tweaks to get those quick scopes in BGMI?</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=ZIP9rjMCgPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>[RU-A] Team Spirit vs. Xtreme Gaming - The International 2026 - Групповой Этап - Раунд 1</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>95</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Gamer</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Esports</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>How do you think Team Spirit's recent roster changes will impact their strategy against Xtreme Gaming, esp in the laning phase? | Curious to see if Xtreme Gaming will stick with their aggressive draft style or play more defensively to counter Team Spirit's experience | Will the new patch updates affect the balance of power in this matchup, particularly for heroes like Phantom Assassin or Ursa?</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=1Uw4Uv48C_k</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>GTA 5 LIVE 🔥 #gta5 #shortslive #gaming</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>95</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Gamer</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>What's your strategy for completing the 'Pacific Standard' heist on hard mode, any tips for avoiding those pesky cops? | How do you handle the tank battles in GTA 5, do you have a preferred vehicle or tactic for taking them down? | Are you using any specific mods to enhance the gameplay experience, like graphics or physics tweaks, or keeping it vanilla?</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=xPC3CfbiqZo</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>The Most Savage Zombies Are Coming! || DAYSGONE #gaming #stream #zombie</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>95</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Gamer</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>How do you think the hordes mechanic in Days Gone will impact our overall survival strategy, especially when facing those super aggressive Freakers? | I've been wondering, will the game's dynamic weather and time-of-day systems affect zombie behavior, like making them more aggressive at night? | What's your take on the bike's customization and upgrade options - do you think it'll be a game-changer for navigating the zombie-infested roads?</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=Ybyy_Icq_-I</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>HORROR GAME GRANNY 🔥 #granny #shortslive #granny #shorts #live #gaming #ericislive</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>98</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Gamer</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>How do you handle the granny's AI when she's in 'rage mode' - do you have any strategies for evading her? | I've noticed the game's sound design really adds to the tension - have you experimented with different audio settings to enhance the horror experience? | What's your approach to navigating the house without triggering granny's detection - do you prioritize stealth or speed?</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=cnNMJ20wKkM</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Free Fire Live 🔴 Bihar-UP Ka Bhaukal 🔥 Lallantop Gaming Ke Saath Aaja Bhai! #lallantopgaming</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>95</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Gamer</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>What's the strategy for clutching up in 1v3 situations in Free Fire, any tips from your experience? | How do you handle lag in ranked matches, is it more about internet quality or optimizing in-game settings? | Do you think the new Bermuda map update will change the meta for pro players, or is it more suited for casual gameplay?</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=PcN-u0gxCN0</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>EFOOTBALL 2027 IS HERE | LETS GOOO</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>95</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Gamer</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>How's the new 'Dynamic Tactics' system gonna affect online multiplayer, any major changes to player switching? | What's the deal with the rumored 'HyperMotion2' tech, does it really improve player animations that much? | Are we getting any new stadium creations or editor features in eFootball 2027, that was a major letdown in the previous version</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=G4xUliuv57M</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>JULIE 57 STUDENT CHARITY</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>95</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Student/Donor</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Education/Non-Profit</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>How does the Julie 57 student charity plan to allocate funds to support education initiatives, and are there any specific programs or partnerships you're excited about? | I'd love to know more about the charity's approach to community engagement - are there any volunteer opportunities or events that attendees can get involved in to support the cause? | What kind of impact has the Julie 57 student charity seen in terms of improving access to education for underprivileged students, and how do you measure the success of your programs?</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=nd_YUEp03cw</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>SARAH 51 STUDENT CHARITY MEMBER</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>90</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Donor/Supporter</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Non-profit</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>What specific initiatives has the Sarah 51 student charity member program implemented to increase community engagement and participation? | How does the charity plan to address potential challenges in fundraising, particularly in terms of donor retention and acquisition? | Can you share any success stories or case studies of the impact the Sarah 51 student charity member program has had on the local community or specific causes?</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=6LASvD_-2_0</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>SAM 49: CHARITY MEMBER</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>95</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Donor</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Non-profit</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>What specific strategies has SAM 49 implemented to increase member engagement and retention, particularly in terms of volunteer opportunities? | How does SAM 49 handle donor management and stewardship, and are there any plans to integrate new technologies to streamline these processes? | Can you discuss the role of corporate partnerships in supporting SAM 49's charitable initiatives, and how these partnerships are cultivated and maintained?</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=VwWO5j1jddw</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>mummy charity ufomba is live! hi guys</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>90</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Donor</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Non-profit</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Ufomba, what inspired you to start Mummy Charity and how do you see it impacting local communities? | I'd love to know more about the charity's current projects - are there any upcoming fundraising events we can support? | How can we as a community get involved and volunteer with Mummy Charity to make a difference?</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=EPllkkjcHjc</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>🔴 LIVE: I’ve NEVER Built a Leveled SS2 City Plan + Scrap Data | Fallout 4 Modding for Charity</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>90</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Gamer</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>How do you plan to balance settlement build size with scrap availability in this SS2 city plan, considering the charity build's focus on sustainability? | What specific mods are you using to optimize scrap data collection and will you be sharing the mod list for viewers to replicate? | Will the charity aspect involve a donation goal tied to specific settlement milestones, like reaching a certain population size or completing a particular build?</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=z0Ju1UncMi8</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Entertainment Tagaytay Ballroom</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>41</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Socialite/Donor</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Entertainment</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>How does the Entertainment Tagaytay Ballroom plan to incorporate charity events or fundraisers into its programming, potentially partnering with local organizations? | I'd love to know more about the ballroom's community outreach initiatives - are there any plans for hosting galas or benefits for local charities? | Can the speakers discuss the potential for the Entertainment Tagaytay Ballroom to serve as a venue for charity auctions or fundraising dinners, and what amenities they could offer to support these types of events?</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=oQMT0xc3aW8</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>🔴 (LIVE) ARISE AND THRIVE CONFERENCE || DAY 3 || SESSION 1 || 13/8/2026</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>70</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Philanthropist/Entrepreneur</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Non-profit/Personal Development</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>How can we apply the thrive mindset discussed in yesterday's session to overcome common obstacles in charity fundraising, particularly in terms of donor engagement? | I'd love to hear more about the role of community partnerships in driving social impact, as mentioned in the conference program - can we discuss potential collaborations between charities and local businesses? | What strategies would you recommend for charities to measure and evaluate the effectiveness of their programs, ensuring that donations are being utilized efficiently and making a tangible difference?</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=OpAzLbbsT-A</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>JEVZ 45 CHARITY MEMBER</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>75</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=ygKNtOFouh8</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DONT MAKE FUN OF MY HAIR but this is an incredible volunteering opportunity in new york area!!❤️ #volunteer #charity #community #giveback #nonprofit  </t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>255</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DONT MAKE FUN OF MY HAIR but this is an incredible volunteering opportunity in new york area!!❤️ #volunteer #charity #community #giveback #nonprofit  </t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>2026-07-25T17:52:54Z</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@emtosta/video/7666525016258907423</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sparkly charity donation baddie let’s goooooo 🧚🏻✨💜🦄 #boomtown #boomtown2026 #boomtownoutfit #boomtownfair #festival </t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>145</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sparkly charity donation baddie let’s goooooo 🧚🏻✨💜🦄 #boomtown #boomtown2026 #boomtownoutfit #boomtownfair #festival </t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>2026-08-11T13:03:54Z</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@onthegowithflo_/video/7672759041143213335</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Idea for starting your own nonprofit or community organization!! Want to get involved in Project Happy Feet? Apply today at ProjectHappyFeet.com!!  #donation #communityservice #nonprofit #studentathletes #passionproject </t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>140</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Idea for starting your own nonprofit or community organization!! Want to get involved in Project Happy Feet? Apply today at ProjectHappyFeet.com!!  #donation #communityservice #nonprofit #studentathletes #passionproject </t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>2026-05-28T22:09:51Z</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@projecthappyfeet/video/7645068329513766157</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A much requested video… 👀 Revealing how I started my non-profit organisation in high school that not only helped me get int top Ivy Leavue and UK schools, but served as one of the greatest sources of fulfillment and learning in my life to this day! 🥹💞 #applyingtocollege #ivyleague #nonprofit #education #fyp #studytok #oxbridge </t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>130</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A much requested video… 👀 Revealing how I started my non-profit organisation in high school that not only helped me get int top Ivy Leavue and UK schools, but served as one of the greatest sources of fulfillment and learning in my life to this day! 🥹💞 #applyingtocollege #ivyleague #nonprofit #education #fyp #studytok #oxbridge </t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>2025-08-06T13:46:57Z</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@lesecritsdejulia/video/7535468646500420872</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">แล้วตี๋มองตามปิ๊ปตาละห้อย 🤟🏻 DOMUNDI CHARITY  #DMDCHARITY2024 #ดูมันดิการกุศล  #ตี๋ตี๋ป๋อ #teeteepor </t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>85</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">แล้วตี๋มองตามปิ๊ปตาละห้อย 🤟🏻 DOMUNDI CHARITY  #DMDCHARITY2024 #ดูมันดิการกุศล  #ตี๋ตี๋ป๋อ #teeteepor </t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>2026-08-12T07:32:26Z</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@_belleena_/video/7673044714999909652</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Im toby and im building the biggest nonprofit in the entire world #nonprofit #financialliteracy #bffofamerica </t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>80</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Im toby and im building the biggest nonprofit in the entire world #nonprofit #financialliteracy #bffofamerica </t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>2026-04-18T06:21:08Z</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@toby_builds/video/7629980341918256415</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Network No Go Hang Pay Me My Money Yeh😹😹@Charity #foryoupage #nsnv❤️💯🤩✅fypgoviral #500kviews </t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>75</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Network No Go Hang Pay Me My Money Yeh😹😹@Charity #foryoupage #nsnv❤️💯🤩✅fypgoviral #500kviews </t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>2025-10-18T20:51:13Z</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@opeyemi3393/video/7562667174125374727</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#funnyclips #beauty #funny #dancing #melanin @joyl.hunter @Charity 🤎🍯 </t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>75</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#funnyclips #beauty #funny #dancing #melanin @joyl.hunter @Charity 🤎🍯 </t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>2026-08-11T17:32:28Z</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@amazinggrace_xoxo/video/7672828242386029855</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">If You Price You Pay😂🎶👨‍🏫#foryoupage @Seyi Vibez #nsnv❤️💯🤩✅fypgoviral #tiktokviral #100kviews #goviral </t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>40</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">If You Price You Pay😂🎶👨‍🏫#foryoupage @Seyi Vibez #nsnv❤️💯🤩✅fypgoviral #tiktokviral #100kviews #goviral </t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>2025-04-27T08:27:12Z</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@opeyemi3393/video/7497906618005212421</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>The Inaugural Financial Audit BOXING MATCH</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>36</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>The Inaugural Financial Audit BOXING MATCH</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>2026-08-12T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@calebhammercomposer/video/7673044308177489166</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>charity purposes only ❤️💕</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>89</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=gMstJkmN8p8</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/livestreams.xlsx
+++ b/data/livestreams.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O130"/>
+  <dimension ref="A1:O204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6442,6 +6442,3387 @@
         </is>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Trưa Mùng11Tháng7Âm Mở Kinh CầuAn Mẹ Rất LinhỨng Hộ Trì Tiền Vô Như Nước MuaBán Đắt Đỏ Vạn Sự Như Ý!</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>190</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Small business owners, retailers, online sellers, entrepreneurs, and individuals engaged in trade who seek spiritual blessings for financial prosperity and booming sales.</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Commerce &amp; Spirituality</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Thật đúng dịp Mùng 11 Tháng 7 Âm này, con cũng đang cầu Mẹ phù hộ cho công việc kinh doanh cuối năm được thuận lợi, hàng hóa đi nhanh ạ. | Nghe Kinh Mẹ xong cảm giác tâm an hẳn, hy vọng Mẹ sẽ hộ trì cho dòng tiền về dồi dào để các kế hoạch đầu tư sắp tới được hanh thông. | Mẹ linh ứng lắm ạ, con xin Mẹ che chở để team bán hàng của con luôn gặp khách tốt, chốt deal thành công, vạn sự như ý trong mọi giao dịch.</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Trưa Mùng11Tháng7Âm Mở Kinh CầuAn Mẹ Rất LinhỨng Hộ Trì Tiền Vô Như Nước MuaBán Đắt Đỏ Vạn Sự Như Ý!</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>2026-08-23T03:30:00Z</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=xjXrEU9AYy0</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>SALE LƯƠNG VỀ</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>150</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Salary earners, value-conscious shoppers, typically employed individuals looking for discounts and deals, especially around payday.</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>E-commerce / Retail</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Chào ad, đợt 'Sale Lương Về' này sản phẩm chủ lực nào đang có ưu đãi tốt nhất mà ad muốn nhấn mạnh không ạ? | Thấy có link Shopee rồi, vậy khi mua qua link này mình có được áp dụng thêm mã giảm giá độc quyền nào cho livestream hoặc freeship không ạ? | Nếu muốn hỏi chi tiết hơn về chất liệu hoặc kích thước sản phẩm mà chưa thấy trên livestream, mình có thể inbox Zalo số 0985592206 để được tư vấn riêng không nhỉ?</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Dalo 0985592206 Link mua hàng sàn cam https://s.shopee.vn/40UvJkjS9I.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>2026-08-23T01:48:47Z</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=41wE-UEXq38</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>[23.8] MIỀN BẮC TUNG DEAL- SĂN SALE ẦM ẦM</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>150</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Parents (primarily mothers) of infants/toddlers, value-conscious and looking for deals on essential baby items like diapers.</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Baby Products Retail</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Cho mình hỏi là ưu đãi giảm 42k khi mua 3 gói Tã quần Molfix Oxygen này có áp dụng cùng với mã giảm giá khác từ Concung không ạ? Đang định mua tích trữ cho bé. | Thấy chương trình là 'Miền Bắc Tung Deal', vậy các tỉnh khác ở miền Trung/Nam có thể săn deal Molfix này không hay chỉ áp dụng riêng cho khu vực miền Bắc thôi ạ? Muốn mua gấu bông cho bé quá. | Mấy chương trình 'săn sale ầm ầm' kiểu này trên Concung thường diễn ra theo định kỳ không nhỉ? Mình thấy deal tã Molfix Oxygen đợt này khá hời mà sợ bỏ lỡ các đợt sau.</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Xem ngay tại: https://concung.vn/qkewar Giảm 42.000đ khi mua 3 gói Tã quần Molfix Oxygen M/L/XL/XXL Tặng quà gấu bông ...</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>2026-08-23T01:00:52Z</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=agr1_xp1XCU</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>🔥 ROBLOX 🔴 | A VER QUE SALE! 🎯💀</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>85</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Children/Teenagers, Roblox players, casual gamers, seeking entertainment and gameplay content.</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Viendo la dinámica, me intriga saber: ¿qué estrategias de monetización has visto que funcionan mejor para creadores en Roblox *actualmente*, más allá de los game passes? ¿Crees que el engagement se traduce bien a ingresos directos? | Con tantas marcas mirando Roblox para el comercio, ¿qué tipo de integración de productos virtuales crees que realmente conecta con los jugadores? Es clave que no se sienta forzado para ambos lados. | Esa emoción de 'A VER QUE SALE' es clave. ¿Qué crees que hace Roblox *bien* para que los jugadores sigan descubriendo y se queden en nuevas experiencias? Esos patrones de retención son súper importantes.</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>XxThejuan96xX #envivo #gameplay -------------------------------------------------------------------------------- •• MIS REDES SOCIALES ...</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>2026-08-23T04:12:59Z</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=aku9qM7wVDw</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Rankeando en LoL de chill (sale mal)🦊</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>85</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Casual League of Legends players and viewers, young adults, individuals seeking lighthearted gaming entertainment, viewers of smaller or hobbyist streamers.</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Gaming, Live Streaming, Entertainment</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Cuando la ranked 'sale mal' de chill, ¿sientes que es más fácil recuperarte en la siguiente o te cuesta quitarte el tilt del mapa anterior? Es un balance complicado. | Para lo de 'no saber qué contenido hacer', ¿has pensado en grabar esos momentos épicos donde 'sale mal' y luego hacer un compilado? A veces esas risas conectan más que el gameplay perfecto. | Siempre me pregunto si el 'de chill' es una estrategia activa para no estresarse o si simplemente es el mood del momento. Y ese 🦊, ¿es por algún main champ o solo good vibes?</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Hago stream cada milenio. Ya no se que contenido hacer xd Timeline de partidas: 0:00 - Inicio (no me digas) ...</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>2026-08-23T03:49:47Z</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=afcXlDDQSA0</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>🔴 UN DÍA MÁS RATEANDO EN FORTNITE 🐀😂 | ¿HOY SALE VICTORIA? 🏆</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>85</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Fortnite players, gamers, couples who game together, viewers seeking casual and entertaining gameplay streams, audience interested in 'rat' style gameplay.</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Genial el 'modo rata' en acción. Pensando en optimización, ¿qué tan consistente les ha resultado esta estrategia para la victoria final en duos, comparado con un push más directo? | Cuando están en 'modo rata', ¿cómo evalúan el riesgo-recompensa de quedarse en un punto vs. hacer un movimiento arriesgado? Esa 'inversión' de tiempo para el endgame es clave. | Con el objetivo de la victoria hoy, y viendo el meta actual, ¿creen que el 'modo rata' ofrece un mejor 'retorno de inversión' de esfuerzo que una estrategia ultra-agresiva en duos?</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>LAS RATITAS SALIERON A RATEAR! Hoy toca Fortnite en pareja, jugando con mi polola y activando el MODO RATA al ...</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>2026-08-23T03:44:07Z</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=MpRDKkK2YMk</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>sale un codsito?? - Baty Reyes #codm</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>100</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Mobile gamers, Call of Duty: Mobile players, fans of Baty Reyes, individuals interested in casual gaming content.</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Gaming, Live Streaming</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Baty, qué onda con esa CBR4, ¿la sigues usando en ranked o ya te pasaste a la Kilo? Siento que la CBR es más consistente para rushear ahora. | Con el último update, ¿qué opinas de Crossfire en Dominio? A mí se me complica un montón si el otro equipo controla bien el edificio central para la B. | Siempre me cuesta un montón contra los snipers agresivos en BR. ¿Algún consejo para pushearles sin que me den un headshot al instante? ¿Depende mucho del perk?</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>codm #callofdutymobile #batyreyes.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>2026-08-23T03:24:31Z</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=kQiF_QFJ0aA</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Tư vấn săn sale cơ bida môi ngày trên Live trym</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>95</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Billiard players, enthusiasts, or individuals looking to purchase billiard cues, especially those interested in finding daily deals or discounts through a livestream format.</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Billiards Equipment Retail, Sporting Goods, E-commerce</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Thanh Minh chia sẻ thêm xíu được không là mình tập trung săn sale các dòng cơ bida phổ biến hay có bất ngờ với những mẫu cao cấp trên livestream mỗi ngày ạ? | Với lịch livestream săn sale cơ bida mỗi ngày, Thanh Minh có mẹo nào để khách hàng dễ theo dõi và không bỏ lỡ các deal hot, đặc biệt với những ai muốn mua số lượng không? | Mình thấy địa chỉ xưởng ở Hiệp Bình Chánh, vậy Thanh Minh có thể bật mí quy trình kiểm tra chất lượng cơ bida trước mỗi phiên săn sale trên live không? Rất quan tâm về độ bền và giá trị đầu tư lâu dài.</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Billiards Thanh Minh ◅ Địa Chỉ Công Ty : 299 , Lê Hồng Phong , phường 2 , Quận 10 . Địa Chỉ Xưởng : Hiệp Bình Chánh , TP .</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>2026-08-23T03:00:21Z</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=yw4vr5LrSAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Y SI ME SALE UN ROJO❓#arenabreakoutinfinite</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>85</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Sale
+Mua Bán
+Kinh Tế</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Sorrelowski, si te sale un 'rojo', ¿cuál es tu estrategia principal? ¿Vas directo a por el high-risk/high-reward o intentas asegurar la extracción primero? | Pensando en lo del 'rojo', ¿hay alguna configuración de arma o tipo de munición específico que uses para maximizar tus chances contra ese tipo de encuentro, o prefieres ser más versátil? | Si consigues sacar un 'rojo' de la raid, ¿sientes que vale la pena el riesgo adicional para venderlo en el mercado o prefieres usarlo tú mismo para futuras incursiones de alto valor?</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>REDES SOCIALES ₪ ₪ ₪ ₪ ₪ ₪ ₪ ₪ ₪ ₪ https://www.youtube.com/@Sorrelowski https://www.tiktok.com/@sorrelowski ...</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>2026-08-23T02:26:53Z</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=fC_QamIaI0Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Online Payday Sale</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>98</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>General consumers, employees with disposable income, individuals seeking deals and discounts around their payday.</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>E-commerce / Retail</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Curious if there are any specific bundle deals or loyalty program bonuses planned for this payday sale, especially for repeat customers looking to maximize value? | Will there be any specific payment gateway promotions or cash-back offers tied to certain banks during this online payday event? Sometimes those really make a difference for bigger purchases. | Wondering if there will be particular 'flash sale' windows or early bird access for some of the higher-demand items today? Always tricky to catch those on payday sales!</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>2026-08-22T23:59:54Z</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=_qJX4MU346Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>23/8 Giam Can ngay 13(Mua lam vch)</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>85</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Individuals interested in health, fitness, and personal weight loss journeys; potentially consumers of health-related products.</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Health &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Thắng Đông Anh * Lịch stream: Ca sáng:8h-11h Ca chiều: 2r-5h Ca tối: flex * Thông tin của mình - FB cá nhân: ...</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>2026-08-23T01:18:05Z</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=qppQT8ld4nA</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Can AI Really Read an Ultrasound? Watch MUA-AI Interpret Images in Real Time!</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>85</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Sale
+Mua Bán
+Kinh Tế</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>LIVE: Can AI Really Read an Ultrasound? Watch MUA-AI Interpret Images in Real Time!** Join **Medical Ultrasound Academy ...</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>2026-08-22T19:29:45Z</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=_X1ic4ZSK70</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Cổ Nhân Dạy - Dù Có Tiền Tỷ Cũng Đừng Mua 6 Thứ Này! Về Già Nhục Lắm</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>85</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Sale
+Mua Bán
+Kinh Tế</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>CHỈ CẦN DẬY LÚC 3 ĐẾN 5 GIỜ SÁNG, BẠN SẼ THAY ĐỔI CẢ CUỘC ĐỜI | TRIẾT LÝ CUỘC SỐNG | LỜI DẠY CỔ NHÂN.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>2026-08-22T01:47:29Z</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=2e2xdDM_TTM</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>[Trực Tiếp] | MUA SẮM ONLINE - NGẬP TRÀN ƯU ĐÃI - ĐỘC QUYỀN TRÊN SCJ TV SHOPPING</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>85</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Sale
+Mua Bán
+Kinh Tế</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Chào mừng bạn đến với kênh mua sắm trực tiếp chính thức của SCJ TV SHOPPING trên YouTube! Giờ đây, bạn có thể xem ...</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>2026-08-19T13:02:44Z</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=0nlpfooY9lY</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>SỰ THẬT KINH HOÀNG TIỀN ĐIỆN NƯỚC: Dân Kêu Cứu Bác Tô Lâm, Bà Phương Hằng Vạch Trần Sự Thật!</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>85</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Sale
+Mua Bán
+Kinh Tế</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>SỰ THẬT KINH HOÀNG TIỀN ĐIỆN NƯỚC: Dân Kêu Cứu Bác Tô Lâm, Bà Phương Hằng Vạch Trần Sự Thật! #tiendien ...</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>2026-08-23T03:26:11Z</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=TZryfBt-PQU</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>🏆 GIẢI PICKLEBALL NỘI BỘ CLB KINH MÔN</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>85</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Sale
+Mua Bán
+Kinh Tế</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>GIẢI PICKLEBALL NỘI BỘ CLB KINH MÔN NGÀY THI ĐẤU: 23/ 08/ /2026. ĐỊA ĐIỂM: CỤM SÂN TRÚC LỘC PICKLEBALL.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>2026-08-23T00:19:54Z</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=j3fqHxeKPqk</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>🔴 Kinh Di Giáo 24/7 | Lời Di Huấn Cuối Cùng Của Đức Phật • Tụng Kinh An Lạc • Thích Trí Bửu</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>85</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Sale
+Mua Bán
+Kinh Tế</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Kinh Di Giáo 24/7 là livestream tụng trì những lời di huấn cuối cùng của Đức Phật Thích Ca Mâu Ni trước khi Ngài nhập Niết-bàn.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>2026-08-20T07:06:42Z</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=z8uHZqEU_k0</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>🔴Vu Lan Báo Hiếu Nghe Kinh Này Tỷ Lần Rơi Lệ, Báo Đáp Công Ơn Cha Mẹ</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>85</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Sale
+Mua Bán
+Kinh Tế</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>giacngochantam Nam mô Đại Hiếu Mục Kiền Liên Bồ Tát. Có những yêu thương trên đời, khi còn ở bên ta, ta cứ ngỡ đó là điều ...</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>2026-08-12T16:40:00Z</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=z-UcCMZfs7k</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Kinh Địa Tạng Trọn Bộ 🙏 Bài Kinh Linh Ứng Nhất – Giải Nghiệp, Gia Đạo Bình An</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>85</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Sale
+Mua Bán
+Kinh Tế</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Kinh Địa Tạng Trọn Bộ Bài Kinh Linh Ứng Nhất – Giải Nghiệp, Gia Đạo Bình An Nghe Kinh Địa Tạng Trọn Bộ giúp người nghe ...</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>2026-08-14T05:00:39Z</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=LB1AnepCIqo</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Tụng Kinh Dược Sư -  Nghe Mỗi Ngày Cầu Bình An , Hết Bệnh Hết Khổ, Tiêu Tai Giải Nạn | Kinh Tụng</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>85</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Sale
+Mua Bán
+Kinh Tế</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>KINH DƯỢC SƯ – Tụng Kinh Dược Sư - Nghe Mỗi Ngày Cầu Bình An, Tiêu Tai Giải Nạn, Hết Bệnh Hết Khổ Kinh Dược Sư là một ...</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>2026-08-16T10:10:00Z</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=8Bdsk-FID3U</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Business Growth TV 24/7 | Entrepreneurship, Leadership, Marketing &amp;amp; Small Business Success</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>340</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Small Business Owners, Entrepreneurs, Business Leaders, Marketing Professionals, Startup Founders</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Business Services / Consulting / Education / Marketing</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Hey team, when we're talking 'marketing for small business success,' what's a lesser-known strategy that significantly boosts enterprise value for a *potential sale*, not just daily lead gen? | Thinking about the 'leadership' aspect for growth: are there specific operational redundancies or 'owner-dependent' systems small businesses often neglect that really bite them when trying to scale or get acquired? | With 'real-world strategies' in mind, what's one key move a small business can make early on to build a truly *defensible* competitive moat, beyond just a unique product, that makes it an attractive acquisition target?</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Welcome to Business Growth TV 24/7, powered by The Prosperity Lounge — nonstop conversations, strategies and real-world ...</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>2026-08-15T17:13:27Z</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=svYQjgEnlGo</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Business Story of the Week 24/7 Live: Entrepreneurial Insights &amp;amp; Growth Mindset</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>200</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Entrepreneurs, small business owners, aspiring business leaders, professionals seeking growth, individuals interested in business strategy and personal development within a business context.</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Business, Entrepreneurship, Professional Development</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Curious, when focusing on entrepreneurial insights, how crucial is the *story behind the pivot* in building long-term brand resilience versus just showcasing the success? | Great to hear about growth mindset. What specific tactics do you recommend for founders to instill that *culture of iterative learning* across their early-stage team, especially when funding is tight? | For the business story you're covering, how did they initially *validate their problem-solution fit* without significant upfront capital? Always interested in those lean market entry strategies.</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Subscribe to the Channel: https://www.youtube.com/channel/UCX59Z1-L4LBe7-qKEz_-QzA/?sub_confirmation=1 Welcome to ...</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>2026-06-04T00:05:00Z</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=xXk768Fe064</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>RUQYAH DUA TO INCREASE RIZQ, BARAKAH, CUSTOMERS &amp;amp; SALES - CURE FOR BUSINESS STRUGGLES &amp;amp; PROBLEMS!</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>180</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Muslim business owners, entrepreneurs, or sales professionals seeking spiritual intervention and guidance from the Quran to resolve business struggles and boost sales and customers.</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Islamic Spiritual Services</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>For small business owners balancing daily operations, what's a realistic routine or frequency for implementing this Al Quran Ruqyah Shariah dua to see consistent growth in sales and barakah? | Many businesses face periods of stagnant customer acquisition or unexpected supply chain issues. Does the Ruqyah Shariah dua offer specific guidance for overcoming these particular 'business struggles and problems'? | It's powerful to think about increasing rizq and barakah. From a practical business standpoint, how have you seen the increase in barakah specifically translate into tangible improvements like better sales conversion rates or stronger customer loyalty?</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Most powerful Al Quran Ruqyah Shariah dua to increase rizq, barakah, customers and sales — delivering a powerful cure for ...</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>2026-08-22T20:25:00Z</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=kJ5N8YO-5I8</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>ENTREPRENEURSHIP SYMPOSIUM</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>145</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Aspiring entrepreneurs, small business owners, students interested in business, community members seeking business insights, individuals looking for tools and strategies for business growth.</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Entrepreneurship, Education, Faith-based Business</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>For founders eyeing quick scaling, what's a common mistake you see when trying to penetrate new markets, particularly around building out robust distribution channels or strategic local partnerships? | Love to hear the panel's perspective on identifying genuine market white space. What’s a signal you look for beyond just a perceived 'gap' – maybe something about unarticulated needs or technological leverage that indicates true breakthrough potential? | Beyond traditional VC, what are some underutilized funding strategies or non-dilutive capital sources that early-stage founders should really be exploring right now, especially those prioritizing sustainable revenue over hyper-growth?</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Welcome to University Seventh-day Adventist Church. We invoke rich blessings upon you from our Father in Heaven. Special ...</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>2026-08-23T06:58:52Z</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=xKkulrprVlE</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>TMP SUNDAY CELEBRATION SERVICE | ENTREPRENEURSHIP &amp;amp; INVESTMENT.</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>145</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Entrepreneurs, aspiring business owners, investors, individuals seeking financial growth and business insights.</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Business, Finance, Entrepreneurship</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Given the JHB context for this service, I'm curious if the discussion will touch on specific high-growth sectors or underserved markets where new entrepreneurs can make a significant impact and attract early investment. | On the investment side, I'm particularly interested in hearing strategies for securing seed funding within the local Strydom Park/JHB ecosystem. What are some key pitfalls to avoid when pitching for initial capital? | Considering this is a 'Celebration Service' focusing on Entrepreneurship &amp; Investment, I'm curious about the role of mentorship and community support networks in sustaining entrepreneurial growth beyond just securing capital. Any thoughts on fostering that in JHB?</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Dates: 23 AUGUST 2026 Venue: The Master's Place, 4 Commercial Avenue, Strydom Park, Johannesburg Guest Minister: Ms ...</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>2026-08-23T07:35:46Z</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=8PdW_zhyQ-c</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Blues Rock Entrepreneurs - Motivational Guitar Playlist Vision, Focus &amp;amp; Business Mindset - 4 Hours</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>145</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Blues/Rock Musicians or aspiring entrepreneurs seeking business guidance, motivation, and skill development for their music ventures.</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Music, Entrepreneurship, Self-help</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>How does the structure of a classic 12-bar blues, with its clear progression, offer a mental framework for entrepreneurs when they're mapping out a complex project or a long-term business vision? | This 'HollowSoul Blues' really gets into deep emotions. How do you suggest entrepreneurs channel that soulful intensity to maintain focus and conviction during a tough sales cycle or when facing market resistance? | For cultivating that 'focus' state, what specific elements of a slow blues guitar solo – maybe the bends or sustain – do you find most effective for sparking new ideas when I'm reviewing a P&amp;L or sketching out a new service offering?</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Welcome to HollowSoul Blues , a place where deep emotions, soulful guitars, slow blues, and timeless melodies come ...</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>2026-08-23T08:07:45Z</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=dIYqsvsN21c</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Business &amp;amp; Career (1st) Service-Dominion City Awoyaya| 23 Aug 2026</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>85</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Professionals, Entrepreneurs, Business Owners, Career-minded individuals seeking development and guidance.</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Religious (with Business &amp; Career focus)</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Given this is the *first* Business &amp; Career session for Service-Dominion City Awoyaya, I'm keen to hear what specific challenges local businesses here are currently navigating. Maybe talent acquisition or market access? | Intrigued by the 'Service-Dominion' part of the title. For those of us running businesses, how do you practically integrate those values into daily operations or strategic planning to drive growth within the community? | From a career perspective, especially for young professionals in Awoyaya, what's one non-obvious skill or networking strategy that could make a significant difference in their trajectory, given the local economic landscape?</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>2026-08-23T07:29:47Z</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=KnHaPBwSBGU</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>BUSINESS, CAREER &amp;amp; LEADERSHIP SERVICE II 23-08-2026 II 1ST SERVICE</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>85</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Professionals, entrepreneurs, and leaders seeking faith-based guidance for business and career growth, or individuals interested in spiritual development for their professional lives.</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Faith-based Professional Development/Ministry</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Rev. Abba, keen to hear your thoughts on navigating business growth targets while upholding deep spiritual integrity. How do we balance ambition with our 'wordalive' principles in competitive markets? | Many leaders struggle with long-term vision amidst daily pressures. What's a key spiritual discipline or 'wordalive' insight you recommend for maintaining that resilience and clarity? | For those of us aiming to expand our reach or overcome client acquisition challenges, what 'wordalive' perspective helps reframe these obstacles into opportunities for genuine purpose-driven impact?</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>LIKE, COMMENT &amp; SHARE #revgodwinabba #wordalive #LiveBroadcast #share #word #worship #praise #like #comment ...</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>2026-08-23T06:35:57Z</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=YpKPtpWcZ5Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>SUNDAY SERVICE || BUSINESS ACTIVATION CODE || TRADE FAIR || 23RD AUGUST, 2026.</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>95</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Small business owners, entrepreneurs, sales and marketing professionals, individuals seeking business growth and networking opportunities, those interested in faith-based business principles.</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Business Development, Entrepreneurship, Sales &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>SUNDAY SERVICE || BUSINESS ACTIVATION CODE || TRADE FAIR || 23RD AUGUST, 2026. MINISTERING: PST. OLAKUNLE ...</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>2026-08-23T06:36:53Z</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=jc5HX83q8vk</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>🔴 LIVE | No Doctor, Yet the Business Continued for 2 Years? | ASMITATVLIVE</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>85</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>General public, concerned citizens, viewers interested in public health and regulatory issues in the healthcare sector.</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Healthcare (News Reporting)</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2 years is a long time for a nursing home to operate without proper medical staff. Were there any official inspections or audits during that period, or was it entirely off the radar until the raid? | Curious about the actual *business model* here. Without a doctor, how were patient cases being handled or billed, and what allowed them to maintain operations for so long from a financial standpoint? | Beyond the immediate shutdown post-raid, what are the longer-term consequences for the operators of this nursing home, especially concerning any fraudulent billing or patient safety violations over those two years?</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>LIVE | ଡାକ୍ତର ନାହାନ୍ତି, ତଥାପି ଚାଲିଥିଲା କାରବାର? ଚଢ଼ାଉ ପରେ ନର୍ସିଂହୋମ ...</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>2026-08-23T04:59:22Z</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=6kYCoxeDvRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>SPECIAL BUSINESS SERVICE TAGGED:OCCUPY WITH CHRIS EMMANUEL  23/8/2026</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>95</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Small business owners, aspiring entrepreneurs, real estate investors, individuals seeking business growth strategies, financial education seekers, direct sales professionals.</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Business Coaching, Entrepreneurship, Financial Services</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Chris, curious about the 'OCCUPY' strategy – for an SMB, what's typically the biggest *practical* hurdle in executing an aggressive market positioning without totally overstretching resources? Budget or team bandwidth usually? | Following up on 'OCCUPY,' once a business has established its foothold, how do you see them best fending off those inevitable competitive counter-moves for sustained market presence? It's a real balancing act. | Hi Chris, on the 'OCCUPY' concept, what's your go-to method for businesses to pinpoint those *truly* underserved market niches that are ready for aggressive capture, not just slow, incremental growth? That initial targeting feels key.</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>SPECIAL BUSINESS SERVICE TAGGED:OCCUPY WITH CHRIS EMMANUEL 23/8/2026 Connect with Chris Emmanuel: ...</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>2026-08-22T16:13:09Z</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=PGE45u68Ei4</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>💚 Music for Plants 🎵 Relaxing Plant Growth Music 24/7 🌱</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>85</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Sale 
+Business</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Welcome to Houseplant 101's relaxing music for plants stream — peaceful background music created for plant lovers, indoor ...</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>2026-08-23T08:32:31Z</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=s6mwUhK4IJ8</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Growth III || Youth Sunday Service || 23-08-26</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>85</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Church members, youth, individuals seeking spiritual worship</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Religious/Non-profit</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Growth III || Youth Sunday Service || 23-08-26 Join us as we worship . Church account Details: IE07AIBK93745223502061.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>2026-08-23T08:01:57Z</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=FBbEzHT04qA</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>CELEBRATION SERVICE | PREPARE FOR GROWTH | PST GEORGE PAUL</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>85</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Sale 
+Business</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Welcome to our Sunday Celebration service We are truly grateful that you've joined us today. Wherever you're watching from, ...</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>2026-08-23T07:49:43Z</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=1GcLi5D3t9Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026 CONFERENCE SUNDAY || BELIEVER’S BALANCED GROWTH || REV&amp;#39;D NATHANIEL EKUNDAYO</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>85</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Sale 
+Business</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>AUGUST 23RD 2026.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>2026-08-23T07:03:53Z</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=LYGni8mc3v0</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Podcast Replay | Socially Awkward Podcast: Hospitality Marketing</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>85</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Business Decision Maker</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Sales &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>This is a live replay of our best episodes, enjoy! Thanks for tuning in to Socially Awkward, the hospitality marketing podcast where ...</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>2026-08-19T19:54:43Z</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=o2-KSuMkE1U</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>live  gold trading everyday / XAUUSD &amp;amp; BTC/ Trading with My own strategy</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>85</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Sale 
+Business</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Admin only trade on demo accounts.This is just a video to learn about forex trading, and also not an invitation or advertisement to ...</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>2026-08-23T08:42:29Z</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=VTut1o_pF78</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Personal Branding Strategy  ala Rizqiani Putri</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>90</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Entrepreneurs, small business owners, freelancers, consultants, coaches, sales professionals, and anyone looking to leverage their personal brand to attract clients and drive sales for their business.</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Business Development, Marketing, Entrepreneurship, Coaching, Consulting</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>2026-08-23T08:17:53Z</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=Z9jxZrcpNW0</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>LIVE Bitcoin &amp;amp; Gold Trading Strategy | 23 AUG | Market Analysis #gold #cryptotrading #livetrading</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>85</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Sale 
+Business</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>LIVE Bitcoin &amp; Gold (XAUUSD) Trading Strategy | Live Market Analysis #gold #cryptotrading #livetrading Welcome to today's LIVE ...</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>2026-08-23T07:34:21Z</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=eMfYfF7nY6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>map editor for grand strategy game in godot</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>85</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Sale 
+Business</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>https://rjljones.itch.io/grandfantasy.</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>2026-08-23T06:56:11Z</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=ItWP4hyio9g</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Super sale Dhmaka Rakhi special 🥳💥💥💥📲9050866606</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>76</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Sale
+Business</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=Fu3chRBRlD0</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>CNBC TV18 24x7 LIVE: Stock Market LIVE Updates | Nifty &amp; Sensex Live | Share Market | Business News</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>75</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Sale
+Business</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=1_Ih0JYmkjI</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>LIVE 24/7 Domains For Sale | Premium Domain Marketplace</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>75</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Sale
+Business</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=fQOMRgEHsEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>kids wear stitched pattu lehenga collection best sale 🥳#9100831197</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>75</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Sale
+Business</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=YJLWz2MvYIQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>24/7 UAE Business &amp; Real Estate Hub | Expert Interviews &amp; Market Insights | MIRA Business FM</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>75</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Sale
+Business</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=61ItflDkggY</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Як відкрити бізнес (БЕЗ КОМАНДИ) по американській системі ONE PERSON BUSINESS</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>75</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Sale
+Business</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=SdV7XI6k5WA</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>​🔴 LIVE: Nikum Fashion MEGA SALE continues! Crazy Discounts on Sandals &amp; Clothes!</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>215</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=ge4xLlledOo</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>raksha bandhan special offer and sale</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>160</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=n5ZYjNafPJo</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Super Sunday Anghrakha Special Exclusive Clearance Sale!!!!</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>155</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Recruiter, HR Manager</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Recruitment</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=nk3ED8Yupic</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>🔴 Live Flash Sale Adenium Bunga Tumpuk Dan Karakter (23 Agustus 2026) #rachmannursery #adenium</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>155</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=v5bzraFACwU</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Sakshi Suit Collection is live beautiful suit 😍 Sale Sale Sale 😍 #fashion #live #suits #viral #suit</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>150</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=OXxaFUZQIBE</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>🔥💃🚀🚛 Shravanam superfast sale 💥beats work, bits 💥offer, live💥ph 7013425271💥 don’t miss✨</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>95</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Recruiter, HR Manager</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Recruitment</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=sMII-zb-uto</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>New Winter Stock Beautiful SALE Dresses</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>90</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=-fKhPQsLqiw</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>sravanam maha sale</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>90</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=XISDLxC-N4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>The Nandlaala Collection is live…Sunday special sale live..Booking no-9871800667</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>90</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=JiuDerZU1pw</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>jagdamba collection is live❤️ Sunday sale dhamaka#8641069309</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>90</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=psKQLLDaIU0</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>💕MAHA SALE COTTON SUITS FESTIVE SUIT ☎️ 9548364102</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>90</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=zN9-uvFyreE</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Sunday special sale 👜👜👜booking no 8860447712</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>90</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=Qa83F1E8ayY</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>SALE LƯƠNG VỀ</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>90</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=ml9AsHQOxrU</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>JADULAN KOLEKSIAN REDY||SALE MINGGU CERIA😍</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>90</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=47kmamY4w9g</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>150 గజాల North Facing G+1 House For Sale | Nagaram Near ECIL | Hyderabad House Tour</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>90</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=henjzMJylpc</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>CULTE DU DIM 23-08-2026 | SOIS SALE POUR ETRE UN PANNEAU PUBLICITAIRE | Pasteur : Elie KATALAYI</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>90</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=7JEfohexZ6w</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>BITCOIN FOREX AI ANALYZER DASHBOARD</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>40</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Ai Automation</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=Zoq2XKS7N60</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>GOLD XAU Ai Market Analyzer Live</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>40</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Ai Automation</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=3VstsarTbn0</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>POCKET OPTION LIVE TRADING ➜ POCKET OPTION AI TRADING | POCKET OPTION SIGNALS | POCKET OPTION 2026</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>40</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Ai Automation</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=sFWPGZ32mY0</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>AI Live Radio - Music, News, Podcasts, Weather</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>40</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Ai Automation</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=b41eVHUU0mc</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>BINARY OPTIONS LIVE TRADING ➜ QUOTEX TRADING STRATEGY | BINARY TRADING LIVE | AI TRADING LIVE</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>40</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Ai Automation</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=0_KALTqzQzM</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>The Agentic Web Live: Honeybot Observatory &amp; AI Crawler Telemetry</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>40</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Ai Automation</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=9TMftX7BDYI</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Build with AI | Claude Code, OpenClaw, Cursor and more | 24/7 Live</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>40</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Ai Automation</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=8vaOW_2EpLc</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>CAN YOU BUILD AN AI AGENT—or only use one?</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>40</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Ai Automation</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=Ea4MMH_WcoQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Live Gold (XAUUSD) Trading with EA bot | AI-Based Strategy</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>40</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Ai Automation</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=3xD_Di85Gsc</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>My Personal JARVIS AI 🔴 LIVE — Sara v2 Review And Guide | Ethical CodeX</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>40</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Ai Automation</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=3J8wYG3_kpc</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Future Intelligence 24/7 ⚡ Deep Tech Documentaries | AI Longevity Future of Work</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>40</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Ai Automation</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=mycW8FFaX2A</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>This 24/7 AI-Generated TV channel will make you question reality.</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>40</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Ai Automation</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=6xuQnM810Zw</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/livestreams.xlsx
+++ b/data/livestreams.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Livestreams" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Livestreams" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O204"/>
+  <dimension ref="A1:O217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9813,15 +9813,343 @@
           <t>YouTube</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr"/>
-      <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr">
         <is>
           <t>https://youtube.com/watch?v=6xuQnM810Zw</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
-      <c r="L204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Delma #32 student charity member</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>90</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=VT3j0maWxx4</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Charity Stream every Brilliant = 3$ (Chat votes to where) 🫂💌👽 !ip !elephant !course !discord</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>80</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=BZDLqXTYTTU</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>【直播】 2026-08-23 大專新星 - 宏遠(慈善)籃球聯賽 STAR PATH (CHARITY) BASKETBALL LEAGUE APEX巔峰 vs C &amp; W Charity</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>80</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=ljMAh-SuciU</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>【直播】 2026-08-23 大專新星 - 宏遠(慈善)籃球聯賽 STAR PATH (CHARITY) BASKETBALL LEAGUE SV vs VC</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>80</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=-mmqCNeIIow</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>RIVER NETWORK TV, Church, Charity, DERBYSHIRE Terry &amp; Jill Eckersley</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>80</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=hWKwOuAhZVc</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>🔴 LIVE: Adam Littler XI vs Michael Littler XI | Julie Littler Memorial Charity Fixture</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>80</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=jaoHESV8-RQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>kalayami cultural charitable trust is live</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>58</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=CaNr-dsHJt8</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Power And Authority(Part 9) - Christingle Fellowship Centre</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>51</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=GvXLs4slBcM</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Morning Service - 23 August 2026 Bon Accord Free Church</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>49</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=mNrDxsjQ_1g</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Unity &amp; Diversity Culture Service - Pauline Dawkins - Livestream - 23.08.2026</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>44</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=RJBVodYmtdQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>[SUN. 23RD-AUG-2026AM] SUNDAY MORNING SERVICE</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>39</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=oX8gp-vPlQo</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Welcome to our morning worship on Sunday 23rd August 2026.</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>35</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=SJdGhQYHiXI</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Back to school sunday 16th August 2026</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>33</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="inlineStr"/>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr"/>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=1hkGi2ISc5g</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr"/>
+      <c r="L217" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/livestreams.xlsx
+++ b/data/livestreams.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O217"/>
+  <dimension ref="A1:O227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10133,23 +10133,285 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
-      <c r="E217" t="inlineStr"/>
-      <c r="F217" t="inlineStr"/>
       <c r="G217" t="inlineStr">
         <is>
           <t>YouTube</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr"/>
-      <c r="I217" t="inlineStr"/>
       <c r="J217" t="inlineStr">
         <is>
           <t>https://youtube.com/watch?v=1hkGi2ISc5g</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
-      <c r="L217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Stand Firm in Charity</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>90</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=f5Zsg66Bm1k</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Faith, Hope, &amp; Charity Ministries is now Live.</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>90</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=Gun1KzkOnec</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>TV WEST LIVE: Agacencwire 23.08.2026 || Charity Mbabazi &amp; Loice Gava</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>80</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=LddnbZp_Slc</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Ebbsfleet United Fans v Dorking Fans LIVE Charity Match</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>80</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=LmUf1LN4Pe4</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Amawanga Gamutende Charity concert</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>80</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=nFb7cGiMNxY</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>mummy charity ufomba is live! hi guys</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>80</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=40u2t4bagzM</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Inaugural Manatee Classic Charity Pickleball Tournament - Sunday Mixed Doubles</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>80</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=dNyQJQ37OEg</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>LIVE - charity stream planning + playing the Gendo the Gatherer demo</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>80</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=8PWC0LEZQBw</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Evening Service - 23 August 2026 Bon Accord Free Church</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>45</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=sq0MChRAiWw</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Sunday Service | Cathy Merchant | August 23, 2026 | Canadian Memorial United Church</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>39</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Charity Decision Maker</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Charity</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Thấy chủ đề này khá thú vị, không biết thực tế triển khai có hay gặp rào cản gì không mọi người? | Góc nhìn rất thực tế. Cho mình hỏi thêm về case study cụ thể ở mảng này được không? | Phần này mình cũng đang quan tâm. Mọi người thường dùng công cụ gì để giải quyết bài toán này?</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr"/>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>https://youtube.com/watch?v=C7cuVfyrMgE</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr"/>
+      <c r="L227" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
